--- a/outputs/机器人本体产品主表.xlsx
+++ b/outputs/机器人本体产品主表.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R06242a5d99524c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="2" r:id="Rfab33a3904874aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="3" r:id="R4144183da65c4d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="4" r:id="Rd5bbee69f4d64883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="5" r:id="Rc0eb9c952cd74709"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R8f89f76bdb56437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="2" r:id="R632c708e5fe44dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="3" r:id="Rcbc6f7c0ce194d38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="4" r:id="R7d77b1a83b984152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="5" r:id="Re1177449639741f4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="model_id"/>
@@ -1475,7 +1475,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re89f68ab153c410c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6200ac30e8d941f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2584,7 +2584,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88ad26e95f4e4255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3e26bbeeb0477e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3216,7 +3216,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ff5b907c53843b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac865f237304d88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3474,7 +3474,7 @@
         <x:v>D1（擎骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>external-private/智动力/D1（擎骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/D1（擎骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str"/>
       <x:c r="G9" s="15" t="str">
@@ -3501,7 +3501,7 @@
         <x:v>JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>external-private/智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str"/>
       <x:c r="G10" s="15" t="str">
@@ -3528,7 +3528,7 @@
         <x:v>JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>external-private/智动力/JUNO1-P（智骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str"/>
       <x:c r="G11" s="15" t="str">
@@ -3555,7 +3555,7 @@
         <x:v>L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>external-private/智动力/L1（灵骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str"/>
       <x:c r="G12" s="15" t="str">
@@ -3582,7 +3582,7 @@
         <x:v>全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>external-private/智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
+        <x:v>sources/raw/01_智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str">
         <x:v>2026-07-25</x:v>
@@ -3599,23 +3599,21 @@
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>src_tianji_marvin</x:v>
+        <x:v>src_zdl_ha</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>tianji_marvin_m6ccs</x:v>
+        <x:v>zdl_ha</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
+        <x:v>人形臂（HA系列）.pdf</x:v>
       </x:c>
       <x:c r="E14" s="15" t="str">
-        <x:v>external-private/天机智能/Marvin系列 三折页 250721-CN.pdf</x:v>
-      </x:c>
-      <x:c r="F14" s="15" t="str">
-        <x:v>2025-07</x:v>
-      </x:c>
+        <x:v>sources/raw/01_智动力/人形臂（HA系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="str"/>
       <x:c r="G14" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -3623,7 +3621,200 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I14" s="15" t="str">
+        <x:v>待纳入机械臂专项对比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="42" customHeight="1">
+      <x:c r="A15" s="15" t="str">
+        <x:v>src_zdl_fa</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="str">
+        <x:v>zdl_fa</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
+        <x:v>桌面臂（FA系列）.pdf</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="str">
+        <x:v>sources/raw/01_智动力/桌面臂（FA系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="str"/>
+      <x:c r="G15" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H15" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I15" s="15" t="str">
+        <x:v>待纳入机械臂专项对比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="42" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>src_flexiv_rizon4_manual</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>flexiv_rizon4</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
+        <x:v>Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="str"/>
+      <x:c r="G16" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H16" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I16" s="15" t="str">
+        <x:v>待纳入机械臂专项对比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>src_flexiv_rizon_datasheet</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="str">
+        <x:v>flexiv_rizon</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
+        <x:v>拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H17" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="str">
+        <x:v>待纳入机械臂专项对比</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="42" customHeight="1">
+      <x:c r="A18" s="15" t="str">
+        <x:v>src_flexiv_grav_manual</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="str">
+        <x:v>flexiv_grav</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
+        <x:v>星擎用户手册_V1.0_202404(2).pdf</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/02_Grav_星擎/星擎用户手册_V1.0_202404(2).pdf</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="str">
+        <x:v>2024-04</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H18" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="str">
+        <x:v>末端执行器资料待结构化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="42" customHeight="1">
+      <x:c r="A19" s="15" t="str">
+        <x:v>src_flexiv_ft_datasheet</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="str">
+        <x:v>flexiv_ft</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
+        <x:v>拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/03_FT_拂晓传感器/拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="str"/>
+      <x:c r="G19" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I19" s="15" t="str">
+        <x:v>力传感器资料待结构化</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="42" customHeight="1">
+      <x:c r="A20" s="15" t="str">
+        <x:v>src_tianji_marvin</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="str">
+        <x:v>tianji_marvin_m6ccs</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
+        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="str">
+        <x:v>sources/raw/03_天机智能_Marvin/01_Marvin双臂/Marvin系列 三折页 250721-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H20" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I20" s="15" t="str">
         <x:v>单臂/双臂模块参数，不含标准底盘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="42" customHeight="1">
+      <x:c r="A21" s="15" t="str">
+        <x:v>src_material_index</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="str"/>
+      <x:c r="C21" s="15" t="str">
+        <x:v>内部索引</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="str">
+        <x:v>供应链材料索引.md</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="str">
+        <x:v>sources/raw/00_索引/供应链材料索引.md</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="str"/>
+      <x:c r="G21" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H21" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I21" s="15" t="str">
+        <x:v>原目录索引的归档副本</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3632,7 +3823,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra76ca5ab740f4230"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re134595142734ffa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/机器人本体产品主表.xlsx
+++ b/outputs/机器人本体产品主表.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R8f89f76bdb56437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="2" r:id="R632c708e5fe44dd9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="3" r:id="Rcbc6f7c0ce194d38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="4" r:id="R7d77b1a83b984152"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="5" r:id="Re1177449639741f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="Rc6adbc6eae404cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="2" r:id="Rad89cee4aa3d4cc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="3" r:id="R614e916d26b44e97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="4" r:id="R448bd1bface44fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="5" r:id="R5f975c33ac3642b0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -234,7 +234,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenarioScores" displayName="ScenarioScores" ref="A6:M16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenarioScores" displayName="ScenarioScores" ref="A6:M23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="厂商"/>
     <x:tableColumn id="2" name="型号"/>
@@ -255,7 +255,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RobotMasterData" displayName="RobotMasterData" ref="A3:AK13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RobotMasterData" displayName="RobotMasterData" ref="A3:AK20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="37">
     <x:tableColumn id="1" name="model_id"/>
     <x:tableColumn id="2" name="vendor"/>
@@ -300,7 +300,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SupplierQuestions" displayName="SupplierQuestions" ref="A3:J21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SupplierQuestions" displayName="SupplierQuestions" ref="A3:J35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="question_id"/>
     <x:tableColumn id="2" name="vendor"/>
@@ -318,7 +318,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="model_id"/>
@@ -656,22 +656,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
-        <x:v>星尘</x:v>
+        <x:v>星海图</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>Astribot S1</x:v>
+        <x:v>Galaxea R1 Pro 2026</x:v>
       </x:c>
       <x:c r="D7" s="16" t="n">
-        <x:v>3.95</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="F7" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G7" s="15" t="str">
-        <x:v>论文确认全向底盘；量产配置、接口和工业认证资料不足</x:v>
+        <x:v>三舵轮全向和工作空间契合；重复精度0.5mm且机械臂无制动器是主要风险</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
@@ -679,13 +679,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>星尘</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>D1 擎骏系列</x:v>
+        <x:v>Astribot S1</x:v>
       </x:c>
       <x:c r="D8" s="16" t="n">
-        <x:v>3.8</x:v>
+        <x:v>3.95</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
         <x:v>通过待实测</x:v>
@@ -694,7 +694,7 @@
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G8" s="15" t="str">
-        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
+        <x:v>论文确认全向底盘；量产配置、接口和工业认证资料不足</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
@@ -702,22 +702,22 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>Boston Dynamics</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Unitree G1-D 旗舰版</x:v>
+        <x:v>Atlas</x:v>
       </x:c>
       <x:c r="D9" s="16" t="n">
-        <x:v>2.3</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str">
-        <x:v>不进入布线 POC</x:v>
+        <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G9" s="15" t="str">
-        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
+        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -725,22 +725,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>Figure AI</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>JUNO2-SD 龙骏系列</x:v>
+        <x:v>Figure 03</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
-        <x:v>2.15</x:v>
+        <x:v>3.8000000000000003</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
-        <x:v>不进入布线 POC</x:v>
+        <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
+        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -748,22 +748,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>Unitree G1-D 通用版</x:v>
+        <x:v>D1 擎骏系列</x:v>
       </x:c>
       <x:c r="D11" s="16" t="n">
-        <x:v>2.05</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
-        <x:v>不进入布线 POC</x:v>
+        <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>官方参数未提供主动移动底盘</x:v>
+        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -771,22 +771,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>它石智航</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>JUNO1-P 智骏系列</x:v>
+        <x:v>TARS A1</x:v>
       </x:c>
       <x:c r="D12" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>3.6500000000000004</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
-        <x:v>不进入布线 POC</x:v>
+        <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G12" s="15" t="str">
-        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
+        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -794,42 +794,203 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="D13" s="16" t="n">
+        <x:v>3.3499999999999996</x:v>
+      </x:c>
+      <x:c r="E13" s="15" t="str">
+        <x:v>待实测</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="str">
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="G13" s="15" t="str">
+        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="32" customHeight="1">
+      <x:c r="A14" s="15" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="D14" s="16" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="str">
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="str">
+        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="32" customHeight="1">
+      <x:c r="A15" s="15" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="str">
+        <x:v>Tesla</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="str">
+        <x:v>Optimus</x:v>
+      </x:c>
+      <x:c r="D15" s="16" t="n">
+        <x:v>2.8000000000000003</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="str">
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="str">
+        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="32" customHeight="1">
+      <x:c r="A16" s="15" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>宇树</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="str">
+        <x:v>Unitree G1-D 旗舰版</x:v>
+      </x:c>
+      <x:c r="D16" s="16" t="n">
+        <x:v>2.3</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="str">
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="F16" s="15" t="str">
+        <x:v>不进入布线 POC</x:v>
+      </x:c>
+      <x:c r="G16" s="15" t="str">
+        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="32" customHeight="1">
+      <x:c r="A17" s="15" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="str">
         <x:v>智动力</x:v>
       </x:c>
-      <x:c r="C13" s="15" t="str">
+      <x:c r="C17" s="15" t="str">
+        <x:v>JUNO2-SD 龙骏系列</x:v>
+      </x:c>
+      <x:c r="D17" s="16" t="n">
+        <x:v>2.15</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="str">
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="str">
+        <x:v>不进入布线 POC</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="str">
+        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
+      <x:c r="A18" s="15" t="n">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="str">
+        <x:v>宇树</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="str">
+        <x:v>Unitree G1-D 通用版</x:v>
+      </x:c>
+      <x:c r="D18" s="16" t="n">
+        <x:v>2.05</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="str">
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="str">
+        <x:v>不进入布线 POC</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="str">
+        <x:v>官方参数未提供主动移动底盘</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="32" customHeight="1">
+      <x:c r="A19" s="15" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="str">
+        <x:v>智动力</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="str">
+        <x:v>JUNO1-P 智骏系列</x:v>
+      </x:c>
+      <x:c r="D19" s="16" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="str">
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="str">
+        <x:v>不进入布线 POC</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="str">
+        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="32" customHeight="1">
+      <x:c r="A20" s="15" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="str">
+        <x:v>智动力</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="str">
         <x:v>L1 灵骏系列</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="n">
+      <x:c r="D20" s="16" t="n">
         <x:v>1.85</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E20" s="15" t="str">
         <x:v>不通过</x:v>
       </x:c>
-      <x:c r="F13" s="15" t="str">
+      <x:c r="F20" s="15" t="str">
         <x:v>不进入布线 POC</x:v>
       </x:c>
-      <x:c r="G13" s="15" t="str">
+      <x:c r="G20" s="15" t="str">
         <x:v>差速底盘且负载、臂展和躯干能力较弱</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="32" customHeight="1">
-      <x:c r="A15" s="19" t="str">
-        <x:v>说明：综合分不能越过硬门槛。星尘 S1 和智动力 D1 的全向能力仍需实机确认；D1 体积、重量与工程代价较高。</x:v>
-      </x:c>
-      <x:c r="B15" s="19"/>
-      <x:c r="C15" s="19"/>
-      <x:c r="D15" s="19"/>
-      <x:c r="E15" s="19"/>
-      <x:c r="F15" s="19"/>
-      <x:c r="G15" s="19"/>
+    <x:row r="22" ht="32" customHeight="1">
+      <x:c r="A22" s="19" t="str">
+        <x:v>说明：综合分不能越过横移硬门槛和供货资格。双足侧步不等同工业蟹行；Atlas、Figure、Optimus 的采购与SDK开放性需单独判断。</x:v>
+      </x:c>
+      <x:c r="B22" s="19"/>
+      <x:c r="C22" s="19"/>
+      <x:c r="D22" s="19"/>
+      <x:c r="E22" s="19"/>
+      <x:c r="F22" s="19"/>
+      <x:c r="G22" s="19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A3:G3"/>
-    <x:mergeCell ref="A15:G15"/>
+    <x:mergeCell ref="A22:G22"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D6:D13">
+  <x:conditionalFormatting sqref="D6:D20">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -841,7 +1002,7 @@
       </x:colorScale>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E6:E13">
+  <x:conditionalFormatting sqref="E6:E20">
     <x:cfRule type="cellIs" dxfId="0" priority="2">
       <x:formula>"不通过"</x:formula>
     </x:cfRule>
@@ -1443,11 +1604,312 @@
         <x:v>双臂模块不含标准底盘；集成全向底盘后再评估</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>Boston Dynamics</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
+        <x:v>待实测</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H17" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J17" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K17" s="16" t="n">
+        <x:f>IF(C17&lt;&gt;"是","",SUMPRODUCT(E17:J17,$B$4:$G$4))</x:f>
+        <x:v>3.85</x:v>
+      </x:c>
+      <x:c r="L17" s="15" t="str">
+        <x:f>IF(C17&lt;&gt;"是","不参与移动本体排名",IF(D17="不通过","不进入布线POC",IF(K17&gt;=4.2,"优先POC",IF(K17&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>条件POC</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="str">
+        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="30" customHeight="1">
+      <x:c r="A18" s="15" t="str">
+        <x:v>Figure AI</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="str">
+        <x:v>Figure 03</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
+        <x:v>待实测</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G18" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H18" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I18" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K18" s="16" t="n">
+        <x:f>IF(C18&lt;&gt;"是","",SUMPRODUCT(E18:J18,$B$4:$G$4))</x:f>
+        <x:v>3.8000000000000003</x:v>
+      </x:c>
+      <x:c r="L18" s="15" t="str">
+        <x:f>IF(C18&lt;&gt;"是","不参与移动本体排名",IF(D18="不通过","不进入布线POC",IF(K18&gt;=4.2,"优先POC",IF(K18&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>条件POC</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="str">
+        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="30" customHeight="1">
+      <x:c r="A19" s="15" t="str">
+        <x:v>Tesla</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="str">
+        <x:v>Optimus</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I19" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K19" s="16" t="n">
+        <x:f>IF(C19&lt;&gt;"是","",SUMPRODUCT(E19:J19,$B$4:$G$4))</x:f>
+        <x:v>2.8000000000000003</x:v>
+      </x:c>
+      <x:c r="L19" s="15" t="str">
+        <x:f>IF(C19&lt;&gt;"是","不参与移动本体排名",IF(D19="不通过","不进入布线POC",IF(K19&gt;=4.2,"优先POC",IF(K19&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="str">
+        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
+        <x:v>待实测</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H20" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I20" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J20" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K20" s="16" t="n">
+        <x:f>IF(C20&lt;&gt;"是","",SUMPRODUCT(E20:J20,$B$4:$G$4))</x:f>
+        <x:v>3.3499999999999996</x:v>
+      </x:c>
+      <x:c r="L20" s="15" t="str">
+        <x:f>IF(C20&lt;&gt;"是","不参与移动本体排名",IF(D20="不通过","不进入布线POC",IF(K20&gt;=4.2,"优先POC",IF(K20&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="str">
+        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H21" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I21" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J21" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K21" s="16" t="n">
+        <x:f>IF(C21&lt;&gt;"是","",SUMPRODUCT(E21:J21,$B$4:$G$4))</x:f>
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="L21" s="15" t="str">
+        <x:f>IF(C21&lt;&gt;"是","不参与移动本体排名",IF(D21="不通过","不进入布线POC",IF(K21&gt;=4.2,"优先POC",IF(K21&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>补齐资料后再评估</x:v>
+      </x:c>
+      <x:c r="M21" s="15" t="str">
+        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="15" t="str">
+        <x:v>星海图</x:v>
+      </x:c>
+      <x:c r="B22" s="15" t="str">
+        <x:v>Galaxea R1 Pro 2026</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="str">
+        <x:v>通过</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H22" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J22" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K22" s="16" t="n">
+        <x:f>IF(C22&lt;&gt;"是","",SUMPRODUCT(E22:J22,$B$4:$G$4))</x:f>
+        <x:v>4.1</x:v>
+      </x:c>
+      <x:c r="L22" s="15" t="str">
+        <x:f>IF(C22&lt;&gt;"是","不参与移动本体排名",IF(D22="不通过","不进入布线POC",IF(K22&gt;=4.2,"优先POC",IF(K22&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>条件POC</x:v>
+      </x:c>
+      <x:c r="M22" s="15" t="str">
+        <x:v>三舵轮全向和工作空间契合；重复精度0.5mm且机械臂无制动器是主要风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K23" s="16" t="n">
+        <x:f>IF(C23&lt;&gt;"是","",SUMPRODUCT(E23:J23,$B$4:$G$4))</x:f>
+        <x:v>3.6500000000000004</x:v>
+      </x:c>
+      <x:c r="L23" s="15" t="str">
+        <x:f>IF(C23&lt;&gt;"是","不参与移动本体排名",IF(D23="不通过","不进入布线POC",IF(K23&gt;=4.2,"优先POC",IF(K23&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>条件POC</x:v>
+      </x:c>
+      <x:c r="M23" s="15" t="str">
+        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="K7:K16">
+  <x:conditionalFormatting sqref="K7:K23">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -1459,7 +1921,7 @@
       </x:colorScale>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:D16">
+  <x:conditionalFormatting sqref="D7:D23">
     <x:cfRule type="cellIs" dxfId="2" priority="2">
       <x:formula>"不通过"</x:formula>
     </x:cfRule>
@@ -1468,14 +1930,14 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation operator="between" showErrorMessage="1" errorTitle="评分超范围" error="请输入 0 到 5 的整数。" sqref="E7:J16">
+    <x:dataValidation operator="between" showErrorMessage="1" errorTitle="评分超范围" error="请输入 0 到 5 的整数。" sqref="E7:J23">
       <x:formula1>0</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6200ac30e8d941f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R728af8975e604a66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2578,13 +3040,552 @@
         <x:v>单臂参数；不含标准移动底盘，不参加移动本体排名</x:v>
       </x:c>
     </x:row>
+    <x:row r="14" ht="34" customHeight="1">
+      <x:c r="A14" s="15" t="str">
+        <x:v>boston_atlas_2026</x:v>
+      </x:c>
+      <x:c r="B14" s="15" t="str">
+        <x:v>Boston Dynamics</x:v>
+      </x:c>
+      <x:c r="C14" s="15" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+      <x:c r="D14" s="15" t="str">
+        <x:v>全尺寸双足工业人形</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="str">
+        <x:v>早期客户导入</x:v>
+      </x:c>
+      <x:c r="F14" s="15" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G14" s="15"/>
+      <x:c r="H14" s="15"/>
+      <x:c r="I14" s="15"/>
+      <x:c r="J14" s="15"/>
+      <x:c r="K14" s="15" t="str">
+        <x:v>双足全电驱</x:v>
+      </x:c>
+      <x:c r="L14" s="15" t="str">
+        <x:v>步态可侧移；连续工业横移待验证</x:v>
+      </x:c>
+      <x:c r="M14" s="15"/>
+      <x:c r="N14" s="15" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="O14" s="15" t="n">
+        <x:v>1900</x:v>
+      </x:c>
+      <x:c r="P14" s="15"/>
+      <x:c r="Q14" s="15"/>
+      <x:c r="R14" s="15" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="S14" s="15"/>
+      <x:c r="T14" s="15"/>
+      <x:c r="U14" s="15"/>
+      <x:c r="V14" s="15"/>
+      <x:c r="W14" s="15" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="X14" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="Y14" s="15" t="str"/>
+      <x:c r="Z14" s="15"/>
+      <x:c r="AA14" s="15"/>
+      <x:c r="AB14" s="15" t="str">
+        <x:v>触觉感知；全身力控量化指标未公开</x:v>
+      </x:c>
+      <x:c r="AC14" s="15"/>
+      <x:c r="AD14" s="15"/>
+      <x:c r="AE14" s="15" t="str"/>
+      <x:c r="AF14" s="15" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AG14" s="15" t="str">
+        <x:v>IP67</x:v>
+      </x:c>
+      <x:c r="AH14" s="15" t="str">
+        <x:v>工业任务手/夹具未披露</x:v>
+      </x:c>
+      <x:c r="AI14" s="15" t="str">
+        <x:v>Orbit可对接MES/WMS；支持条码和工作流集成</x:v>
+      </x:c>
+      <x:c r="AJ14" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="AK14" s="15" t="str">
+        <x:v>全身Reach 2.3m；持续负载30kg/瞬时50kg；自动换电；仅面向选择性早期客户</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="34" customHeight="1">
+      <x:c r="A15" s="15" t="str">
+        <x:v>figure_03</x:v>
+      </x:c>
+      <x:c r="B15" s="15" t="str">
+        <x:v>Figure AI</x:v>
+      </x:c>
+      <x:c r="C15" s="15" t="str">
+        <x:v>Figure 03</x:v>
+      </x:c>
+      <x:c r="D15" s="15" t="str">
+        <x:v>全尺寸双足通用人形</x:v>
+      </x:c>
+      <x:c r="E15" s="15" t="str">
+        <x:v>量产爬坡/客户验证</x:v>
+      </x:c>
+      <x:c r="F15" s="15"/>
+      <x:c r="G15" s="15"/>
+      <x:c r="H15" s="15"/>
+      <x:c r="I15" s="15"/>
+      <x:c r="J15" s="15"/>
+      <x:c r="K15" s="15" t="str">
+        <x:v>双足电驱</x:v>
+      </x:c>
+      <x:c r="L15" s="15" t="str">
+        <x:v>步态可侧移；工业横移精度未披露</x:v>
+      </x:c>
+      <x:c r="M15" s="15" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="N15" s="15" t="n">
+        <x:v>1727</x:v>
+      </x:c>
+      <x:c r="O15" s="15" t="n">
+        <x:v>1727</x:v>
+      </x:c>
+      <x:c r="P15" s="15"/>
+      <x:c r="Q15" s="15"/>
+      <x:c r="R15" s="15" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="S15" s="15"/>
+      <x:c r="T15" s="15"/>
+      <x:c r="U15" s="15"/>
+      <x:c r="V15" s="15"/>
+      <x:c r="W15" s="15" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="X15" s="15"/>
+      <x:c r="Y15" s="15" t="str"/>
+      <x:c r="Z15" s="15"/>
+      <x:c r="AA15" s="15"/>
+      <x:c r="AB15" s="15" t="str">
+        <x:v>柔顺触觉手；指尖可检测约3g压力</x:v>
+      </x:c>
+      <x:c r="AC15" s="15"/>
+      <x:c r="AD15" s="15"/>
+      <x:c r="AE15" s="15" t="str"/>
+      <x:c r="AF15" s="15" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="AG15" s="15" t="str"/>
+      <x:c r="AH15" s="15" t="str">
+        <x:v>自研触觉灵巧手</x:v>
+      </x:c>
+      <x:c r="AI15" s="15" t="str">
+        <x:v>Helix专有系统；10Gbps毫米波数据卸载；无公开工业SDK</x:v>
+      </x:c>
+      <x:c r="AJ15" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="AK15" s="15" t="str">
+        <x:v>2.3kWh电池；2kW无线充电；UN38.3；BMW生产验证；接口和采购方式不公开</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="A16" s="15" t="str">
+        <x:v>tesla_optimus</x:v>
+      </x:c>
+      <x:c r="B16" s="15" t="str">
+        <x:v>Tesla</x:v>
+      </x:c>
+      <x:c r="C16" s="15" t="str">
+        <x:v>Optimus</x:v>
+      </x:c>
+      <x:c r="D16" s="15" t="str">
+        <x:v>全尺寸双足通用人形</x:v>
+      </x:c>
+      <x:c r="E16" s="15" t="str">
+        <x:v>产线建设/内部验证</x:v>
+      </x:c>
+      <x:c r="F16" s="15"/>
+      <x:c r="G16" s="15"/>
+      <x:c r="H16" s="15"/>
+      <x:c r="I16" s="15"/>
+      <x:c r="J16" s="15"/>
+      <x:c r="K16" s="15" t="str">
+        <x:v>双足电驱</x:v>
+      </x:c>
+      <x:c r="L16" s="15" t="str">
+        <x:v>工业横移能力与精度未披露</x:v>
+      </x:c>
+      <x:c r="M16" s="15"/>
+      <x:c r="N16" s="15"/>
+      <x:c r="O16" s="15"/>
+      <x:c r="P16" s="15"/>
+      <x:c r="Q16" s="15"/>
+      <x:c r="R16" s="15"/>
+      <x:c r="S16" s="15"/>
+      <x:c r="T16" s="15"/>
+      <x:c r="U16" s="15"/>
+      <x:c r="V16" s="15"/>
+      <x:c r="W16" s="15"/>
+      <x:c r="X16" s="15"/>
+      <x:c r="Y16" s="15" t="str"/>
+      <x:c r="Z16" s="15"/>
+      <x:c r="AA16" s="15"/>
+      <x:c r="AB16" s="15" t="str">
+        <x:v>未公开</x:v>
+      </x:c>
+      <x:c r="AC16" s="15"/>
+      <x:c r="AD16" s="15"/>
+      <x:c r="AE16" s="15" t="str"/>
+      <x:c r="AF16" s="15" t="str"/>
+      <x:c r="AG16" s="15" t="str"/>
+      <x:c r="AH16" s="15" t="str">
+        <x:v>灵巧手</x:v>
+      </x:c>
+      <x:c r="AI16" s="15" t="str">
+        <x:v>专有软硬件栈；未公开第三方SDK</x:v>
+      </x:c>
+      <x:c r="AJ16" s="15" t="str">
+        <x:v>官方网站+投资者披露</x:v>
+      </x:c>
+      <x:c r="AK16" s="15" t="str">
+        <x:v>官方当前页面未披露身高负载续航自由度等可采购规格；不具备供应商选型基线</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="34" customHeight="1">
+      <x:c r="A17" s="15" t="str">
+        <x:v>limx_oli_edu</x:v>
+      </x:c>
+      <x:c r="B17" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C17" s="15" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="D17" s="15" t="str">
+        <x:v>全尺寸双足开发平台</x:v>
+      </x:c>
+      <x:c r="E17" s="15" t="str">
+        <x:v>可购/持续迭代</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="n">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H17" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J17" s="15"/>
+      <x:c r="K17" s="15" t="str">
+        <x:v>双足步行</x:v>
+      </x:c>
+      <x:c r="L17" s="15" t="str">
+        <x:v>步态可侧移；连续贴线横移待实测</x:v>
+      </x:c>
+      <x:c r="M17" s="15" t="n">
+        <x:v>1.389</x:v>
+      </x:c>
+      <x:c r="N17" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="O17" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="P17" s="15" t="n">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="Q17" s="15"/>
+      <x:c r="R17" s="15" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="S17" s="15" t="n">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="T17" s="15"/>
+      <x:c r="U17" s="15"/>
+      <x:c r="V17" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="W17" s="15"/>
+      <x:c r="X17" s="15"/>
+      <x:c r="Y17" s="15" t="str"/>
+      <x:c r="Z17" s="15"/>
+      <x:c r="AA17" s="15"/>
+      <x:c r="AB17" s="15" t="str">
+        <x:v>未公开</x:v>
+      </x:c>
+      <x:c r="AC17" s="15"/>
+      <x:c r="AD17" s="15"/>
+      <x:c r="AE17" s="15" t="str">
+        <x:v>RK3588运控+Orin NX 157TOPS感知</x:v>
+      </x:c>
+      <x:c r="AF17" s="15" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG17" s="15" t="str"/>
+      <x:c r="AH17" s="15" t="str">
+        <x:v>二指夹爪或五指灵巧手</x:v>
+      </x:c>
+      <x:c r="AI17" s="15" t="str">
+        <x:v>WiFi6；蓝牙；USB3；千兆网；Type-C；遥控/传感/底层和上层运动API</x:v>
+      </x:c>
+      <x:c r="AJ17" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="AK17" s="15" t="str">
+        <x:v>约2h续航；9500mAh抽屉式电池；最大负载3kg；开放度较好但工业精度和认证未公开</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="34" customHeight="1">
+      <x:c r="A18" s="15" t="str">
+        <x:v>limx_tron2_dualarm</x:v>
+      </x:c>
+      <x:c r="B18" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C18" s="15" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="D18" s="15" t="str">
+        <x:v>多形态双臂移动平台</x:v>
+      </x:c>
+      <x:c r="E18" s="15" t="str">
+        <x:v>可购/持续迭代</x:v>
+      </x:c>
+      <x:c r="F18" s="15"/>
+      <x:c r="G18" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H18" s="15"/>
+      <x:c r="I18" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J18" s="15"/>
+      <x:c r="K18" s="15" t="str">
+        <x:v>双足/双轮足可换形</x:v>
+      </x:c>
+      <x:c r="L18" s="15" t="str">
+        <x:v>官方称四向移动；纯横移机制待确认</x:v>
+      </x:c>
+      <x:c r="M18" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N18" s="15"/>
+      <x:c r="O18" s="15"/>
+      <x:c r="P18" s="15"/>
+      <x:c r="Q18" s="15"/>
+      <x:c r="R18" s="15"/>
+      <x:c r="S18" s="15"/>
+      <x:c r="T18" s="15"/>
+      <x:c r="U18" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="V18" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="W18" s="15"/>
+      <x:c r="X18" s="15"/>
+      <x:c r="Y18" s="15" t="str"/>
+      <x:c r="Z18" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AA18" s="15"/>
+      <x:c r="AB18" s="15" t="str">
+        <x:v>双臂安全边界；力控和力传感量化未公开</x:v>
+      </x:c>
+      <x:c r="AC18" s="15"/>
+      <x:c r="AD18" s="15"/>
+      <x:c r="AE18" s="15" t="str">
+        <x:v>Intel Core Ultra拓展模块</x:v>
+      </x:c>
+      <x:c r="AF18" s="15" t="str"/>
+      <x:c r="AG18" s="15" t="str"/>
+      <x:c r="AH18" s="15" t="str">
+        <x:v>夹爪或灵巧手</x:v>
+      </x:c>
+      <x:c r="AI18" s="15" t="str">
+        <x:v>Python；C++；ROS1/ROS2；以太网；USB3；EtherCAT×2；RS485；多电压供电</x:v>
+      </x:c>
+      <x:c r="AJ18" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="AK18" s="15" t="str">
+        <x:v>双轮足速度3至5m/s；重复定位±0.5mm；遥操延迟100ms；更偏研发和多形态验证</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="34" customHeight="1">
+      <x:c r="A19" s="15" t="str">
+        <x:v>galaxea_r1pro_2026</x:v>
+      </x:c>
+      <x:c r="B19" s="15" t="str">
+        <x:v>星海图</x:v>
+      </x:c>
+      <x:c r="C19" s="15" t="str">
+        <x:v>Galaxea R1 Pro 2026</x:v>
+      </x:c>
+      <x:c r="D19" s="15" t="str">
+        <x:v>轮式双臂仿人形本体</x:v>
+      </x:c>
+      <x:c r="E19" s="15" t="str">
+        <x:v>现货/科研与行业落地</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I19" s="15"/>
+      <x:c r="J19" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K19" s="15" t="str">
+        <x:v>三舵轮360度全向底盘</x:v>
+      </x:c>
+      <x:c r="L19" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M19" s="15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N19" s="15" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="O19" s="15" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="P19" s="15" t="n">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="Q19" s="15" t="n">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="R19" s="15" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="S19" s="15" t="n">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="T19" s="15"/>
+      <x:c r="U19" s="15" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="V19" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="W19" s="15"/>
+      <x:c r="X19" s="15"/>
+      <x:c r="Y19" s="15" t="str"/>
+      <x:c r="Z19" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="AA19" s="15"/>
+      <x:c r="AB19" s="15" t="str">
+        <x:v>七轴仿人力控机械臂；力传感为选配</x:v>
+      </x:c>
+      <x:c r="AC19" s="15"/>
+      <x:c r="AD19" s="15"/>
+      <x:c r="AE19" s="15" t="str">
+        <x:v>Jetson AGX Orin 32GB 200TOPS</x:v>
+      </x:c>
+      <x:c r="AF19" s="15" t="str"/>
+      <x:c r="AG19" s="15" t="str"/>
+      <x:c r="AH19" s="15" t="str">
+        <x:v>电动平行夹爪</x:v>
+      </x:c>
+      <x:c r="AI19" s="15" t="str">
+        <x:v>USB3；HDMI；千兆以太网；WiFi6；蓝牙</x:v>
+      </x:c>
+      <x:c r="AJ19" s="15" t="str">
+        <x:v>官方产品页+开发文档</x:v>
+      </x:c>
+      <x:c r="AK19" s="15" t="str">
+        <x:v>垂直工作空间0至2m；带夹爪水平半径861mm；夹持力额定150N峰值350N；A2机械臂无制动器需重点评估断电下坠</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="34" customHeight="1">
+      <x:c r="A20" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="B20" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="C20" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="D20" s="15" t="str">
+        <x:v>轮式工业具身本体</x:v>
+      </x:c>
+      <x:c r="E20" s="15" t="str">
+        <x:v>产线验证/规模部署计划</x:v>
+      </x:c>
+      <x:c r="F20" s="15"/>
+      <x:c r="G20" s="15"/>
+      <x:c r="H20" s="15"/>
+      <x:c r="I20" s="15"/>
+      <x:c r="J20" s="15"/>
+      <x:c r="K20" s="15" t="str">
+        <x:v>轮式底盘（轮系未公开）</x:v>
+      </x:c>
+      <x:c r="L20" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="M20" s="15"/>
+      <x:c r="N20" s="15"/>
+      <x:c r="O20" s="15"/>
+      <x:c r="P20" s="15"/>
+      <x:c r="Q20" s="15"/>
+      <x:c r="R20" s="15"/>
+      <x:c r="S20" s="15"/>
+      <x:c r="T20" s="15"/>
+      <x:c r="U20" s="15"/>
+      <x:c r="V20" s="15"/>
+      <x:c r="W20" s="15"/>
+      <x:c r="X20" s="15"/>
+      <x:c r="Y20" s="15" t="str"/>
+      <x:c r="Z20" s="15"/>
+      <x:c r="AA20" s="15"/>
+      <x:c r="AB20" s="15" t="str">
+        <x:v>线束亚毫米装配有公开任务证据；本体力控指标未公开</x:v>
+      </x:c>
+      <x:c r="AC20" s="15"/>
+      <x:c r="AD20" s="15"/>
+      <x:c r="AE20" s="15" t="str"/>
+      <x:c r="AF20" s="15" t="str"/>
+      <x:c r="AG20" s="15" t="str"/>
+      <x:c r="AH20" s="15" t="str">
+        <x:v>定制夹爪或DexHand</x:v>
+      </x:c>
+      <x:c r="AI20" s="15" t="str">
+        <x:v>SDK与末端电气接口未公开</x:v>
+      </x:c>
+      <x:c r="AJ20" s="15" t="str">
+        <x:v>客户/政府/吉尼斯+内部沟通</x:v>
+      </x:c>
+      <x:c r="AK20" s="15" t="str">
+        <x:v>公开完成105次每小时亚毫米线束装配纪录；内部沟通显示规模部署验收仍有差距且前期工装耗材投入高</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:AK1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3e26bbeeb0477e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab0e2da811f447fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3197,11 +4198,403 @@
       <x:c r="I21" s="15" t="str"/>
       <x:c r="J21" s="15" t="str"/>
     </x:row>
+    <x:row r="22" ht="38" customHeight="1">
+      <x:c r="A22" s="15" t="str">
+        <x:v>Q019</x:v>
+      </x:c>
+      <x:c r="B22" s="15" t="str">
+        <x:v>Boston Dynamics</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="str">
+        <x:v>底盘/步态</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="str">
+        <x:v>能否保持上身朝向工装完成连续2米横移并给出轨迹与末端误差</x:v>
+      </x:c>
+      <x:c r="G22" s="15" t="str">
+        <x:v>官网仅说明动态双足能力</x:v>
+      </x:c>
+      <x:c r="H22" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str"/>
+      <x:c r="J22" s="15" t="str"/>
+    </x:row>
+    <x:row r="23" ht="38" customHeight="1">
+      <x:c r="A23" s="15" t="str">
+        <x:v>Q020</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="str">
+        <x:v>Boston Dynamics</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="str">
+        <x:v>采购与集成</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="str">
+        <x:v>中国工厂能否采购并开放任务开发、末端工具和MES接口</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="str">
+        <x:v>当前仅面向选择性早期客户且Orbit为专有平台</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="str"/>
+      <x:c r="J23" s="15" t="str"/>
+    </x:row>
+    <x:row r="24" ht="38" customHeight="1">
+      <x:c r="A24" s="15" t="str">
+        <x:v>Q021</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="str">
+        <x:v>Figure AI</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="str">
+        <x:v>Figure 03</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="str">
+        <x:v>步态与精度</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="str">
+        <x:v>侧移后双手TCP重定位误差、停稳时间和连续运行节拍是多少</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="str">
+        <x:v>官网未披露工业步态精度</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="str"/>
+      <x:c r="J24" s="15" t="str"/>
+    </x:row>
+    <x:row r="25" ht="38" customHeight="1">
+      <x:c r="A25" s="15" t="str">
+        <x:v>Q022</x:v>
+      </x:c>
+      <x:c r="B25" s="15" t="str">
+        <x:v>Figure AI</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="str">
+        <x:v>Figure 03</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="str">
+        <x:v>接口</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="str">
+        <x:v>是否提供第三方SDK、末端机械接口、电气接口和离线部署能力</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="str">
+        <x:v>公开资料仅描述Helix专有系统</x:v>
+      </x:c>
+      <x:c r="H25" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I25" s="15" t="str"/>
+      <x:c r="J25" s="15" t="str"/>
+    </x:row>
+    <x:row r="26" ht="38" customHeight="1">
+      <x:c r="A26" s="15" t="str">
+        <x:v>Q023</x:v>
+      </x:c>
+      <x:c r="B26" s="15" t="str">
+        <x:v>Tesla</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="str">
+        <x:v>Optimus</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="str">
+        <x:v>可采购性</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="str">
+        <x:v>是否提供外部销售、工程规格书、SDK和售后服务边界</x:v>
+      </x:c>
+      <x:c r="G26" s="15" t="str">
+        <x:v>官方尚未给出采购规格</x:v>
+      </x:c>
+      <x:c r="H26" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I26" s="15" t="str"/>
+      <x:c r="J26" s="15" t="str"/>
+    </x:row>
+    <x:row r="27" ht="38" customHeight="1">
+      <x:c r="A27" s="15" t="str">
+        <x:v>Q024</x:v>
+      </x:c>
+      <x:c r="B27" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="str">
+        <x:v>横移POC</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="str">
+        <x:v>能否在保持胸部朝向的情况下完成连续贴线横移并量化足端稳定和末端误差</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="str">
+        <x:v>官网只披露行走速度</x:v>
+      </x:c>
+      <x:c r="H27" s="15" t="str">
+        <x:v>待POC</x:v>
+      </x:c>
+      <x:c r="I27" s="15" t="str"/>
+      <x:c r="J27" s="15" t="str"/>
+    </x:row>
+    <x:row r="28" ht="38" customHeight="1">
+      <x:c r="A28" s="15" t="str">
+        <x:v>Q025</x:v>
+      </x:c>
+      <x:c r="B28" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="str">
+        <x:v>工业可靠性</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="str">
+        <x:v>重复定位精度、IP等级、MTBF、连续运行和电池循环寿命是多少</x:v>
+      </x:c>
+      <x:c r="G28" s="15" t="str">
+        <x:v>公开资料未披露</x:v>
+      </x:c>
+      <x:c r="H28" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I28" s="15" t="str"/>
+      <x:c r="J28" s="15" t="str"/>
+    </x:row>
+    <x:row r="29" ht="38" customHeight="1">
+      <x:c r="A29" s="15" t="str">
+        <x:v>Q026</x:v>
+      </x:c>
+      <x:c r="B29" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="str">
+        <x:v>底盘</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str">
+        <x:v>官方四向移动是否包含无需转向的纯横移；双轮足转向结构是什么</x:v>
+      </x:c>
+      <x:c r="G29" s="15" t="str">
+        <x:v>官网表述不足以判断蟹行能力</x:v>
+      </x:c>
+      <x:c r="H29" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str"/>
+      <x:c r="J29" s="15" t="str"/>
+    </x:row>
+    <x:row r="30" ht="38" customHeight="1">
+      <x:c r="A30" s="15" t="str">
+        <x:v>Q027</x:v>
+      </x:c>
+      <x:c r="B30" s="15" t="str">
+        <x:v>逐际动力</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="str">
+        <x:v>P1</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="str">
+        <x:v>力控</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="str">
+        <x:v>双臂是否具有关节力矩或末端六维力传感；控制频率和量化精度是多少</x:v>
+      </x:c>
+      <x:c r="G30" s="15" t="str">
+        <x:v>只公开安全边界未公开力控参数</x:v>
+      </x:c>
+      <x:c r="H30" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I30" s="15" t="str"/>
+      <x:c r="J30" s="15" t="str"/>
+    </x:row>
+    <x:row r="31" ht="38" customHeight="1">
+      <x:c r="A31" s="15" t="str">
+        <x:v>Q028</x:v>
+      </x:c>
+      <x:c r="B31" s="15" t="str">
+        <x:v>星海图</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="str">
+        <x:v>R1 Pro 2026</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="str">
+        <x:v>断电安全</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="str">
+        <x:v>A2机械臂无制动器时如何防止断电下坠、夹具碰撞和线束损伤</x:v>
+      </x:c>
+      <x:c r="G31" s="15" t="str">
+        <x:v>官方开发文档明确无制动器</x:v>
+      </x:c>
+      <x:c r="H31" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I31" s="15" t="str"/>
+      <x:c r="J31" s="15" t="str"/>
+    </x:row>
+    <x:row r="32" ht="38" customHeight="1">
+      <x:c r="A32" s="15" t="str">
+        <x:v>Q029</x:v>
+      </x:c>
+      <x:c r="B32" s="15" t="str">
+        <x:v>星海图</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="str">
+        <x:v>R1 Pro 2026</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="str">
+        <x:v>整链路精度</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="str">
+        <x:v>横移停稳后视觉重定位与双手TCP误差是多少；能否稳定插接端子</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="str">
+        <x:v>机械臂重复定位精度为0.5mm</x:v>
+      </x:c>
+      <x:c r="H32" s="15" t="str">
+        <x:v>待POC</x:v>
+      </x:c>
+      <x:c r="I32" s="15" t="str"/>
+      <x:c r="J32" s="15" t="str"/>
+    </x:row>
+    <x:row r="33" ht="38" customHeight="1">
+      <x:c r="A33" s="15" t="str">
+        <x:v>Q030</x:v>
+      </x:c>
+      <x:c r="B33" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="str">
+        <x:v>本体参数</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="str">
+        <x:v>底盘轮型、是否支持纯横移、臂展、负载、自由度、续航和IP等级是什么</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="str">
+        <x:v>公开任务成果多但本体规格缺失</x:v>
+      </x:c>
+      <x:c r="H33" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I33" s="15" t="str"/>
+      <x:c r="J33" s="15" t="str"/>
+    </x:row>
+    <x:row r="34" ht="38" customHeight="1">
+      <x:c r="A34" s="15" t="str">
+        <x:v>Q031</x:v>
+      </x:c>
+      <x:c r="B34" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="str">
+        <x:v>规模验收</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="str">
+        <x:v>已部署机器人按工序的节拍、一次成功率、OEE、损伤率、人工介入率和最终验收比例是多少</x:v>
+      </x:c>
+      <x:c r="G34" s="15" t="str">
+        <x:v>内部沟通反馈百台部署要求尚未达标</x:v>
+      </x:c>
+      <x:c r="H34" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I34" s="15" t="str"/>
+      <x:c r="J34" s="15" t="str"/>
+    </x:row>
+    <x:row r="35" ht="38" customHeight="1">
+      <x:c r="A35" s="15" t="str">
+        <x:v>Q032</x:v>
+      </x:c>
+      <x:c r="B35" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="str">
+        <x:v>项目经济性</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="str">
+        <x:v>按2.5年回本目标给出本体、场地、工装板、接插件耗材、夹爪迭代、MES集成和维护全成本</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="str">
+        <x:v>前期场地工装和端子损耗可能显著</x:v>
+      </x:c>
+      <x:c r="H35" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I35" s="15" t="str"/>
+      <x:c r="J35" s="15" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D4:D21">
+  <x:conditionalFormatting sqref="D4:D35">
     <x:cfRule type="cellIs" dxfId="4" priority="1">
       <x:formula>"P0"</x:formula>
     </x:cfRule>
@@ -3210,13 +4603,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H4:H21">
+    <x:dataValidation type="list" sqref="H4:H35">
       <x:formula1>"待供应商回复,待POC,待IT联调,进行中,已关闭,不适用"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ac865f237304d88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01a047f617b34a1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3817,13 +5210,403 @@
         <x:v>原目录索引的归档副本</x:v>
       </x:c>
     </x:row>
+    <x:row r="22" ht="42" customHeight="1">
+      <x:c r="A22" s="15" t="str">
+        <x:v>src_boston_atlas</x:v>
+      </x:c>
+      <x:c r="B22" s="15" t="str">
+        <x:v>boston_atlas_2026</x:v>
+      </x:c>
+      <x:c r="C22" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D22" s="15" t="str">
+        <x:v>Atlas产品与规格</x:v>
+      </x:c>
+      <x:c r="E22" s="15" t="str">
+        <x:v>https://bostondynamics.com/products/atlas/</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="str"/>
+      <x:c r="G22" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H22" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I22" s="15" t="str">
+        <x:v>披露56自由度、负载、续航、IP67、工作范围和Orbit集成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="15" t="str">
+        <x:v>src_figure03_product</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="str">
+        <x:v>figure_03</x:v>
+      </x:c>
+      <x:c r="C23" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D23" s="15" t="str">
+        <x:v>Figure 03产品页</x:v>
+      </x:c>
+      <x:c r="E23" s="15" t="str">
+        <x:v>https://www.figure.ai/figure</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="str"/>
+      <x:c r="G23" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I23" s="15" t="str">
+        <x:v>披露身高、重量、负载、速度和续航</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="15" t="str">
+        <x:v>src_figure03_intro</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="str">
+        <x:v>figure_03</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="str">
+        <x:v>官方技术文章</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
+        <x:v>Introducing Figure 03</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="str">
+        <x:v>https://www.figure.ai/news/introducing-figure-03</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="str">
+        <x:v>2025-10-09</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="str">
+        <x:v>披露触觉、感知、充电、电池安全和量产设计</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="15" t="str">
+        <x:v>src_figure03_bmw</x:v>
+      </x:c>
+      <x:c r="B25" s="15" t="str">
+        <x:v>figure_03</x:v>
+      </x:c>
+      <x:c r="C25" s="15" t="str">
+        <x:v>官方客户进展</x:v>
+      </x:c>
+      <x:c r="D25" s="15" t="str">
+        <x:v>F.03 Arrives at BMW</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="str">
+        <x:v>https://www.figure.ai/news/f-03-at-bmw</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="G25" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H25" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I25" s="15" t="str">
+        <x:v>披露BMW工厂物流验证和全身操作</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="15" t="str">
+        <x:v>src_tesla_ai</x:v>
+      </x:c>
+      <x:c r="B26" s="15" t="str">
+        <x:v>tesla_optimus</x:v>
+      </x:c>
+      <x:c r="C26" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D26" s="15" t="str">
+        <x:v>Tesla AI and Robotics</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="str">
+        <x:v>https://www.tesla.com/AI</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="str"/>
+      <x:c r="G26" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H26" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I26" s="15" t="str">
+        <x:v>仅说明双足通用自主机器人目标；未给工程规格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="42" customHeight="1">
+      <x:c r="A27" s="15" t="str">
+        <x:v>src_tesla_2026q2</x:v>
+      </x:c>
+      <x:c r="B27" s="15" t="str">
+        <x:v>tesla_optimus</x:v>
+      </x:c>
+      <x:c r="C27" s="15" t="str">
+        <x:v>官方投资者文件</x:v>
+      </x:c>
+      <x:c r="D27" s="15" t="str">
+        <x:v>Tesla 2026 Q2 Update</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="str">
+        <x:v>https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
+      <x:c r="G27" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H27" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I27" s="15" t="str">
+        <x:v>披露Optimus产线建设与训练数据用途；未给本体规格</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="42" customHeight="1">
+      <x:c r="A28" s="15" t="str">
+        <x:v>src_limx_oli</x:v>
+      </x:c>
+      <x:c r="B28" s="15" t="str">
+        <x:v>limx_oli_edu</x:v>
+      </x:c>
+      <x:c r="C28" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D28" s="15" t="str">
+        <x:v>LimX Oli产品参数</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="str">
+        <x:v>https://www.limxdynamics.com/zh/products/oli/spec</x:v>
+      </x:c>
+      <x:c r="F28" s="15" t="str"/>
+      <x:c r="G28" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H28" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I28" s="15" t="str">
+        <x:v>披露自由度、尺寸、负载、续航、算力和开发接口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="42" customHeight="1">
+      <x:c r="A29" s="15" t="str">
+        <x:v>src_limx_tron2</x:v>
+      </x:c>
+      <x:c r="B29" s="15" t="str">
+        <x:v>limx_tron2_dualarm</x:v>
+      </x:c>
+      <x:c r="C29" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D29" s="15" t="str">
+        <x:v>TRON 2产品参数</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="str">
+        <x:v>https://www.limxdynamics.com/zh/products/tron2/spec</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str"/>
+      <x:c r="G29" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H29" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I29" s="15" t="str">
+        <x:v>披露双臂负载精度、多形态移动、接口和开发工具</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="42" customHeight="1">
+      <x:c r="A30" s="15" t="str">
+        <x:v>src_galaxea_r1pro_product</x:v>
+      </x:c>
+      <x:c r="B30" s="15" t="str">
+        <x:v>galaxea_r1pro_2026</x:v>
+      </x:c>
+      <x:c r="C30" s="15" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="D30" s="15" t="str">
+        <x:v>R1 Pro产品参数</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="str">
+        <x:v>https://galaxea-ai.com/cn/products/R1-Pro</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="str"/>
+      <x:c r="G30" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H30" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I30" s="15" t="str">
+        <x:v>披露三舵轮全向底盘、双臂负载、工作空间和算力</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="42" customHeight="1">
+      <x:c r="A31" s="15" t="str">
+        <x:v>src_galaxea_r1pro_docs</x:v>
+      </x:c>
+      <x:c r="B31" s="15" t="str">
+        <x:v>galaxea_r1pro_2026</x:v>
+      </x:c>
+      <x:c r="C31" s="15" t="str">
+        <x:v>官方开发文档</x:v>
+      </x:c>
+      <x:c r="D31" s="15" t="str">
+        <x:v>R1 Pro 2026硬件说明</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="str">
+        <x:v>https://docs.galaxea-dynamics.com/R1Pro/docs/2026/</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="str"/>
+      <x:c r="G31" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H31" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I31" s="15" t="str">
+        <x:v>披露重量、电池、夹爪、接口和机械臂无制动器风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="42" customHeight="1">
+      <x:c r="A32" s="15" t="str">
+        <x:v>src_tars_tianhai</x:v>
+      </x:c>
+      <x:c r="B32" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C32" s="15" t="str">
+        <x:v>客户官方新闻</x:v>
+      </x:c>
+      <x:c r="D32" s="15" t="str">
+        <x:v>天海电子与它石智航战略合作</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="str">
+        <x:v>https://www.thb.com.cn/content/details_17_319668.html</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="str">
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G32" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H32" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I32" s="15" t="str">
+        <x:v>确认汽车线束联合产线与近半年联合攻坚</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="42" customHeight="1">
+      <x:c r="A33" s="15" t="str">
+        <x:v>src_tars_shanghai</x:v>
+      </x:c>
+      <x:c r="B33" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C33" s="15" t="str">
+        <x:v>政府官方信息</x:v>
+      </x:c>
+      <x:c r="D33" s="15" t="str">
+        <x:v>它石智航产业化闭环</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="str">
+        <x:v>https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="G33" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H33" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I33" s="15" t="str">
+        <x:v>披露安波福百台计划、33类场景、46工位和DexHand</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="42" customHeight="1">
+      <x:c r="A34" s="15" t="str">
+        <x:v>src_tars_guinness</x:v>
+      </x:c>
+      <x:c r="B34" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C34" s="15" t="str">
+        <x:v>独立纪录机构</x:v>
+      </x:c>
+      <x:c r="D34" s="15" t="str">
+        <x:v>Most sub-millimeter wire harness assembled by a robot in one hour</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="str">
+        <x:v>https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="str"/>
+      <x:c r="G34" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H34" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I34" s="15" t="str">
+        <x:v>确认一小时105次亚毫米线束装配纪录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="42" customHeight="1">
+      <x:c r="A35" s="15" t="str">
+        <x:v>src_tars_internal</x:v>
+      </x:c>
+      <x:c r="B35" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C35" s="15" t="str">
+        <x:v>内部沟通</x:v>
+      </x:c>
+      <x:c r="D35" s="15" t="str">
+        <x:v>它石线束部署与工程问题纪要</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="str">
+        <x:v>conversation-context:2026-09-15</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="G35" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H35" s="15" t="str">
+        <x:v>待核验</x:v>
+      </x:c>
+      <x:c r="I35" s="15" t="str">
+        <x:v>反馈百台部署尚未达到要求并存在臂展、工装耗材、夹爪和MES依赖问题</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:I1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re134595142734ffa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a5ac16dabe9421a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/机器人本体产品主表.xlsx
+++ b/outputs/机器人本体产品主表.xlsx
@@ -2,11 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="Rc6adbc6eae404cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="2" r:id="Rad89cee4aa3d4cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="3" r:id="R614e916d26b44e97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="4" r:id="R448bd1bface44fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="5" r:id="R5f975c33ac3642b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R3ed96af3fcb64d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="型号图示" sheetId="2" r:id="Ra0efeb1d15634d72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="3" r:id="R309e999abf524a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="4" r:id="Rda6d8609b6234339"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="5" r:id="Rc18e434436c242e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="6" r:id="R8576dac86e3841f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +22,7 @@
     <x:numFmt numFmtId="200" formatCode="0.00"/>
     <x:numFmt numFmtId="201" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -53,6 +54,18 @@
       <x:i/>
       <x:sz val="11"/>
       <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="9"/>
+      <x:color rgb="FF6B7280"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -101,7 +114,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="28">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -140,22 +153,39 @@
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="201" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
   </x:cellXfs>
@@ -231,6 +261,335 @@
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="bac3d4ac-6310-4050-9783-14cfdba677ae"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R66cdb46197e146f7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="f150938f-c0ce-49a7-866c-0ced09993435"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R06cb6e2fe5f34865"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="b014cd1a-00ce-4f13-bdf2-b331697cc429"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7ee2b1508e5f40aa"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="6ea4bc63-c241-40a2-a958-92d82d4122c2"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2d0314bcdd0a49d0"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="64a8a201-4279-4c15-b819-f08d78405f5e"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R032b736719cc4d96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="d56e322e-82f1-47d4-bb80-c94e1043b0e7"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6b544f7a2b3048f9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="576a465f-5405-4978-beec-4e5548e5b1aa"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R07a47e47521b447a"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="8a13efc3-8166-4539-8085-0c43ca22eefc"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0e9fff79102340e8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="3eb2d835-326f-4a45-951f-22b66f5a91d8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1c32660de22244be"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="e84268cf-7b5c-4f24-80c7-19c313984720"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rabef248c63fd4c3f"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="32a03535-4485-4296-a516-8190d9315295"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3dec1176d8b5473d"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="5475ec6d-a94e-476b-a43e-aab0ba7284a0"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R71706e1d61cf4963"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -318,7 +677,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="model_id"/>
@@ -679,22 +1038,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>星尘</x:v>
+        <x:v>Boston Dynamics</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Astribot S1</x:v>
+        <x:v>Atlas</x:v>
       </x:c>
       <x:c r="D8" s="16" t="n">
-        <x:v>3.95</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G8" s="15" t="str">
-        <x:v>论文确认全向底盘；量产配置、接口和工业认证资料不足</x:v>
+        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
@@ -702,13 +1061,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>Boston Dynamics</x:v>
+        <x:v>Figure AI</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Atlas</x:v>
+        <x:v>Figure 03</x:v>
       </x:c>
       <x:c r="D9" s="16" t="n">
-        <x:v>3.85</x:v>
+        <x:v>3.8000000000000003</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>待实测</x:v>
@@ -717,7 +1076,7 @@
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G9" s="15" t="str">
-        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
+        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -725,22 +1084,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>Figure AI</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>Figure 03</x:v>
+        <x:v>D1 擎骏系列</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
-        <x:v>3.8000000000000003</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
+        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -748,22 +1107,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>它石智航</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>D1 擎骏系列</x:v>
+        <x:v>TARS A1</x:v>
       </x:c>
       <x:c r="D11" s="16" t="n">
-        <x:v>3.8</x:v>
+        <x:v>3.6500000000000004</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
+        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -771,22 +1130,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>它石智航</x:v>
+        <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>TARS A1</x:v>
+        <x:v>LimX Oli EDU</x:v>
       </x:c>
       <x:c r="D12" s="16" t="n">
-        <x:v>3.6500000000000004</x:v>
+        <x:v>3.3499999999999996</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
-        <x:v>条件 POC</x:v>
+        <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G12" s="15" t="str">
-        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
+        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -794,22 +1153,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
-        <x:v>逐际动力</x:v>
+        <x:v>星尘</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>LimX Oli EDU</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="D13" s="16" t="n">
-        <x:v>3.3499999999999996</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str">
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G13" s="15" t="str">
-        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
+        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
@@ -1015,6 +1374,227 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="3" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="3" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>当前评比型号图示｜仅用于型号识别，参数与配置以来源证据为准</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+      <x:c r="M1" s="1"/>
+      <x:c r="N1" s="1"/>
+      <x:c r="O1" s="1"/>
+      <x:c r="P1" s="1"/>
+      <x:c r="Q1" s="1"/>
+      <x:c r="R1" s="1"/>
+      <x:c r="S1" s="1"/>
+      <x:c r="T1" s="1"/>
+      <x:c r="U1" s="1"/>
+      <x:c r="V1" s="1"/>
+      <x:c r="W1" s="1"/>
+      <x:c r="X1" s="1"/>
+      <x:c r="Y1" s="1"/>
+      <x:c r="Z1" s="1"/>
+      <x:c r="AA1" s="1"/>
+      <x:c r="AB1" s="1"/>
+      <x:c r="AC1" s="1"/>
+      <x:c r="AD1" s="1"/>
+      <x:c r="AE1" s="1"/>
+      <x:c r="AF1" s="1"/>
+      <x:c r="AG1" s="1"/>
+      <x:c r="AH1" s="1"/>
+      <x:c r="AI1" s="1"/>
+      <x:c r="AJ1" s="1"/>
+      <x:c r="AK1" s="1"/>
+      <x:c r="AL1" s="1"/>
+      <x:c r="AM1" s="1"/>
+      <x:c r="AN1" s="1"/>
+      <x:c r="AO1" s="1"/>
+      <x:c r="AP1" s="1"/>
+      <x:c r="AQ1" s="1"/>
+      <x:c r="AR1" s="1"/>
+      <x:c r="AS1" s="1"/>
+      <x:c r="AT1" s="1"/>
+      <x:c r="AU1" s="1"/>
+      <x:c r="AV1" s="1"/>
+      <x:c r="AW1" s="1"/>
+      <x:c r="AX1" s="1"/>
+      <x:c r="AY1" s="1"/>
+      <x:c r="AZ1" s="1"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="21" t="str">
+        <x:v>图片来源和本地文件映射见 data/images.csv；图片版权归原厂商或原发布方。</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str"/>
+      <x:c r="C2" s="21" t="str"/>
+      <x:c r="D2" s="21" t="str"/>
+      <x:c r="E2" s="21" t="str"/>
+      <x:c r="F2" s="21" t="str"/>
+    </x:row>
+    <x:row r="3" ht="18" customHeight="1"/>
+    <x:row r="4" ht="18" customHeight="1">
+      <x:c r="A4" s="25" t="str">
+        <x:v>AgiBot 精灵G2</x:v>
+      </x:c>
+      <x:c r="C4" s="25" t="str">
+        <x:v>Astribot T1</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="str">
+        <x:v>D1 擎骏系列</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="18" customHeight="1"/>
+    <x:row r="6" ht="18" customHeight="1"/>
+    <x:row r="7" ht="18" customHeight="1"/>
+    <x:row r="8" ht="18" customHeight="1"/>
+    <x:row r="9" ht="18" customHeight="1"/>
+    <x:row r="10" ht="18" customHeight="1"/>
+    <x:row r="11" ht="18" customHeight="1"/>
+    <x:row r="12" ht="18" customHeight="1"/>
+    <x:row r="13" ht="18" customHeight="1"/>
+    <x:row r="14" ht="18" customHeight="1"/>
+    <x:row r="15" ht="18" customHeight="1">
+      <x:c r="A15" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="C15" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="18" customHeight="1"/>
+    <x:row r="17" ht="18" customHeight="1">
+      <x:c r="A17" s="25" t="str">
+        <x:v>JUNO2-SD 龙骏系列</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="str">
+        <x:v>Unitree G1-D 旗舰版</x:v>
+      </x:c>
+      <x:c r="E17" s="25" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="18" customHeight="1"/>
+    <x:row r="19" ht="18" customHeight="1"/>
+    <x:row r="20" ht="18" customHeight="1"/>
+    <x:row r="21" ht="18" customHeight="1"/>
+    <x:row r="22" ht="18" customHeight="1"/>
+    <x:row r="23" ht="18" customHeight="1"/>
+    <x:row r="24" ht="18" customHeight="1"/>
+    <x:row r="25" ht="18" customHeight="1"/>
+    <x:row r="26" ht="18" customHeight="1"/>
+    <x:row r="27" ht="18" customHeight="1"/>
+    <x:row r="28" ht="18" customHeight="1">
+      <x:c r="A28" s="27" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="C28" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="E28" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="18" customHeight="1"/>
+    <x:row r="30" ht="18" customHeight="1">
+      <x:c r="A30" s="25" t="str">
+        <x:v>Figure 03</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="str">
+        <x:v>Optimus</x:v>
+      </x:c>
+      <x:c r="E30" s="25" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="18" customHeight="1"/>
+    <x:row r="32" ht="18" customHeight="1"/>
+    <x:row r="33" ht="18" customHeight="1"/>
+    <x:row r="34" ht="18" customHeight="1"/>
+    <x:row r="35" ht="18" customHeight="1"/>
+    <x:row r="36" ht="18" customHeight="1"/>
+    <x:row r="37" ht="18" customHeight="1"/>
+    <x:row r="38" ht="18" customHeight="1"/>
+    <x:row r="39" ht="18" customHeight="1"/>
+    <x:row r="40" ht="18" customHeight="1"/>
+    <x:row r="41" ht="18" customHeight="1">
+      <x:c r="A41" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="C41" s="27" t="str">
+        <x:v>第三方型号图库</x:v>
+      </x:c>
+      <x:c r="E41" s="27" t="str">
+        <x:v>经销商产品图</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="18" customHeight="1"/>
+    <x:row r="43" ht="18" customHeight="1">
+      <x:c r="A43" s="25" t="str">
+        <x:v>TRON 2 双臂形态</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="str">
+        <x:v>Galaxea R1 Pro 2026</x:v>
+      </x:c>
+      <x:c r="E43" s="25" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="18" customHeight="1"/>
+    <x:row r="45" ht="18" customHeight="1"/>
+    <x:row r="46" ht="18" customHeight="1"/>
+    <x:row r="47" ht="18" customHeight="1"/>
+    <x:row r="48" ht="18" customHeight="1"/>
+    <x:row r="49" ht="18" customHeight="1"/>
+    <x:row r="50" ht="18" customHeight="1"/>
+    <x:row r="51" ht="18" customHeight="1"/>
+    <x:row r="52" ht="18" customHeight="1"/>
+    <x:row r="53" ht="18" customHeight="1"/>
+    <x:row r="54" ht="18" customHeight="1">
+      <x:c r="A54" s="27" t="str">
+        <x:v>第三方型号图库</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="E54" s="27" t="str">
+        <x:v>政府公开信息</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="18" customHeight="1"/>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc34418df3938428d"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1090,48 +1670,48 @@
       <x:c r="AZ1" s="1"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="24" t="str">
+      <x:c r="A3" s="31" t="str">
         <x:v>评分维度</x:v>
       </x:c>
-      <x:c r="B3" s="24" t="str">
+      <x:c r="B3" s="31" t="str">
         <x:v>底盘全向与贴线能力</x:v>
       </x:c>
-      <x:c r="C3" s="24" t="str">
+      <x:c r="C3" s="31" t="str">
         <x:v>双臂与躯干工作空间</x:v>
       </x:c>
-      <x:c r="D3" s="24" t="str">
+      <x:c r="D3" s="31" t="str">
         <x:v>力控与柔顺能力</x:v>
       </x:c>
-      <x:c r="E3" s="24" t="str">
+      <x:c r="E3" s="31" t="str">
         <x:v>定位与视觉闭环</x:v>
       </x:c>
-      <x:c r="F3" s="24" t="str">
+      <x:c r="F3" s="31" t="str">
         <x:v>SDK与末端接口成熟度</x:v>
       </x:c>
-      <x:c r="G3" s="24" t="str">
+      <x:c r="G3" s="31" t="str">
         <x:v>工业可靠性与维护</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="26" t="str">
+      <x:c r="A4" s="33" t="str">
         <x:v>权重</x:v>
       </x:c>
-      <x:c r="B4" s="27" t="n">
+      <x:c r="B4" s="34" t="n">
         <x:v>0.25</x:v>
       </x:c>
-      <x:c r="C4" s="27" t="n">
+      <x:c r="C4" s="34" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="D4" s="27" t="n">
+      <x:c r="D4" s="34" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="E4" s="27" t="n">
+      <x:c r="E4" s="34" t="n">
         <x:v>0.15</x:v>
       </x:c>
-      <x:c r="F4" s="27" t="n">
+      <x:c r="F4" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="G4" s="27" t="n">
+      <x:c r="G4" s="34" t="n">
         <x:v>0.15</x:v>
       </x:c>
     </x:row>
@@ -1224,42 +1804,42 @@
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>Astribot S1</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="E8" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F8" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G8" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H8" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I8" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:f>IF(C8&lt;&gt;"是","",SUMPRODUCT(E8:J8,$B$4:$G$4))</x:f>
-        <x:v>3.95</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="L8" s="15" t="str">
         <x:f>IF(C8&lt;&gt;"是","不参与移动本体排名",IF(D8="不通过","不进入布线POC",IF(K8&gt;=4.2,"优先POC",IF(K8&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>条件POC</x:v>
+        <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="M8" s="15" t="str">
-        <x:v>论文确认全向底盘；量产配置、接口和工业认证资料不足</x:v>
+        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
@@ -1937,12 +2517,12 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R728af8975e604a66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe4832f0df04260"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2265,93 +2845,75 @@
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
-        <x:v>astribot_s1</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
-        <x:v>Astribot S1</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
         <x:v>移动双臂本体</x:v>
       </x:c>
       <x:c r="E5" s="15" t="str">
-        <x:v>科研/行业共创</x:v>
+        <x:v>量产/发货</x:v>
       </x:c>
       <x:c r="F5" s="15" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G5" s="15" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H5" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I5" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J5" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="G5" s="15"/>
+      <x:c r="H5" s="15"/>
+      <x:c r="I5" s="15"/>
+      <x:c r="J5" s="15"/>
       <x:c r="K5" s="15" t="str">
-        <x:v>三自由度全向移动底盘</x:v>
+        <x:v>紧凑轮式底盘（轮系未公开）</x:v>
       </x:c>
       <x:c r="L5" s="15" t="str">
-        <x:v>是</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="M5" s="15"/>
       <x:c r="N5" s="15" t="n">
-        <x:v>1700</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="O5" s="15" t="n">
-        <x:v>1700</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="P5" s="15"/>
       <x:c r="Q5" s="15"/>
       <x:c r="R5" s="15" t="n">
-        <x:v>80</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="S5" s="15"/>
-      <x:c r="T5" s="15" t="n">
-        <x:v>1940</x:v>
-      </x:c>
+      <x:c r="T5" s="15"/>
       <x:c r="U5" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="V5" s="15"/>
       <x:c r="W5" s="15"/>
       <x:c r="X5" s="15"/>
-      <x:c r="Y5" s="15" t="str">
-        <x:v>0-2.0</x:v>
-      </x:c>
-      <x:c r="Z5" s="15" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
+      <x:c r="Y5" s="15" t="str"/>
+      <x:c r="Z5" s="15"/>
       <x:c r="AA5" s="15"/>
       <x:c r="AB5" s="15" t="str">
-        <x:v>强调柔顺与全身操作，公开量化不足</x:v>
+        <x:v>绳驱柔性；碰撞卸力（控制与传感指标未公开）</x:v>
       </x:c>
       <x:c r="AC5" s="15"/>
       <x:c r="AD5" s="15"/>
-      <x:c r="AE5" s="15" t="str">
-        <x:v>未公开</x:v>
-      </x:c>
-      <x:c r="AF5" s="15" t="str">
-        <x:v>4-6</x:v>
-      </x:c>
+      <x:c r="AE5" s="15" t="str"/>
+      <x:c r="AF5" s="15" t="str"/>
       <x:c r="AG5" s="15" t="str"/>
       <x:c r="AH5" s="15" t="str">
-        <x:v>平行二指夹爪</x:v>
+        <x:v>支持多样末端配置与更换</x:v>
       </x:c>
       <x:c r="AI5" s="15" t="str">
-        <x:v>API；VR遥操作；仿真与训练工具链</x:v>
+        <x:v>末端与算力背包扩展接口；自动回充；快捷换电（协议未公开）</x:v>
       </x:c>
       <x:c r="AJ5" s="15" t="str">
-        <x:v>官网+研发论文</x:v>
+        <x:v>官网+政府及媒体报道</x:v>
       </x:c>
       <x:c r="AK5" s="15" t="str">
-        <x:v>底盘轮型、速度、定位精度及工业认证未公开</x:v>
+        <x:v>8.99万元起；底盘是否全向、移动与操作精度、SDK协议、续航和工业认证未公开</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -3585,12 +4147,12 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab0e2da811f447fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47646d5dd2334ada"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3842,7 +4404,7 @@
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>S1</x:v>
+        <x:v>T1</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
         <x:v>P0</x:v>
@@ -3851,10 +4413,10 @@
         <x:v>底盘</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str">
-        <x:v>全向底盘的轮型、最大横移速度、定位精度和航向误差是多少</x:v>
+        <x:v>紧凑轮式底盘采用什么轮系，是否支持保持机身朝向纯横移/蟹行，最大横移速度、定位精度和航向误差是多少</x:v>
       </x:c>
       <x:c r="G9" s="15" t="str">
-        <x:v>论文只确认3DOF全向底盘</x:v>
+        <x:v>公开资料只说明紧凑轮式底盘和自动回充，未证明全向能力</x:v>
       </x:c>
       <x:c r="H9" s="15" t="str">
         <x:v>待供应商回复</x:v>
@@ -3870,19 +4432,19 @@
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>S1</x:v>
+        <x:v>T1</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
         <x:v>P0</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>力控</x:v>
+        <x:v>精度与力控</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
-        <x:v>关节或末端力传感器的分辨率、采样率和阻抗控制接口是什么</x:v>
+        <x:v>机械臂重复定位精度、整机移动后TCP误差、力传感器分辨率/采样率及阻抗控制接口分别是多少</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>官网未公开量化参数</x:v>
+        <x:v>仅公开绳驱柔性和碰撞卸力，未给量化精度与力控指标</x:v>
       </x:c>
       <x:c r="H10" s="15" t="str">
         <x:v>待供应商回复</x:v>
@@ -3898,19 +4460,19 @@
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>S1</x:v>
+        <x:v>T1</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>P1</x:v>
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
         <x:v>接口</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
-        <x:v>SDK协议、控制频率、ROS版本和末端供电通信接口是什么</x:v>
+        <x:v>SDK协议、控制频率、ROS版本、末端供电通信和算力背包接口定义是什么</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>官网只说明提供API和工具链</x:v>
+        <x:v>公开资料只说明支持软硬件扩展、末端与算力背包更换</x:v>
       </x:c>
       <x:c r="H11" s="15" t="str">
         <x:v>待供应商回复</x:v>
@@ -3926,7 +4488,7 @@
         <x:v>星尘</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>S1</x:v>
+        <x:v>T1</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
         <x:v>P1</x:v>
@@ -3935,10 +4497,10 @@
         <x:v>工业安全</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
-        <x:v>IP等级、安全认证、MTBF和连续运行数据是什么</x:v>
+        <x:v>电池容量与续航、换电/回充节拍、IP等级、安全认证、MTBF和连续运行数据是什么</x:v>
       </x:c>
       <x:c r="G12" s="15" t="str">
-        <x:v>公开资料未披露</x:v>
+        <x:v>公开资料未披露量化指标</x:v>
       </x:c>
       <x:c r="H12" s="15" t="str">
         <x:v>待供应商回复</x:v>
@@ -4609,12 +5171,12 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01a047f617b34a1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfceb751f894a4c15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4631,7 +5193,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="5" t="str">
-        <x:v>来源证据登记｜内部文件仅登记名称，不随仓库上传</x:v>
+        <x:v>来源证据登记｜原始供应商文件按仓库策略归档</x:v>
       </x:c>
       <x:c r="B1" s="5"/>
       <x:c r="C1" s="5"/>
@@ -4727,8 +5289,9 @@
       <x:c r="D4" s="15" t="str">
         <x:v>智元精灵G2产品用户手册</x:v>
       </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>https://www.agibot.com.cn/filepage/362.html</x:v>
+      <x:c r="E4" s="15" t="e">
+        <x:f>HYPERLINK("https://www.agibot.com.cn/filepage/362.html","https://www.agibot.com.cn/filepage/362.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.agibot.com.cn/filepage/362.html, friendlyName=https://www.agibot.com.cn/filepage/362.html</x:v>
       </x:c>
       <x:c r="F4" s="15" t="str">
         <x:v>2026-04-28</x:v>
@@ -4745,19 +5308,20 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="15" t="str">
-        <x:v>src_astribot_s1_official</x:v>
+        <x:v>src_astribot_t1_home</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
-        <x:v>astribot_s1</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
-        <x:v>星尘智能S1产品页</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="str">
-        <x:v>https://www.astribot.com/product/</x:v>
+        <x:v>星尘智能首页 T1 发布信息</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="e">
+        <x:f>HYPERLINK("https://www.astribot.com/","https://www.astribot.com/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.astribot.com/, friendlyName=https://www.astribot.com/</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str"/>
       <x:c r="G5" s="15" t="str">
@@ -4767,27 +5331,28 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I5" s="15" t="str">
-        <x:v>包含操作性能和整机基础参数</x:v>
+        <x:v>确认T1型号与8.99万元起售价；官网尚无T1完整数据表</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>src_astribot_suite</x:v>
+        <x:v>src_astribot_t1_wuxi</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>astribot_s1</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
-        <x:v>研发论文</x:v>
+        <x:v>政府公开信息</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>Towards Human-level Intelligence via Human-like Whole-Body Manipulation</x:v>
-      </x:c>
-      <x:c r="E6" s="15" t="str">
-        <x:v>https://arxiv.org/abs/2507.17141</x:v>
+        <x:v>技术硬核价格亲民 多元场景显身手</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="e">
+        <x:f>HYPERLINK("https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml","https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml, friendlyName=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
-        <x:v>2025-07-23</x:v>
+        <x:v>2026-07-11</x:v>
       </x:c>
       <x:c r="G6" s="15" t="str">
         <x:v>2026-09-15</x:v>
@@ -4796,132 +5361,140 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I6" s="15" t="str">
-        <x:v>包含23自由度构成和三自由度全向底盘</x:v>
+        <x:v>确认无锡工厂量产下线、23自由度、单臂5kg、绳驱和底盘扩展接口</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
       <x:c r="A7" s="15" t="str">
-        <x:v>src_unitree_g1d</x:v>
+        <x:v>src_astribot_t1_sznews</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
-        <x:v>unitree_g1d_flagship</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>地方官方媒体</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
-        <x:v>Unitree G1-D产品参数</x:v>
-      </x:c>
-      <x:c r="E7" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/mobile/G1-D/</x:v>
-      </x:c>
-      <x:c r="F7" s="15" t="str"/>
+        <x:v>煎牛排调酒做实验 星尘智能发布绳驱AI机器人T1</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="e">
+        <x:f>HYPERLINK("https://www.sznews.com/news/content/2026-05/27/content_32067943.htm","https://www.sznews.com/news/content/2026-05/27/content_32067943.htm")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm, friendlyName=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str">
+        <x:v>2026-05-27</x:v>
+      </x:c>
       <x:c r="G7" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H7" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I7" s="15" t="str">
-        <x:v>同时覆盖旗舰版和通用版</x:v>
+        <x:v>确认155cm、约66kg、23自由度不含末端、单臂5kg、自动回充和快捷换电</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" customHeight="1">
       <x:c r="A8" s="15" t="str">
-        <x:v>src_unitree_g1d_std</x:v>
+        <x:v>src_astribot_t1_wrc</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>unitree_g1d_standard</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>行业展会官方信息</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>Unitree G1-D产品参数</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="str">
-        <x:v>https://www.unitree.com/cn/mobile/G1-D/</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="str"/>
+        <x:v>2026世界机器人大会星尘智能展品介绍</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="e">
+        <x:f>HYPERLINK("https://wrc.cie.org.cn/expo/company/441.html","https://wrc.cie.org.cn/expo/company/441.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://wrc.cie.org.cn/expo/company/441.html, friendlyName=https://wrc.cie.org.cn/expo/company/441.html</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="str">
+        <x:v>2026-08-19</x:v>
+      </x:c>
       <x:c r="G8" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H8" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中高</x:v>
       </x:c>
       <x:c r="I8" s="15" t="str">
-        <x:v>通用版无主动底盘参数</x:v>
+        <x:v>确认轻量化机身、紧凑底盘、多样末端和软硬件扩展；未披露轮系</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="42" customHeight="1">
       <x:c r="A9" s="15" t="str">
-        <x:v>src_zdl_d1</x:v>
+        <x:v>src_unitree_g1d</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>zdl_d1</x:v>
+        <x:v>unitree_g1d_flagship</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>供应商PDF</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>D1（擎骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="str">
-        <x:v>sources/raw/01_智动力/D1（擎骏系列）.pdf</x:v>
+        <x:v>Unitree G1-D产品参数</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="e">
+        <x:f>HYPERLINK("https://www.unitree.com/cn/mobile/G1-D/","https://www.unitree.com/cn/mobile/G1-D/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.unitree.com/cn/mobile/G1-D/, friendlyName=https://www.unitree.com/cn/mobile/G1-D/</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str"/>
       <x:c r="G9" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H9" s="15" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I9" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
+        <x:v>同时覆盖旗舰版和通用版</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>src_zdl_juno2</x:v>
+        <x:v>src_unitree_g1d_std</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>zdl_juno2</x:v>
+        <x:v>unitree_g1d_standard</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>供应商PDF</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>JUNO2-SD（龙骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E10" s="15" t="str">
-        <x:v>sources/raw/01_智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
+        <x:v>Unitree G1-D产品参数</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="e">
+        <x:f>HYPERLINK("https://www.unitree.com/cn/mobile/G1-D/","https://www.unitree.com/cn/mobile/G1-D/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.unitree.com/cn/mobile/G1-D/, friendlyName=https://www.unitree.com/cn/mobile/G1-D/</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str"/>
       <x:c r="G10" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H10" s="15" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I10" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
+        <x:v>通用版无主动底盘参数</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="42" customHeight="1">
       <x:c r="A11" s="15" t="str">
-        <x:v>src_zdl_juno1</x:v>
+        <x:v>src_zdl_d1</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>zdl_juno1</x:v>
+        <x:v>zdl_d1</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>JUNO1-P（智骏系列）.pdf</x:v>
+        <x:v>D1（擎骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>sources/raw/01_智动力/JUNO1-P（智骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/D1（擎骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str"/>
       <x:c r="G11" s="15" t="str">
@@ -4936,19 +5509,19 @@
     </x:row>
     <x:row r="12" ht="42" customHeight="1">
       <x:c r="A12" s="15" t="str">
-        <x:v>src_zdl_l1</x:v>
+        <x:v>src_zdl_juno2</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>zdl_l1</x:v>
+        <x:v>zdl_juno2</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
-        <x:v>L1（灵骏系列）.pdf</x:v>
+        <x:v>JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>sources/raw/01_智动力/L1（灵骏系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str"/>
       <x:c r="G12" s="15" t="str">
@@ -4963,23 +5536,21 @@
     </x:row>
     <x:row r="13" ht="42" customHeight="1">
       <x:c r="A13" s="15" t="str">
-        <x:v>src_zdl_z1</x:v>
+        <x:v>src_zdl_juno1</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
-        <x:v>zdl_z1</x:v>
+        <x:v>zdl_juno1</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>供应商开发手册</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
-        <x:v>全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
+        <x:v>JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>sources/raw/01_智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
-      </x:c>
-      <x:c r="F13" s="15" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
+        <x:v>sources/raw/01_智动力/JUNO1-P（智骏系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F13" s="15" t="str"/>
       <x:c r="G13" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -4987,24 +5558,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>接口文档存在多项待澄清问题</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>src_zdl_ha</x:v>
+        <x:v>src_zdl_l1</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>zdl_ha</x:v>
+        <x:v>zdl_l1</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>人形臂（HA系列）.pdf</x:v>
+        <x:v>L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E14" s="15" t="str">
-        <x:v>sources/raw/01_智动力/人形臂（HA系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F14" s="15" t="str"/>
       <x:c r="G14" s="15" t="str">
@@ -5014,26 +5585,28 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I14" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="15" t="str">
-        <x:v>src_zdl_fa</x:v>
+        <x:v>src_zdl_z1</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>zdl_fa</x:v>
+        <x:v>zdl_z1</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>供应商PDF</x:v>
+        <x:v>供应商开发手册</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>桌面臂（FA系列）.pdf</x:v>
+        <x:v>全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
-        <x:v>sources/raw/01_智动力/桌面臂（FA系列）.pdf</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="str"/>
+        <x:v>sources/raw/01_智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="str">
+        <x:v>2026-07-25</x:v>
+      </x:c>
       <x:c r="G15" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5041,24 +5614,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I15" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>接口文档存在多项待澄清问题</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="15" t="str">
-        <x:v>src_flexiv_rizon4_manual</x:v>
+        <x:v>src_zdl_ha</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>flexiv_rizon4</x:v>
+        <x:v>zdl_ha</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+        <x:v>人形臂（HA系列）.pdf</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+        <x:v>sources/raw/01_智动力/人形臂（HA系列）.pdf</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str"/>
       <x:c r="G16" s="15" t="str">
@@ -5073,23 +5646,21 @@
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="15" t="str">
-        <x:v>src_flexiv_rizon_datasheet</x:v>
+        <x:v>src_zdl_fa</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>flexiv_rizon</x:v>
+        <x:v>zdl_fa</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+        <x:v>桌面臂（FA系列）.pdf</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="str">
-        <x:v>2024-09</x:v>
-      </x:c>
+        <x:v>sources/raw/01_智动力/桌面臂（FA系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F17" s="15" t="str"/>
       <x:c r="G17" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5102,23 +5673,21 @@
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="15" t="str">
-        <x:v>src_flexiv_grav_manual</x:v>
+        <x:v>src_flexiv_rizon4_manual</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>flexiv_grav</x:v>
+        <x:v>flexiv_rizon4</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>星擎用户手册_V1.0_202404(2).pdf</x:v>
+        <x:v>Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/02_Grav_星擎/星擎用户手册_V1.0_202404(2).pdf</x:v>
-      </x:c>
-      <x:c r="F18" s="15" t="str">
-        <x:v>2024-04</x:v>
-      </x:c>
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F18" s="15" t="str"/>
       <x:c r="G18" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5126,26 +5695,28 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>末端执行器资料待结构化</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="15" t="str">
-        <x:v>src_flexiv_ft_datasheet</x:v>
+        <x:v>src_flexiv_rizon_datasheet</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>flexiv_ft</x:v>
+        <x:v>flexiv_rizon</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+        <x:v>拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/03_FT_拂晓传感器/拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="str"/>
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+      </x:c>
+      <x:c r="F19" s="15" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
       <x:c r="G19" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5153,27 +5724,27 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>力传感器资料待结构化</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="15" t="str">
-        <x:v>src_tianji_marvin</x:v>
+        <x:v>src_flexiv_grav_manual</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>tianji_marvin_m6ccs</x:v>
+        <x:v>flexiv_grav</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
+        <x:v>星擎用户手册_V1.0_202404(2).pdf</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
-        <x:v>sources/raw/03_天机智能_Marvin/01_Marvin双臂/Marvin系列 三折页 250721-CN.pdf</x:v>
+        <x:v>sources/raw/02_非夕_Flexiv/02_Grav_星擎/星擎用户手册_V1.0_202404(2).pdf</x:v>
       </x:c>
       <x:c r="F20" s="15" t="str">
-        <x:v>2025-07</x:v>
+        <x:v>2024-04</x:v>
       </x:c>
       <x:c r="G20" s="15" t="str">
         <x:v>2026-09-15</x:v>
@@ -5182,22 +5753,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>单臂/双臂模块参数，不含标准底盘</x:v>
+        <x:v>末端执行器资料待结构化</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="15" t="str">
-        <x:v>src_material_index</x:v>
-      </x:c>
-      <x:c r="B21" s="15" t="str"/>
+        <x:v>src_flexiv_ft_datasheet</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="str">
+        <x:v>flexiv_ft</x:v>
+      </x:c>
       <x:c r="C21" s="15" t="str">
-        <x:v>内部索引</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>供应链材料索引.md</x:v>
+        <x:v>拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
       </x:c>
       <x:c r="E21" s="15" t="str">
-        <x:v>sources/raw/00_索引/供应链材料索引.md</x:v>
+        <x:v>sources/raw/02_非夕_Flexiv/03_FT_拂晓传感器/拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
       </x:c>
       <x:c r="F21" s="15" t="str"/>
       <x:c r="G21" s="15" t="str">
@@ -5207,82 +5780,81 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>原目录索引的归档副本</x:v>
+        <x:v>力传感器资料待结构化</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="15" t="str">
-        <x:v>src_boston_atlas</x:v>
+        <x:v>src_tianji_marvin</x:v>
       </x:c>
       <x:c r="B22" s="15" t="str">
-        <x:v>boston_atlas_2026</x:v>
+        <x:v>tianji_marvin_m6ccs</x:v>
       </x:c>
       <x:c r="C22" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>Atlas产品与规格</x:v>
+        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
       </x:c>
       <x:c r="E22" s="15" t="str">
-        <x:v>https://bostondynamics.com/products/atlas/</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="str"/>
+        <x:v>sources/raw/03_天机智能_Marvin/01_Marvin双臂/Marvin系列 三折页 250721-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="str">
+        <x:v>2025-07</x:v>
+      </x:c>
       <x:c r="G22" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H22" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>披露56自由度、负载、续航、IP67、工作范围和Orbit集成</x:v>
+        <x:v>单臂/双臂模块参数，不含标准底盘</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="15" t="str">
-        <x:v>src_figure03_product</x:v>
-      </x:c>
-      <x:c r="B23" s="15" t="str">
-        <x:v>figure_03</x:v>
-      </x:c>
+        <x:v>src_material_index</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="str"/>
       <x:c r="C23" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>内部索引</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>Figure 03产品页</x:v>
+        <x:v>供应链材料索引.md</x:v>
       </x:c>
       <x:c r="E23" s="15" t="str">
-        <x:v>https://www.figure.ai/figure</x:v>
+        <x:v>sources/raw/00_索引/供应链材料索引.md</x:v>
       </x:c>
       <x:c r="F23" s="15" t="str"/>
       <x:c r="G23" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H23" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>披露身高、重量、负载、速度和续航</x:v>
+        <x:v>原目录索引的归档副本</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="15" t="str">
-        <x:v>src_figure03_intro</x:v>
+        <x:v>src_boston_atlas</x:v>
       </x:c>
       <x:c r="B24" s="15" t="str">
-        <x:v>figure_03</x:v>
+        <x:v>boston_atlas_2026</x:v>
       </x:c>
       <x:c r="C24" s="15" t="str">
-        <x:v>官方技术文章</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
-        <x:v>Introducing Figure 03</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="str">
-        <x:v>https://www.figure.ai/news/introducing-figure-03</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="str">
-        <x:v>2025-10-09</x:v>
-      </x:c>
+        <x:v>Atlas产品与规格</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="e">
+        <x:f>HYPERLINK("https://bostondynamics.com/products/atlas/","https://bostondynamics.com/products/atlas/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://bostondynamics.com/products/atlas/, friendlyName=https://bostondynamics.com/products/atlas/</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="str"/>
       <x:c r="G24" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5290,28 +5862,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>披露触觉、感知、充电、电池安全和量产设计</x:v>
+        <x:v>披露56自由度、负载、续航、IP67、工作范围和Orbit集成</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="15" t="str">
-        <x:v>src_figure03_bmw</x:v>
+        <x:v>src_figure03_product</x:v>
       </x:c>
       <x:c r="B25" s="15" t="str">
         <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C25" s="15" t="str">
-        <x:v>官方客户进展</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>F.03 Arrives at BMW</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="str">
-        <x:v>https://www.figure.ai/news/f-03-at-bmw</x:v>
-      </x:c>
-      <x:c r="F25" s="15" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
+        <x:v>Figure 03产品页</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="e">
+        <x:f>HYPERLINK("https://www.figure.ai/figure","https://www.figure.ai/figure")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/figure, friendlyName=https://www.figure.ai/figure</x:v>
+      </x:c>
+      <x:c r="F25" s="15" t="str"/>
       <x:c r="G25" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5319,26 +5890,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I25" s="15" t="str">
-        <x:v>披露BMW工厂物流验证和全身操作</x:v>
+        <x:v>披露身高、重量、负载、速度和续航</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="15" t="str">
-        <x:v>src_tesla_ai</x:v>
+        <x:v>src_figure03_intro</x:v>
       </x:c>
       <x:c r="B26" s="15" t="str">
-        <x:v>tesla_optimus</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C26" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>官方技术文章</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>Tesla AI and Robotics</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="str">
-        <x:v>https://www.tesla.com/AI</x:v>
-      </x:c>
-      <x:c r="F26" s="15" t="str"/>
+        <x:v>Introducing Figure 03</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="e">
+        <x:f>HYPERLINK("https://www.figure.ai/news/introducing-figure-03","https://www.figure.ai/news/introducing-figure-03")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/introducing-figure-03, friendlyName=https://www.figure.ai/news/introducing-figure-03</x:v>
+      </x:c>
+      <x:c r="F26" s="15" t="str">
+        <x:v>2025-10-09</x:v>
+      </x:c>
       <x:c r="G26" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5346,27 +5920,28 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>仅说明双足通用自主机器人目标；未给工程规格</x:v>
+        <x:v>披露触觉、感知、充电、电池安全和量产设计</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="15" t="str">
-        <x:v>src_tesla_2026q2</x:v>
+        <x:v>src_figure03_bmw</x:v>
       </x:c>
       <x:c r="B27" s="15" t="str">
-        <x:v>tesla_optimus</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C27" s="15" t="str">
-        <x:v>官方投资者文件</x:v>
+        <x:v>官方客户进展</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>Tesla 2026 Q2 Update</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="str">
-        <x:v>https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf</x:v>
+        <x:v>F.03 Arrives at BMW</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="e">
+        <x:f>HYPERLINK("https://www.figure.ai/news/f-03-at-bmw","https://www.figure.ai/news/f-03-at-bmw")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/f-03-at-bmw, friendlyName=https://www.figure.ai/news/f-03-at-bmw</x:v>
       </x:c>
       <x:c r="F27" s="15" t="str">
-        <x:v>2026-07-22</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="G27" s="15" t="str">
         <x:v>2026-09-15</x:v>
@@ -5375,24 +5950,25 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>披露Optimus产线建设与训练数据用途；未给本体规格</x:v>
+        <x:v>披露BMW工厂物流验证和全身操作</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="15" t="str">
-        <x:v>src_limx_oli</x:v>
+        <x:v>src_tesla_ai</x:v>
       </x:c>
       <x:c r="B28" s="15" t="str">
-        <x:v>limx_oli_edu</x:v>
+        <x:v>tesla_optimus</x:v>
       </x:c>
       <x:c r="C28" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>LimX Oli产品参数</x:v>
-      </x:c>
-      <x:c r="E28" s="15" t="str">
-        <x:v>https://www.limxdynamics.com/zh/products/oli/spec</x:v>
+        <x:v>Tesla AI and Robotics</x:v>
+      </x:c>
+      <x:c r="E28" s="15" t="e">
+        <x:f>HYPERLINK("https://www.tesla.com/AI","https://www.tesla.com/AI")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.tesla.com/AI, friendlyName=https://www.tesla.com/AI</x:v>
       </x:c>
       <x:c r="F28" s="15" t="str"/>
       <x:c r="G28" s="15" t="str">
@@ -5402,26 +5978,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>披露自由度、尺寸、负载、续航、算力和开发接口</x:v>
+        <x:v>仅说明双足通用自主机器人目标；未给工程规格</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="15" t="str">
-        <x:v>src_limx_tron2</x:v>
+        <x:v>src_tesla_2026q2</x:v>
       </x:c>
       <x:c r="B29" s="15" t="str">
-        <x:v>limx_tron2_dualarm</x:v>
+        <x:v>tesla_optimus</x:v>
       </x:c>
       <x:c r="C29" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>官方投资者文件</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
-        <x:v>TRON 2产品参数</x:v>
-      </x:c>
-      <x:c r="E29" s="15" t="str">
-        <x:v>https://www.limxdynamics.com/zh/products/tron2/spec</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="str"/>
+        <x:v>Tesla 2026 Q2 Update</x:v>
+      </x:c>
+      <x:c r="E29" s="15" t="e">
+        <x:f>HYPERLINK("https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf","https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf, friendlyName=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
       <x:c r="G29" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5429,24 +6008,25 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I29" s="15" t="str">
-        <x:v>披露双臂负载精度、多形态移动、接口和开发工具</x:v>
+        <x:v>披露Optimus产线建设与训练数据用途；未给本体规格</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="15" t="str">
-        <x:v>src_galaxea_r1pro_product</x:v>
+        <x:v>src_limx_oli</x:v>
       </x:c>
       <x:c r="B30" s="15" t="str">
-        <x:v>galaxea_r1pro_2026</x:v>
+        <x:v>limx_oli_edu</x:v>
       </x:c>
       <x:c r="C30" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
-        <x:v>R1 Pro产品参数</x:v>
-      </x:c>
-      <x:c r="E30" s="15" t="str">
-        <x:v>https://galaxea-ai.com/cn/products/R1-Pro</x:v>
+        <x:v>LimX Oli产品参数</x:v>
+      </x:c>
+      <x:c r="E30" s="15" t="e">
+        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/oli/spec","https://www.limxdynamics.com/zh/products/oli/spec")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/oli/spec, friendlyName=https://www.limxdynamics.com/zh/products/oli/spec</x:v>
       </x:c>
       <x:c r="F30" s="15" t="str"/>
       <x:c r="G30" s="15" t="str">
@@ -5456,24 +6036,25 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>披露三舵轮全向底盘、双臂负载、工作空间和算力</x:v>
+        <x:v>披露自由度、尺寸、负载、续航、算力和开发接口</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="15" t="str">
-        <x:v>src_galaxea_r1pro_docs</x:v>
+        <x:v>src_limx_tron2</x:v>
       </x:c>
       <x:c r="B31" s="15" t="str">
-        <x:v>galaxea_r1pro_2026</x:v>
+        <x:v>limx_tron2_dualarm</x:v>
       </x:c>
       <x:c r="C31" s="15" t="str">
-        <x:v>官方开发文档</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
-        <x:v>R1 Pro 2026硬件说明</x:v>
-      </x:c>
-      <x:c r="E31" s="15" t="str">
-        <x:v>https://docs.galaxea-dynamics.com/R1Pro/docs/2026/</x:v>
+        <x:v>TRON 2产品参数</x:v>
+      </x:c>
+      <x:c r="E31" s="15" t="e">
+        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/tron2/spec","https://www.limxdynamics.com/zh/products/tron2/spec")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/tron2/spec, friendlyName=https://www.limxdynamics.com/zh/products/tron2/spec</x:v>
       </x:c>
       <x:c r="F31" s="15" t="str"/>
       <x:c r="G31" s="15" t="str">
@@ -5483,28 +6064,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>披露重量、电池、夹爪、接口和机械臂无制动器风险</x:v>
+        <x:v>披露双臂负载精度、多形态移动、接口和开发工具</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="15" t="str">
-        <x:v>src_tars_tianhai</x:v>
+        <x:v>src_galaxea_r1pro_product</x:v>
       </x:c>
       <x:c r="B32" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>galaxea_r1pro_2026</x:v>
       </x:c>
       <x:c r="C32" s="15" t="str">
-        <x:v>客户官方新闻</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>天海电子与它石智航战略合作</x:v>
-      </x:c>
-      <x:c r="E32" s="15" t="str">
-        <x:v>https://www.thb.com.cn/content/details_17_319668.html</x:v>
-      </x:c>
-      <x:c r="F32" s="15" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
+        <x:v>R1 Pro产品参数</x:v>
+      </x:c>
+      <x:c r="E32" s="15" t="e">
+        <x:f>HYPERLINK("https://galaxea-ai.com/cn/products/R1-Pro","https://galaxea-ai.com/cn/products/R1-Pro")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://galaxea-ai.com/cn/products/R1-Pro, friendlyName=https://galaxea-ai.com/cn/products/R1-Pro</x:v>
+      </x:c>
+      <x:c r="F32" s="15" t="str"/>
       <x:c r="G32" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5512,28 +6092,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>确认汽车线束联合产线与近半年联合攻坚</x:v>
+        <x:v>披露三舵轮全向底盘、双臂负载、工作空间和算力</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="15" t="str">
-        <x:v>src_tars_shanghai</x:v>
+        <x:v>src_galaxea_r1pro_docs</x:v>
       </x:c>
       <x:c r="B33" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>galaxea_r1pro_2026</x:v>
       </x:c>
       <x:c r="C33" s="15" t="str">
-        <x:v>政府官方信息</x:v>
+        <x:v>官方开发文档</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
-        <x:v>它石智航产业化闭环</x:v>
-      </x:c>
-      <x:c r="E33" s="15" t="str">
-        <x:v>https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="str">
-        <x:v>2026-07-10</x:v>
-      </x:c>
+        <x:v>R1 Pro 2026硬件说明</x:v>
+      </x:c>
+      <x:c r="E33" s="15" t="e">
+        <x:f>HYPERLINK("https://docs.galaxea-dynamics.com/R1Pro/docs/2026/","https://docs.galaxea-dynamics.com/R1Pro/docs/2026/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/, friendlyName=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="str"/>
       <x:c r="G33" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5541,26 +6120,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>披露安波福百台计划、33类场景、46工位和DexHand</x:v>
+        <x:v>披露重量、电池、夹爪、接口和机械臂无制动器风险</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="15" t="str">
-        <x:v>src_tars_guinness</x:v>
+        <x:v>src_tars_tianhai</x:v>
       </x:c>
       <x:c r="B34" s="15" t="str">
         <x:v>tars_a1</x:v>
       </x:c>
       <x:c r="C34" s="15" t="str">
-        <x:v>独立纪录机构</x:v>
+        <x:v>客户官方新闻</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>Most sub-millimeter wire harness assembled by a robot in one hour</x:v>
-      </x:c>
-      <x:c r="E34" s="15" t="str">
-        <x:v>https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="str"/>
+        <x:v>天海电子与它石智航战略合作</x:v>
+      </x:c>
+      <x:c r="E34" s="15" t="e">
+        <x:f>HYPERLINK("https://www.thb.com.cn/content/details_17_319668.html","https://www.thb.com.cn/content/details_17_319668.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thb.com.cn/content/details_17_319668.html, friendlyName=https://www.thb.com.cn/content/details_17_319668.html</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="str">
+        <x:v>2026-06-28</x:v>
+      </x:c>
       <x:c r="G34" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5568,35 +6150,93 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>确认一小时105次亚毫米线束装配纪录</x:v>
+        <x:v>确认汽车线束联合产线与近半年联合攻坚</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="15" t="str">
-        <x:v>src_tars_internal</x:v>
+        <x:v>src_tars_shanghai</x:v>
       </x:c>
       <x:c r="B35" s="15" t="str">
         <x:v>tars_a1</x:v>
       </x:c>
       <x:c r="C35" s="15" t="str">
-        <x:v>内部沟通</x:v>
+        <x:v>政府官方信息</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>它石线束部署与工程问题纪要</x:v>
-      </x:c>
-      <x:c r="E35" s="15" t="str">
-        <x:v>conversation-context:2026-09-15</x:v>
+        <x:v>它石智航产业化闭环</x:v>
+      </x:c>
+      <x:c r="E35" s="15" t="e">
+        <x:f>HYPERLINK("https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html","https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html, friendlyName=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html</x:v>
       </x:c>
       <x:c r="F35" s="15" t="str">
-        <x:v>2026-09-15</x:v>
+        <x:v>2026-07-10</x:v>
       </x:c>
       <x:c r="G35" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H35" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I35" s="15" t="str">
+        <x:v>披露安波福百台计划、33类场景、46工位和DexHand</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="42" customHeight="1">
+      <x:c r="A36" s="15" t="str">
+        <x:v>src_tars_guinness</x:v>
+      </x:c>
+      <x:c r="B36" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="str">
+        <x:v>独立纪录机构</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="str">
+        <x:v>Most sub-millimeter wire harness assembled by a robot in one hour</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="e">
+        <x:f>HYPERLINK("https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour","https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour, friendlyName=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="str"/>
+      <x:c r="G36" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H36" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I36" s="15" t="str">
+        <x:v>确认一小时105次亚毫米线束装配纪录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="42" customHeight="1">
+      <x:c r="A37" s="15" t="str">
+        <x:v>src_tars_internal</x:v>
+      </x:c>
+      <x:c r="B37" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="str">
+        <x:v>内部沟通</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="str">
+        <x:v>它石线束部署与工程问题纪要</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="str">
+        <x:v>conversation-context:2026-09-15</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H37" s="15" t="str">
         <x:v>待核验</x:v>
       </x:c>
-      <x:c r="I35" s="15" t="str">
+      <x:c r="I37" s="15" t="str">
         <x:v>反馈百台部署尚未达到要求并存在臂展、工装耗材、夹爪和MES依赖问题</x:v>
       </x:c>
     </x:row>
@@ -5606,7 +6246,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a5ac16dabe9421a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b3be9ef54844195"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/outputs/机器人本体产品主表.xlsx
+++ b/outputs/机器人本体产品主表.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R3ed96af3fcb64d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="型号图示" sheetId="2" r:id="Ra0efeb1d15634d72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="3" r:id="R309e999abf524a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="4" r:id="Rda6d8609b6234339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="5" r:id="Rc18e434436c242e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="6" r:id="R8576dac86e3841f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策摘要" sheetId="1" r:id="R0aa2ed9f26844519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="型号图示" sheetId="2" r:id="R9665de49860c4e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="场景评分" sheetId="3" r:id="Re7cca890e1ca4a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="参数主表" sheetId="4" r:id="Rcda07856eb204325"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="问题清单" sheetId="5" r:id="R45bc5f5aea8e4425"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源证据" sheetId="6" r:id="Re4fc46698c7f4191"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -275,13 +275,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="bac3d4ac-6310-4050-9783-14cfdba677ae"/>
+        <xdr:cNvPr id="1" name="03b4268d-ac6b-4f66-a807-5dbf59272491"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R66cdb46197e146f7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R4ac1393e09d9472a"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -302,13 +302,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="f150938f-c0ce-49a7-866c-0ced09993435"/>
+        <xdr:cNvPr id="2" name="73a47158-f626-4f66-b0b0-622addffe156"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R06cb6e2fe5f34865"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R225ddbee07054bad"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -329,13 +329,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="b014cd1a-00ce-4f13-bdf2-b331697cc429"/>
+        <xdr:cNvPr id="3" name="cc737262-bb31-4303-82be-54f38dab873e"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R7ee2b1508e5f40aa"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rc97c8ba56204483f"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -356,13 +356,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="6ea4bc63-c241-40a2-a958-92d82d4122c2"/>
+        <xdr:cNvPr id="4" name="cb930666-83ea-4fa1-96d9-d6059e82f4df"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2d0314bcdd0a49d0"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R92eb2ecda0684980"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -383,13 +383,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="64a8a201-4279-4c15-b819-f08d78405f5e"/>
+        <xdr:cNvPr id="5" name="3b31aacf-a529-409a-8ce2-49904cff6cf1"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R032b736719cc4d96"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0081b5770f474f99"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -410,13 +410,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="d56e322e-82f1-47d4-bb80-c94e1043b0e7"/>
+        <xdr:cNvPr id="6" name="6b1ff8aa-ada8-4c98-9d33-4d320d079ecb"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R6b544f7a2b3048f9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R34b28396bd774e10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -437,13 +437,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="576a465f-5405-4978-beec-4e5548e5b1aa"/>
+        <xdr:cNvPr id="7" name="412ae72b-9d2a-4209-9541-84539f065766"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R07a47e47521b447a"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R514e13dab62142d4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -464,13 +464,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="8a13efc3-8166-4539-8085-0c43ca22eefc"/>
+        <xdr:cNvPr id="8" name="1fc1774b-3b5c-4533-929d-5fca74bc5a4d"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R0e9fff79102340e8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra4280c070b204449"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -491,13 +491,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="3eb2d835-326f-4a45-951f-22b66f5a91d8"/>
+        <xdr:cNvPr id="9" name="2ad9e88f-f344-4690-bc83-eb0af9774690"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R1c32660de22244be"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R90b08f748ee84fb4"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -518,13 +518,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="e84268cf-7b5c-4f24-80c7-19c313984720"/>
+        <xdr:cNvPr id="10" name="015b1c84-7b84-47ec-9937-950489cb68b0"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rabef248c63fd4c3f"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ra8db886c670a47d9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -545,13 +545,13 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="32a03535-4485-4296-a516-8190d9315295"/>
+        <xdr:cNvPr id="11" name="7f1d90a2-67b7-4e30-bc84-4beda8044c36"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R3dec1176d8b5473d"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2306d71898134d48"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -572,13 +572,40 @@
     <xdr:ext cx="2333625" cy="1809750"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="5475ec6d-a94e-476b-a43e-aab0ba7284a0"/>
+        <xdr:cNvPr id="12" name="b4340986-ee25-441c-ba15-75587654d235"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R71706e1d61cf4963"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R2eabf397051144f7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2333625" cy="1809750"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="3e9f5014-a14d-4e78-a24a-46419bea01a8"/>
+        <xdr:cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R9a8bb8bfafa64c26"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -593,7 +620,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenarioScores" displayName="ScenarioScores" ref="A6:M23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ScenarioScores" displayName="ScenarioScores" ref="A6:M24" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="13">
     <x:tableColumn id="1" name="厂商"/>
     <x:tableColumn id="2" name="型号"/>
@@ -614,7 +641,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RobotMasterData" displayName="RobotMasterData" ref="A3:AK20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="RobotMasterData" displayName="RobotMasterData" ref="A3:AK21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="37">
     <x:tableColumn id="1" name="model_id"/>
     <x:tableColumn id="2" name="vendor"/>
@@ -659,7 +686,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SupplierQuestions" displayName="SupplierQuestions" ref="A3:J35" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SupplierQuestions" displayName="SupplierQuestions" ref="A3:J42" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="question_id"/>
     <x:tableColumn id="2" name="vendor"/>
@@ -677,7 +704,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I37" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EvidenceSources" displayName="EvidenceSources" ref="A3:I41" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="source_id"/>
     <x:tableColumn id="2" name="model_id"/>
@@ -1038,22 +1065,22 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>Boston Dynamics</x:v>
+        <x:v>千寻智能</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>Atlas</x:v>
+        <x:v>Moz1 Pro</x:v>
       </x:c>
       <x:c r="D8" s="16" t="n">
-        <x:v>3.85</x:v>
+        <x:v>3.925</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G8" s="15" t="str">
-        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
+        <x:v>SDK明确开放vx/vy/wz三自由度底盘速度并支持ROS2/Python；公开SDK未开放力矩和末端力控且Pro专属手册与工业证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32" customHeight="1">
@@ -1061,13 +1088,13 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>Figure AI</x:v>
+        <x:v>Boston Dynamics</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>Figure 03</x:v>
+        <x:v>Atlas</x:v>
       </x:c>
       <x:c r="D9" s="16" t="n">
-        <x:v>3.8000000000000003</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>待实测</x:v>
@@ -1076,7 +1103,7 @@
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G9" s="15" t="str">
-        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
+        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32" customHeight="1">
@@ -1084,22 +1111,22 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>Figure AI</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>D1 擎骏系列</x:v>
+        <x:v>Figure 03</x:v>
       </x:c>
       <x:c r="D10" s="16" t="n">
-        <x:v>3.8</x:v>
+        <x:v>3.8000000000000003</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F10" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
+        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="32" customHeight="1">
@@ -1107,22 +1134,22 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>它石智航</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>TARS A1</x:v>
+        <x:v>D1 擎骏系列</x:v>
       </x:c>
       <x:c r="D11" s="16" t="n">
-        <x:v>3.6500000000000004</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="F11" s="15" t="str">
         <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
+        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="32" customHeight="1">
@@ -1130,22 +1157,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>逐际动力</x:v>
+        <x:v>它石智航</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>LimX Oli EDU</x:v>
+        <x:v>TARS A1</x:v>
       </x:c>
       <x:c r="D12" s="16" t="n">
-        <x:v>3.3499999999999996</x:v>
+        <x:v>3.6500000000000004</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="F12" s="15" t="str">
-        <x:v>补齐资料后再评估</x:v>
+        <x:v>条件 POC</x:v>
       </x:c>
       <x:c r="G12" s="15" t="str">
-        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
+        <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="32" customHeight="1">
@@ -1153,22 +1180,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
-        <x:v>星尘</x:v>
+        <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Astribot T1</x:v>
+        <x:v>LimX Oli EDU</x:v>
       </x:c>
       <x:c r="D13" s="16" t="n">
-        <x:v>3.2</x:v>
+        <x:v>3.3499999999999996</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str">
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G13" s="15" t="str">
-        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
+        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="32" customHeight="1">
@@ -1176,10 +1203,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>逐际动力</x:v>
+        <x:v>星尘</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>TRON 2 双臂形态</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="D14" s="16" t="n">
         <x:v>3.2</x:v>
@@ -1191,7 +1218,7 @@
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G14" s="15" t="str">
-        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
+        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="32" customHeight="1">
@@ -1199,13 +1226,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>Tesla</x:v>
+        <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Optimus</x:v>
+        <x:v>TRON 2 双臂形态</x:v>
       </x:c>
       <x:c r="D15" s="16" t="n">
-        <x:v>2.8000000000000003</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
         <x:v>待确认</x:v>
@@ -1214,7 +1241,7 @@
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G15" s="15" t="str">
-        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
+        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="32" customHeight="1">
@@ -1222,22 +1249,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>Tesla</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Unitree G1-D 旗舰版</x:v>
+        <x:v>Optimus</x:v>
       </x:c>
       <x:c r="D16" s="16" t="n">
-        <x:v>2.3</x:v>
+        <x:v>2.8000000000000003</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str">
-        <x:v>不进入布线 POC</x:v>
+        <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="G16" s="15" t="str">
-        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
+        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="32" customHeight="1">
@@ -1245,13 +1272,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>宇树</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>JUNO2-SD 龙骏系列</x:v>
+        <x:v>Unitree G1-D 旗舰版</x:v>
       </x:c>
       <x:c r="D17" s="16" t="n">
-        <x:v>2.15</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
         <x:v>不通过</x:v>
@@ -1260,7 +1287,7 @@
         <x:v>不进入布线 POC</x:v>
       </x:c>
       <x:c r="G17" s="15" t="str">
-        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
+        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="32" customHeight="1">
@@ -1268,13 +1295,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>Unitree G1-D 通用版</x:v>
+        <x:v>JUNO2-SD 龙骏系列</x:v>
       </x:c>
       <x:c r="D18" s="16" t="n">
-        <x:v>2.05</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
         <x:v>不通过</x:v>
@@ -1283,7 +1310,7 @@
         <x:v>不进入布线 POC</x:v>
       </x:c>
       <x:c r="G18" s="15" t="str">
-        <x:v>官方参数未提供主动移动底盘</x:v>
+        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="32" customHeight="1">
@@ -1291,13 +1318,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>宇树</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>JUNO1-P 智骏系列</x:v>
+        <x:v>Unitree G1-D 通用版</x:v>
       </x:c>
       <x:c r="D19" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
         <x:v>不通过</x:v>
@@ -1306,7 +1333,7 @@
         <x:v>不进入布线 POC</x:v>
       </x:c>
       <x:c r="G19" s="15" t="str">
-        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
+        <x:v>官方参数未提供主动移动底盘</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="32" customHeight="1">
@@ -1317,10 +1344,10 @@
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>L1 灵骏系列</x:v>
+        <x:v>JUNO1-P 智骏系列</x:v>
       </x:c>
       <x:c r="D20" s="16" t="n">
-        <x:v>1.85</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
         <x:v>不通过</x:v>
@@ -1329,27 +1356,50 @@
         <x:v>不进入布线 POC</x:v>
       </x:c>
       <x:c r="G20" s="15" t="str">
+        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="32" customHeight="1">
+      <x:c r="A21" s="15" t="n">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="str">
+        <x:v>智动力</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="str">
+        <x:v>L1 灵骏系列</x:v>
+      </x:c>
+      <x:c r="D21" s="16" t="n">
+        <x:v>1.85</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="str">
+        <x:v>不通过</x:v>
+      </x:c>
+      <x:c r="F21" s="15" t="str">
+        <x:v>不进入布线 POC</x:v>
+      </x:c>
+      <x:c r="G21" s="15" t="str">
         <x:v>差速底盘且负载、臂展和躯干能力较弱</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="32" customHeight="1">
-      <x:c r="A22" s="19" t="str">
+    <x:row r="23" ht="32" customHeight="1">
+      <x:c r="A23" s="19" t="str">
         <x:v>说明：综合分不能越过横移硬门槛和供货资格。双足侧步不等同工业蟹行；Atlas、Figure、Optimus 的采购与SDK开放性需单独判断。</x:v>
       </x:c>
-      <x:c r="B22" s="19"/>
-      <x:c r="C22" s="19"/>
-      <x:c r="D22" s="19"/>
-      <x:c r="E22" s="19"/>
-      <x:c r="F22" s="19"/>
-      <x:c r="G22" s="19"/>
+      <x:c r="B23" s="19"/>
+      <x:c r="C23" s="19"/>
+      <x:c r="D23" s="19"/>
+      <x:c r="E23" s="19"/>
+      <x:c r="F23" s="19"/>
+      <x:c r="G23" s="19"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:G1"/>
     <x:mergeCell ref="A3:G3"/>
-    <x:mergeCell ref="A22:G22"/>
+    <x:mergeCell ref="A23:G23"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D6:D20">
+  <x:conditionalFormatting sqref="D6:D21">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -1361,7 +1411,7 @@
       </x:colorScale>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="E6:E20">
+  <x:conditionalFormatting sqref="E6:E21">
     <x:cfRule type="cellIs" dxfId="0" priority="2">
       <x:formula>"不通过"</x:formula>
     </x:cfRule>
@@ -1457,10 +1507,10 @@
         <x:v>AgiBot 精灵G2</x:v>
       </x:c>
       <x:c r="C4" s="25" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="E4" s="25" t="str">
         <x:v>Astribot T1</x:v>
-      </x:c>
-      <x:c r="E4" s="25" t="str">
-        <x:v>D1 擎骏系列</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1"/>
@@ -1478,22 +1528,22 @@
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="C15" s="27" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="E15" s="27" t="str">
         <x:v>官方网站</x:v>
-      </x:c>
-      <x:c r="E15" s="27" t="str">
-        <x:v>供应商PDF</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1"/>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="25" t="str">
+        <x:v>D1 擎骏系列</x:v>
+      </x:c>
+      <x:c r="C17" s="25" t="str">
         <x:v>JUNO2-SD 龙骏系列</x:v>
       </x:c>
-      <x:c r="C17" s="25" t="str">
+      <x:c r="E17" s="25" t="str">
         <x:v>Unitree G1-D 旗舰版</x:v>
-      </x:c>
-      <x:c r="E17" s="25" t="str">
-        <x:v>Atlas</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1"/>
@@ -1511,7 +1561,7 @@
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="C28" s="27" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="E28" s="27" t="str">
         <x:v>官方网站</x:v>
@@ -1520,13 +1570,13 @@
     <x:row r="29" ht="18" customHeight="1"/>
     <x:row r="30" ht="18" customHeight="1">
       <x:c r="A30" s="25" t="str">
+        <x:v>Atlas</x:v>
+      </x:c>
+      <x:c r="C30" s="25" t="str">
         <x:v>Figure 03</x:v>
       </x:c>
-      <x:c r="C30" s="25" t="str">
+      <x:c r="E30" s="25" t="str">
         <x:v>Optimus</x:v>
-      </x:c>
-      <x:c r="E30" s="25" t="str">
-        <x:v>LimX Oli EDU</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="18" customHeight="1"/>
@@ -1544,22 +1594,22 @@
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="C41" s="27" t="str">
+        <x:v>官方网站</x:v>
+      </x:c>
+      <x:c r="E41" s="27" t="str">
         <x:v>第三方型号图库</x:v>
-      </x:c>
-      <x:c r="E41" s="27" t="str">
-        <x:v>经销商产品图</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="18" customHeight="1"/>
     <x:row r="43" ht="18" customHeight="1">
       <x:c r="A43" s="25" t="str">
+        <x:v>LimX Oli EDU</x:v>
+      </x:c>
+      <x:c r="C43" s="25" t="str">
         <x:v>TRON 2 双臂形态</x:v>
       </x:c>
-      <x:c r="C43" s="25" t="str">
+      <x:c r="E43" s="25" t="str">
         <x:v>Galaxea R1 Pro 2026</x:v>
-      </x:c>
-      <x:c r="E43" s="25" t="str">
-        <x:v>TARS A1</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="18" customHeight="1"/>
@@ -1574,23 +1624,33 @@
     <x:row r="53" ht="18" customHeight="1"/>
     <x:row r="54" ht="18" customHeight="1">
       <x:c r="A54" s="27" t="str">
+        <x:v>经销商产品图</x:v>
+      </x:c>
+      <x:c r="C54" s="27" t="str">
         <x:v>第三方型号图库</x:v>
       </x:c>
-      <x:c r="C54" s="27" t="str">
+      <x:c r="E54" s="27" t="str">
         <x:v>官方网站</x:v>
       </x:c>
-      <x:c r="E54" s="27" t="str">
+    </x:row>
+    <x:row r="55" ht="18" customHeight="1"/>
+    <x:row r="56">
+      <x:c r="A56" s="25" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="27" t="str">
         <x:v>政府公开信息</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="18" customHeight="1"/>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc34418df3938428d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41dee1678a364070"/>
 </x:worksheet>
 </file>
 
@@ -1801,111 +1861,111 @@
     </x:row>
     <x:row r="8" ht="30" customHeight="1">
       <x:c r="A8" s="15" t="str">
-        <x:v>星尘</x:v>
+        <x:v>千寻智能</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>Astribot T1</x:v>
+        <x:v>Moz1 Pro</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="E8" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>4.5</x:v>
       </x:c>
       <x:c r="F8" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G8" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H8" s="15" t="n">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="I8" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="J8" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K8" s="16" t="n">
         <x:f>IF(C8&lt;&gt;"是","",SUMPRODUCT(E8:J8,$B$4:$G$4))</x:f>
-        <x:v>3.2</x:v>
+        <x:v>3.925</x:v>
       </x:c>
       <x:c r="L8" s="15" t="str">
         <x:f>IF(C8&lt;&gt;"是","不参与移动本体排名",IF(D8="不通过","不进入布线POC",IF(K8&gt;=4.2,"优先POC",IF(K8&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>补齐资料后再评估</x:v>
+        <x:v>条件POC</x:v>
       </x:c>
       <x:c r="M8" s="15" t="str">
-        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
+        <x:v>SDK明确开放vx/vy/wz三自由度底盘速度并支持ROS2/Python；公开SDK未开放力矩和末端力控且Pro专属手册与工业证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
       <x:c r="A9" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>星尘</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>D1 擎骏系列</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>通过待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="E9" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F9" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G9" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I9" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="J9" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K9" s="16" t="n">
         <x:f>IF(C9&lt;&gt;"是","",SUMPRODUCT(E9:J9,$B$4:$G$4))</x:f>
-        <x:v>3.8</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="L9" s="15" t="str">
         <x:f>IF(C9&lt;&gt;"是","不参与移动本体排名",IF(D9="不通过","不进入布线POC",IF(K9&gt;=4.2,"优先POC",IF(K9&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>条件POC</x:v>
+        <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="M9" s="15" t="str">
-        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
+        <x:v>紧凑轮式底盘但轮系和蟹行能力未公开；绳驱柔性和量产进展较好，精度与SDK量化不足</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>Unitree G1-D 旗舰版</x:v>
+        <x:v>D1 擎骏系列</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>不通过</x:v>
+        <x:v>通过待实测</x:v>
       </x:c>
       <x:c r="E10" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G10" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H10" s="15" t="n">
         <x:v>3</x:v>
@@ -1914,26 +1974,26 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="J10" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K10" s="16" t="n">
         <x:f>IF(C10&lt;&gt;"是","",SUMPRODUCT(E10:J10,$B$4:$G$4))</x:f>
-        <x:v>2.3</x:v>
+        <x:v>3.8</x:v>
       </x:c>
       <x:c r="L10" s="15" t="str">
         <x:f>IF(C10&lt;&gt;"是","不参与移动本体排名",IF(D10="不通过","不进入布线POC",IF(K10&gt;=4.2,"优先POC",IF(K10&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>不进入布线POC</x:v>
+        <x:v>条件POC</x:v>
       </x:c>
       <x:c r="M10" s="15" t="str">
-        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
+        <x:v>四轮四转明确支持蟹行；整机重且精度和力控证据不足</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
       <x:c r="A11" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>宇树</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>JUNO2-SD 龙骏系列</x:v>
+        <x:v>Unitree G1-D 旗舰版</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
         <x:v>是</x:v>
@@ -1951,7 +2011,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="H11" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I11" s="15" t="n">
         <x:v>3</x:v>
@@ -1961,14 +2021,14 @@
       </x:c>
       <x:c r="K11" s="16" t="n">
         <x:f>IF(C11&lt;&gt;"是","",SUMPRODUCT(E11:J11,$B$4:$G$4))</x:f>
-        <x:v>2.15</x:v>
+        <x:v>2.3</x:v>
       </x:c>
       <x:c r="L11" s="15" t="str">
         <x:f>IF(C11&lt;&gt;"是","不参与移动本体排名",IF(D11="不通过","不进入布线POC",IF(K11&gt;=4.2,"优先POC",IF(K11&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>不进入布线POC</x:v>
       </x:c>
       <x:c r="M11" s="15" t="str">
-        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
+        <x:v>差速底盘不能纯横移；更偏数据采集和开发平台</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
@@ -1976,7 +2036,7 @@
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
-        <x:v>JUNO1-P 智骏系列</x:v>
+        <x:v>JUNO2-SD 龙骏系列</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
         <x:v>是</x:v>
@@ -1988,7 +2048,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G12" s="15" t="n">
         <x:v>2</x:v>
@@ -2004,14 +2064,14 @@
       </x:c>
       <x:c r="K12" s="16" t="n">
         <x:f>IF(C12&lt;&gt;"是","",SUMPRODUCT(E12:J12,$B$4:$G$4))</x:f>
-        <x:v>2</x:v>
+        <x:v>2.15</x:v>
       </x:c>
       <x:c r="L12" s="15" t="str">
         <x:f>IF(C12&lt;&gt;"是","不参与移动本体排名",IF(D12="不通过","不进入布线POC",IF(K12&gt;=4.2,"优先POC",IF(K12&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>不进入布线POC</x:v>
       </x:c>
       <x:c r="M12" s="15" t="str">
-        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
+        <x:v>差速底盘为硬伤；重复定位和力控指标未公开</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
@@ -2019,7 +2079,7 @@
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
-        <x:v>L1 灵骏系列</x:v>
+        <x:v>JUNO1-P 智骏系列</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
         <x:v>是</x:v>
@@ -2031,7 +2091,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G13" s="15" t="n">
         <x:v>2</x:v>
@@ -2047,22 +2107,22 @@
       </x:c>
       <x:c r="K13" s="16" t="n">
         <x:f>IF(C13&lt;&gt;"是","",SUMPRODUCT(E13:J13,$B$4:$G$4))</x:f>
-        <x:v>1.85</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L13" s="15" t="str">
         <x:f>IF(C13&lt;&gt;"是","不参与移动本体排名",IF(D13="不通过","不进入布线POC",IF(K13&gt;=4.2,"优先POC",IF(K13&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>不进入布线POC</x:v>
       </x:c>
       <x:c r="M13" s="15" t="str">
-        <x:v>差速底盘且负载、臂展和躯干能力较弱</x:v>
+        <x:v>差速底盘为硬伤；负载和升降能力低于JUNO2</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Unitree G1-D 通用版</x:v>
+        <x:v>L1 灵骏系列</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
         <x:v>是</x:v>
@@ -2071,16 +2131,16 @@
         <x:v>不通过</x:v>
       </x:c>
       <x:c r="E14" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="G14" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H14" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I14" s="15" t="n">
         <x:v>3</x:v>
@@ -2090,88 +2150,89 @@
       </x:c>
       <x:c r="K14" s="16" t="n">
         <x:f>IF(C14&lt;&gt;"是","",SUMPRODUCT(E14:J14,$B$4:$G$4))</x:f>
-        <x:v>2.05</x:v>
+        <x:v>1.85</x:v>
       </x:c>
       <x:c r="L14" s="15" t="str">
         <x:f>IF(C14&lt;&gt;"是","不参与移动本体排名",IF(D14="不通过","不进入布线POC",IF(K14&gt;=4.2,"优先POC",IF(K14&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>不进入布线POC</x:v>
       </x:c>
       <x:c r="M14" s="15" t="str">
-        <x:v>官方参数未提供主动移动底盘</x:v>
+        <x:v>差速底盘且负载、臂展和躯干能力较弱</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
       <x:c r="A15" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>宇树</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>Z1</x:v>
+        <x:v>Unitree G1-D 通用版</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
         <x:v>不通过</x:v>
       </x:c>
       <x:c r="E15" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F15" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G15" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H15" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G15" s="15" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="I15" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="J15" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K15" s="16" t="str">
+      <x:c r="K15" s="16" t="n">
         <x:f>IF(C15&lt;&gt;"是","",SUMPRODUCT(E15:J15,$B$4:$G$4))</x:f>
+        <x:v>2.05</x:v>
       </x:c>
       <x:c r="L15" s="15" t="str">
         <x:f>IF(C15&lt;&gt;"是","不参与移动本体排名",IF(D15="不通过","不进入布线POC",IF(K15&gt;=4.2,"优先POC",IF(K15&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>不参与移动本体排名</x:v>
+        <x:v>不进入布线POC</x:v>
       </x:c>
       <x:c r="M15" s="15" t="str">
-        <x:v>仅有SDK手册且差速底盘；不纳入排名</x:v>
+        <x:v>官方参数未提供主动移动底盘</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
       <x:c r="A16" s="15" t="str">
-        <x:v>天机智能</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>Marvin M6 CCS</x:v>
+        <x:v>Z1</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>待集成</x:v>
+        <x:v>不通过</x:v>
       </x:c>
       <x:c r="E16" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F16" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G16" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H16" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I16" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J16" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K16" s="16" t="str">
         <x:f>IF(C16&lt;&gt;"是","",SUMPRODUCT(E16:J16,$B$4:$G$4))</x:f>
@@ -2181,58 +2242,57 @@
         <x:v>不参与移动本体排名</x:v>
       </x:c>
       <x:c r="M16" s="15" t="str">
-        <x:v>双臂模块不含标准底盘；集成全向底盘后再评估</x:v>
+        <x:v>仅有SDK手册且差速底盘；不纳入排名</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
       <x:c r="A17" s="15" t="str">
-        <x:v>Boston Dynamics</x:v>
+        <x:v>天机智能</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>Atlas</x:v>
+        <x:v>Marvin M6 CCS</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>待集成</x:v>
       </x:c>
       <x:c r="E17" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G17" s="15" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="G17" s="15" t="n">
+      <x:c r="H17" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I17" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H17" s="15" t="n">
+      <x:c r="J17" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="I17" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J17" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="K17" s="16" t="n">
+      <x:c r="K17" s="16" t="str">
         <x:f>IF(C17&lt;&gt;"是","",SUMPRODUCT(E17:J17,$B$4:$G$4))</x:f>
-        <x:v>3.85</x:v>
       </x:c>
       <x:c r="L17" s="15" t="str">
         <x:f>IF(C17&lt;&gt;"是","不参与移动本体排名",IF(D17="不通过","不进入布线POC",IF(K17&gt;=4.2,"优先POC",IF(K17&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>条件POC</x:v>
+        <x:v>不参与移动本体排名</x:v>
       </x:c>
       <x:c r="M17" s="15" t="str">
-        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
+        <x:v>双臂模块不含标准底盘；集成全向底盘后再评估</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
       <x:c r="A18" s="15" t="str">
-        <x:v>Figure AI</x:v>
+        <x:v>Boston Dynamics</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>Figure 03</x:v>
+        <x:v>Atlas</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
         <x:v>是</x:v>
@@ -2247,90 +2307,90 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="G18" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H18" s="15" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="I18" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="J18" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K18" s="16" t="n">
         <x:f>IF(C18&lt;&gt;"是","",SUMPRODUCT(E18:J18,$B$4:$G$4))</x:f>
-        <x:v>3.8000000000000003</x:v>
+        <x:v>3.85</x:v>
       </x:c>
       <x:c r="L18" s="15" t="str">
         <x:f>IF(C18&lt;&gt;"是","不参与移动本体排名",IF(D18="不通过","不进入布线POC",IF(K18&gt;=4.2,"优先POC",IF(K18&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>条件POC</x:v>
       </x:c>
       <x:c r="M18" s="15" t="str">
-        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
+        <x:v>工业可靠性负载和工作空间领先；但双足连续贴线横移、采购与集成开放性待确认</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
       <x:c r="A19" s="15" t="str">
-        <x:v>Tesla</x:v>
+        <x:v>Figure AI</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>Optimus</x:v>
+        <x:v>Figure 03</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="E19" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F19" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G19" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H19" s="15" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="G19" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H19" s="15" t="n">
-        <x:v>3</x:v>
       </x:c>
       <x:c r="I19" s="15" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J19" s="15" t="n">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K19" s="16" t="n">
         <x:f>IF(C19&lt;&gt;"是","",SUMPRODUCT(E19:J19,$B$4:$G$4))</x:f>
-        <x:v>2.8000000000000003</x:v>
+        <x:v>3.8000000000000003</x:v>
       </x:c>
       <x:c r="L19" s="15" t="str">
         <x:f>IF(C19&lt;&gt;"是","不参与移动本体排名",IF(D19="不通过","不进入布线POC",IF(K19&gt;=4.2,"优先POC",IF(K19&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>补齐资料后再评估</x:v>
+        <x:v>条件POC</x:v>
       </x:c>
       <x:c r="M19" s="15" t="str">
-        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
+        <x:v>触觉手和量产设计突出；无公开SDK且双足横移节拍与精度未披露</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
       <x:c r="A20" s="15" t="str">
-        <x:v>逐际动力</x:v>
+        <x:v>Tesla</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>LimX Oli EDU</x:v>
+        <x:v>Optimus</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>待实测</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="E20" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F20" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G20" s="15" t="n">
         <x:v>3</x:v>
@@ -2339,21 +2399,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I20" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J20" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K20" s="16" t="n">
         <x:f>IF(C20&lt;&gt;"是","",SUMPRODUCT(E20:J20,$B$4:$G$4))</x:f>
-        <x:v>3.3499999999999996</x:v>
+        <x:v>2.8000000000000003</x:v>
       </x:c>
       <x:c r="L20" s="15" t="str">
         <x:f>IF(C20&lt;&gt;"是","不参与移动本体排名",IF(D20="不通过","不进入布线POC",IF(K20&gt;=4.2,"优先POC",IF(K20&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="M20" s="15" t="str">
-        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
+        <x:v>官方工程参数和外部集成方式严重不足；暂不具备正式采购比较条件</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
@@ -2361,19 +2421,19 @@
         <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="B21" s="15" t="str">
-        <x:v>TRON 2 双臂形态</x:v>
+        <x:v>LimX Oli EDU</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>待实测</x:v>
       </x:c>
       <x:c r="E21" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="F21" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G21" s="15" t="n">
         <x:v>3</x:v>
@@ -2389,99 +2449,142 @@
       </x:c>
       <x:c r="K21" s="16" t="n">
         <x:f>IF(C21&lt;&gt;"是","",SUMPRODUCT(E21:J21,$B$4:$G$4))</x:f>
-        <x:v>3.2</x:v>
+        <x:v>3.3499999999999996</x:v>
       </x:c>
       <x:c r="L21" s="15" t="str">
         <x:f>IF(C21&lt;&gt;"是","不参与移动本体排名",IF(D21="不通过","不进入布线POC",IF(K21&gt;=4.2,"优先POC",IF(K21&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="M21" s="15" t="str">
-        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
+        <x:v>开放开发工具链和全尺寸工作空间较好；双足贴线横移、精度和工业认证需验证</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="15" t="str">
-        <x:v>星海图</x:v>
+        <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="B22" s="15" t="str">
-        <x:v>Galaxea R1 Pro 2026</x:v>
+        <x:v>TRON 2 双臂形态</x:v>
       </x:c>
       <x:c r="C22" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>通过</x:v>
+        <x:v>待确认</x:v>
       </x:c>
       <x:c r="E22" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F22" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G22" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H22" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="I22" s="15" t="n">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J22" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K22" s="16" t="n">
         <x:f>IF(C22&lt;&gt;"是","",SUMPRODUCT(E22:J22,$B$4:$G$4))</x:f>
-        <x:v>4.1</x:v>
+        <x:v>3.2</x:v>
       </x:c>
       <x:c r="L22" s="15" t="str">
         <x:f>IF(C22&lt;&gt;"是","不参与移动本体排名",IF(D22="不通过","不进入布线POC",IF(K22&gt;=4.2,"优先POC",IF(K22&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
-        <x:v>条件POC</x:v>
+        <x:v>补齐资料后再评估</x:v>
       </x:c>
       <x:c r="M22" s="15" t="str">
-        <x:v>三舵轮全向和工作空间契合；重复精度0.5mm且机械臂无制动器是主要风险</x:v>
+        <x:v>接口开放且多形态；四向移动是否包含保持朝向纯横移需要供应商确认</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
       <x:c r="A23" s="15" t="str">
-        <x:v>它石智航</x:v>
+        <x:v>星海图</x:v>
       </x:c>
       <x:c r="B23" s="15" t="str">
-        <x:v>TARS A1</x:v>
+        <x:v>Galaxea R1 Pro 2026</x:v>
       </x:c>
       <x:c r="C23" s="15" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>待确认</x:v>
+        <x:v>通过</x:v>
       </x:c>
       <x:c r="E23" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G23" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H23" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F23" s="15" t="n">
+      <x:c r="I23" s="15" t="n">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="G23" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H23" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I23" s="15" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="J23" s="15" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K23" s="16" t="n">
         <x:f>IF(C23&lt;&gt;"是","",SUMPRODUCT(E23:J23,$B$4:$G$4))</x:f>
-        <x:v>3.6500000000000004</x:v>
+        <x:v>4.1</x:v>
       </x:c>
       <x:c r="L23" s="15" t="str">
         <x:f>IF(C23&lt;&gt;"是","不参与移动本体排名",IF(D23="不通过","不进入布线POC",IF(K23&gt;=4.2,"优先POC",IF(K23&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
         <x:v>条件POC</x:v>
       </x:c>
       <x:c r="M23" s="15" t="str">
+        <x:v>三舵轮全向和工作空间契合；重复精度0.5mm且机械臂无制动器是主要风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="30" customHeight="1">
+      <x:c r="A24" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="B24" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="C24" s="15" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D24" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G24" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H24" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I24" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K24" s="16" t="n">
+        <x:f>IF(C24&lt;&gt;"是","",SUMPRODUCT(E24:J24,$B$4:$G$4))</x:f>
+        <x:v>3.6500000000000004</x:v>
+      </x:c>
+      <x:c r="L24" s="15" t="str">
+        <x:f>IF(C24&lt;&gt;"是","不参与移动本体排名",IF(D24="不通过","不进入布线POC",IF(K24&gt;=4.2,"优先POC",IF(K24&gt;=3.5,"条件POC","补齐资料后再评估"))))</x:f>
+        <x:v>条件POC</x:v>
+      </x:c>
+      <x:c r="M24" s="15" t="str">
         <x:v>线束任务证据最强；底盘轮型接口参数和规模部署验收数据未公开且内部反馈仍有差距</x:v>
       </x:c>
     </x:row>
@@ -2489,7 +2592,7 @@
   <x:mergeCells>
     <x:mergeCell ref="A1:M1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="K7:K23">
+  <x:conditionalFormatting sqref="K7:K24">
     <x:cfRule type="colorScale" priority="1">
       <x:colorScale>
         <x:cfvo type="min"/>
@@ -2501,7 +2604,7 @@
       </x:colorScale>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="D7:D23">
+  <x:conditionalFormatting sqref="D7:D24">
     <x:cfRule type="cellIs" dxfId="2" priority="2">
       <x:formula>"不通过"</x:formula>
     </x:cfRule>
@@ -2510,14 +2613,14 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation operator="between" showErrorMessage="1" errorTitle="评分超范围" error="请输入 0 到 5 的整数。" sqref="E7:J23">
+    <x:dataValidation operator="between" showErrorMessage="1" errorTitle="评分超范围" error="请输入 0 到 5 的整数。" sqref="E7:J24">
       <x:formula1>0</x:formula1>
       <x:formula2>5</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbe4832f0df04260"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6bd5840663774cf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2845,46 +2948,58 @@
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
-        <x:v>astribot_t1</x:v>
+        <x:v>spirit_moz1_pro</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
-        <x:v>星尘</x:v>
+        <x:v>千寻智能</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
-        <x:v>Astribot T1</x:v>
+        <x:v>Moz1 Pro</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
-        <x:v>移动双臂本体</x:v>
+        <x:v>轮式双臂人形本体</x:v>
       </x:c>
       <x:c r="E5" s="15" t="str">
-        <x:v>量产/发货</x:v>
+        <x:v>供应商发布/待交付验证</x:v>
       </x:c>
       <x:c r="F5" s="15" t="n">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G5" s="15"/>
-      <x:c r="H5" s="15"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="I5" s="15"/>
-      <x:c r="J5" s="15"/>
+      <x:c r="J5" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="K5" s="15" t="str">
-        <x:v>紧凑轮式底盘（轮系未公开）</x:v>
+        <x:v>四轮全向移动平台（SDK开放vx/vy/wz）</x:v>
       </x:c>
       <x:c r="L5" s="15" t="str">
-        <x:v>待确认</x:v>
-      </x:c>
-      <x:c r="M5" s="15"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M5" s="15" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="N5" s="15" t="n">
-        <x:v>1550</x:v>
+        <x:v>1500</x:v>
       </x:c>
       <x:c r="O5" s="15" t="n">
-        <x:v>1550</x:v>
-      </x:c>
-      <x:c r="P5" s="15"/>
-      <x:c r="Q5" s="15"/>
-      <x:c r="R5" s="15" t="n">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="S5" s="15"/>
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="P5" s="15" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="Q5" s="15" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="R5" s="15"/>
+      <x:c r="S5" s="15" t="n">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="T5" s="15"/>
       <x:c r="U5" s="15" t="n">
         <x:v>5</x:v>
@@ -2893,125 +3008,115 @@
       <x:c r="W5" s="15"/>
       <x:c r="X5" s="15"/>
       <x:c r="Y5" s="15" t="str"/>
-      <x:c r="Z5" s="15"/>
+      <x:c r="Z5" s="15" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
       <x:c r="AA5" s="15"/>
       <x:c r="AB5" s="15" t="str">
-        <x:v>绳驱柔性；碰撞卸力（控制与传感指标未公开）</x:v>
+        <x:v>全关节力矩传感；内部关节阻抗和碰撞检测；公开SDK未开放力矩或末端力控制</x:v>
       </x:c>
       <x:c r="AC5" s="15"/>
       <x:c r="AD5" s="15"/>
-      <x:c r="AE5" s="15" t="str"/>
+      <x:c r="AE5" s="15" t="str">
+        <x:v>NVIDIA Thor一体化平台</x:v>
+      </x:c>
       <x:c r="AF5" s="15" t="str"/>
       <x:c r="AG5" s="15" t="str"/>
       <x:c r="AH5" s="15" t="str">
-        <x:v>支持多样末端配置与更换</x:v>
+        <x:v>自研二指夹爪；兼容第三方末端</x:v>
       </x:c>
       <x:c r="AI5" s="15" t="str">
-        <x:v>末端与算力背包扩展接口；自动回充；快捷换电（协议未公开）</x:v>
+        <x:v>ROS2 Humble；Python3.10+；最高120Hz；CAN；RS485；2.5GbE；USB；HDMI</x:v>
       </x:c>
       <x:c r="AJ5" s="15" t="str">
-        <x:v>官网+政府及媒体报道</x:v>
+        <x:v>供应商彩页+官方在线手册（在线手册主体为旧款Moz1）</x:v>
       </x:c>
       <x:c r="AK5" s="15" t="str">
-        <x:v>8.99万元起；底盘是否全向、移动与操作精度、SDK协议、续航和工业认证未公开</x:v>
+        <x:v>理论最高速度1.5m/s；48V 40Ah且充电约1.5h；Pro重量和单次续航未披露；彩页自动回充/无线充电与旧款手册手动插线存在版本差异</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="15" t="str">
-        <x:v>zdl_d1</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>智动力</x:v>
+        <x:v>星尘</x:v>
       </x:c>
       <x:c r="C6" s="15" t="str">
-        <x:v>D1 擎骏系列</x:v>
+        <x:v>Astribot T1</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
         <x:v>移动双臂本体</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
-        <x:v>供应商产品资料</x:v>
+        <x:v>量产/发货</x:v>
       </x:c>
       <x:c r="F6" s="15" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="G6" s="15" t="n">
-        <x:v>7</x:v>
-      </x:c>
+      <x:c r="G6" s="15"/>
       <x:c r="H6" s="15"/>
       <x:c r="I6" s="15"/>
       <x:c r="J6" s="15"/>
       <x:c r="K6" s="15" t="str">
-        <x:v>四轮四转底盘</x:v>
+        <x:v>紧凑轮式底盘（轮系未公开）</x:v>
       </x:c>
       <x:c r="L6" s="15" t="str">
-        <x:v>是</x:v>
-      </x:c>
-      <x:c r="M6" s="15" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="M6" s="15"/>
       <x:c r="N6" s="15" t="n">
-        <x:v>1850</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="O6" s="15" t="n">
-        <x:v>1850</x:v>
+        <x:v>1550</x:v>
       </x:c>
       <x:c r="P6" s="15"/>
       <x:c r="Q6" s="15"/>
       <x:c r="R6" s="15" t="n">
-        <x:v>300</x:v>
-      </x:c>
-      <x:c r="S6" s="15" t="n">
-        <x:v>1000</x:v>
-      </x:c>
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="S6" s="15"/>
       <x:c r="T6" s="15"/>
       <x:c r="U6" s="15" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="V6" s="15" t="n">
-        <x:v>25</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="V6" s="15"/>
       <x:c r="W6" s="15"/>
       <x:c r="X6" s="15"/>
       <x:c r="Y6" s="15" t="str"/>
       <x:c r="Z6" s="15"/>
       <x:c r="AA6" s="15"/>
       <x:c r="AB6" s="15" t="str">
-        <x:v>全力控双臂，缺少量化指标</x:v>
+        <x:v>绳驱柔性；碰撞卸力（控制与传感指标未公开）</x:v>
       </x:c>
       <x:c r="AC6" s="15"/>
       <x:c r="AD6" s="15"/>
-      <x:c r="AE6" s="15" t="str">
-        <x:v>AGX Orin 200 TOPS；可选275 TOPS</x:v>
-      </x:c>
-      <x:c r="AF6" s="15" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="AG6" s="15" t="str">
-        <x:v>IP50</x:v>
-      </x:c>
+      <x:c r="AE6" s="15" t="str"/>
+      <x:c r="AF6" s="15" t="str"/>
+      <x:c r="AG6" s="15" t="str"/>
       <x:c r="AH6" s="15" t="str">
-        <x:v>七自由度灵巧手或夹爪</x:v>
+        <x:v>支持多样末端配置与更换</x:v>
       </x:c>
       <x:c r="AI6" s="15" t="str">
-        <x:v>C++；ROS；Python；EtherCAT×2；CAN×2；UART×6</x:v>
+        <x:v>末端与算力背包扩展接口；自动回充；快捷换电（协议未公开）</x:v>
       </x:c>
       <x:c r="AJ6" s="15" t="str">
-        <x:v>供应商产品册</x:v>
+        <x:v>官网+政府及媒体报道</x:v>
       </x:c>
       <x:c r="AK6" s="15" t="str">
-        <x:v>1000mm升降；额定承载200kg；体积和重量较大</x:v>
+        <x:v>8.99万元起；底盘是否全向、移动与操作精度、SDK协议、续航和工业认证未公开</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="15" t="str">
-        <x:v>zdl_juno2</x:v>
+        <x:v>zdl_d1</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="C7" s="15" t="str">
-        <x:v>JUNO2-SD 龙骏系列</x:v>
+        <x:v>D1 擎骏系列</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
         <x:v>移动双臂本体</x:v>
@@ -3020,47 +3125,43 @@
         <x:v>供应商产品资料</x:v>
       </x:c>
       <x:c r="F7" s="15" t="n">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H7" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
+      <x:c r="H7" s="15"/>
       <x:c r="I7" s="15"/>
       <x:c r="J7" s="15"/>
       <x:c r="K7" s="15" t="str">
-        <x:v>双差速线控底盘</x:v>
+        <x:v>四轮四转底盘</x:v>
       </x:c>
       <x:c r="L7" s="15" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="M7" s="15" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="N7" s="15" t="n">
-        <x:v>1780</x:v>
+        <x:v>1850</x:v>
       </x:c>
       <x:c r="O7" s="15" t="n">
-        <x:v>1780</x:v>
-      </x:c>
-      <x:c r="P7" s="15" t="n">
-        <x:v>600</x:v>
-      </x:c>
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="P7" s="15"/>
       <x:c r="Q7" s="15"/>
       <x:c r="R7" s="15" t="n">
-        <x:v>160</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="S7" s="15" t="n">
-        <x:v>800</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="T7" s="15"/>
       <x:c r="U7" s="15" t="n">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="V7" s="15" t="n">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="W7" s="15"/>
       <x:c r="X7" s="15"/>
@@ -3068,18 +3169,18 @@
       <x:c r="Z7" s="15"/>
       <x:c r="AA7" s="15"/>
       <x:c r="AB7" s="15" t="str">
-        <x:v>未公开</x:v>
+        <x:v>全力控双臂，缺少量化指标</x:v>
       </x:c>
       <x:c r="AC7" s="15"/>
       <x:c r="AD7" s="15"/>
       <x:c r="AE7" s="15" t="str">
-        <x:v>Jetson Orin NX 157 TOPS；可选275 TOPS</x:v>
+        <x:v>AGX Orin 200 TOPS；可选275 TOPS</x:v>
       </x:c>
       <x:c r="AF7" s="15" t="str">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AG7" s="15" t="str">
-        <x:v>IP40</x:v>
+        <x:v>IP50</x:v>
       </x:c>
       <x:c r="AH7" s="15" t="str">
         <x:v>七自由度灵巧手或夹爪</x:v>
@@ -3091,18 +3192,18 @@
         <x:v>供应商产品册</x:v>
       </x:c>
       <x:c r="AK7" s="15" t="str">
-        <x:v>550mm升降；差速底盘不支持保持朝向横移</x:v>
+        <x:v>1000mm升降；额定承载200kg；体积和重量较大</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="15" t="str">
-        <x:v>zdl_juno1</x:v>
+        <x:v>zdl_juno2</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="C8" s="15" t="str">
-        <x:v>JUNO1-P 智骏系列</x:v>
+        <x:v>JUNO2-SD 龙骏系列</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
         <x:v>移动双臂本体</x:v>
@@ -3111,13 +3212,13 @@
         <x:v>供应商产品资料</x:v>
       </x:c>
       <x:c r="F8" s="15" t="n">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="G8" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H8" s="15" t="n">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I8" s="15"/>
       <x:c r="J8" s="15"/>
@@ -3131,26 +3232,28 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="N8" s="15" t="n">
-        <x:v>1750</x:v>
+        <x:v>1780</x:v>
       </x:c>
       <x:c r="O8" s="15" t="n">
-        <x:v>1750</x:v>
+        <x:v>1780</x:v>
       </x:c>
       <x:c r="P8" s="15" t="n">
         <x:v>600</x:v>
       </x:c>
       <x:c r="Q8" s="15"/>
       <x:c r="R8" s="15" t="n">
-        <x:v>120</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="S8" s="15" t="n">
         <x:v>800</x:v>
       </x:c>
       <x:c r="T8" s="15"/>
       <x:c r="U8" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="V8" s="15"/>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="V8" s="15" t="n">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="W8" s="15"/>
       <x:c r="X8" s="15"/>
       <x:c r="Y8" s="15" t="str"/>
@@ -3162,10 +3265,10 @@
       <x:c r="AC8" s="15"/>
       <x:c r="AD8" s="15"/>
       <x:c r="AE8" s="15" t="str">
-        <x:v>Jetson Orin NX 157 TOPS</x:v>
+        <x:v>Jetson Orin NX 157 TOPS；可选275 TOPS</x:v>
       </x:c>
       <x:c r="AF8" s="15" t="str">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AG8" s="15" t="str">
         <x:v>IP40</x:v>
@@ -3174,44 +3277,44 @@
         <x:v>七自由度灵巧手或夹爪</x:v>
       </x:c>
       <x:c r="AI8" s="15" t="str">
-        <x:v>C++；ROS；Python</x:v>
+        <x:v>C++；ROS；Python；EtherCAT×2；CAN×2；UART×6</x:v>
       </x:c>
       <x:c r="AJ8" s="15" t="str">
         <x:v>供应商产品册</x:v>
       </x:c>
       <x:c r="AK8" s="15" t="str">
-        <x:v>300mm升降；负载包含末端</x:v>
+        <x:v>550mm升降；差速底盘不支持保持朝向横移</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="15" t="str">
-        <x:v>zdl_l1</x:v>
+        <x:v>zdl_juno1</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="C9" s="15" t="str">
-        <x:v>L1 灵骏系列</x:v>
+        <x:v>JUNO1-P 智骏系列</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>轻量移动双臂本体</x:v>
+        <x:v>移动双臂本体</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>供应商产品资料</x:v>
       </x:c>
       <x:c r="F9" s="15" t="n">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G9" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H9" s="15" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I9" s="15"/>
       <x:c r="J9" s="15"/>
       <x:c r="K9" s="15" t="str">
-        <x:v>差速轮式底盘</x:v>
+        <x:v>双差速线控底盘</x:v>
       </x:c>
       <x:c r="L9" s="15" t="str">
         <x:v>否</x:v>
@@ -3220,24 +3323,24 @@
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="N9" s="15" t="n">
-        <x:v>1280</x:v>
+        <x:v>1750</x:v>
       </x:c>
       <x:c r="O9" s="15" t="n">
-        <x:v>1280</x:v>
+        <x:v>1750</x:v>
       </x:c>
       <x:c r="P9" s="15" t="n">
-        <x:v>580</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="Q9" s="15"/>
       <x:c r="R9" s="15" t="n">
-        <x:v>40</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="S9" s="15" t="n">
-        <x:v>600</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="T9" s="15"/>
       <x:c r="U9" s="15" t="n">
-        <x:v>1.5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V9" s="15"/>
       <x:c r="W9" s="15"/>
@@ -3251,10 +3354,10 @@
       <x:c r="AC9" s="15"/>
       <x:c r="AD9" s="15"/>
       <x:c r="AE9" s="15" t="str">
-        <x:v>RK3588 6 TOPS</x:v>
+        <x:v>Jetson Orin NX 157 TOPS</x:v>
       </x:c>
       <x:c r="AF9" s="15" t="str">
-        <x:v>4-6</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="AG9" s="15" t="str">
         <x:v>IP40</x:v>
@@ -3269,53 +3372,65 @@
         <x:v>供应商产品册</x:v>
       </x:c>
       <x:c r="AK9" s="15" t="str">
-        <x:v>无长行程升降；负载较低</x:v>
+        <x:v>300mm升降；负载包含末端</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>zdl_z1</x:v>
+        <x:v>zdl_l1</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
         <x:v>智动力</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
-        <x:v>Z1</x:v>
+        <x:v>L1 灵骏系列</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>移动双臂本体/SDK平台</x:v>
+        <x:v>轻量移动双臂本体</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
-        <x:v>开发手册r26.6</x:v>
-      </x:c>
-      <x:c r="F10" s="15"/>
+        <x:v>供应商产品资料</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="n">
+        <x:v>15</x:v>
+      </x:c>
       <x:c r="G10" s="15" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H10" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I10" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J10" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I10" s="15"/>
+      <x:c r="J10" s="15"/>
       <x:c r="K10" s="15" t="str">
-        <x:v>双轮差速底盘</x:v>
+        <x:v>差速轮式底盘</x:v>
       </x:c>
       <x:c r="L10" s="15" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="M10" s="15"/>
-      <x:c r="N10" s="15"/>
-      <x:c r="O10" s="15"/>
-      <x:c r="P10" s="15"/>
+      <x:c r="M10" s="15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N10" s="15" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="O10" s="15" t="n">
+        <x:v>1280</x:v>
+      </x:c>
+      <x:c r="P10" s="15" t="n">
+        <x:v>580</x:v>
+      </x:c>
       <x:c r="Q10" s="15"/>
-      <x:c r="R10" s="15"/>
-      <x:c r="S10" s="15"/>
+      <x:c r="R10" s="15" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="S10" s="15" t="n">
+        <x:v>600</x:v>
+      </x:c>
       <x:c r="T10" s="15"/>
-      <x:c r="U10" s="15"/>
+      <x:c r="U10" s="15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
       <x:c r="V10" s="15"/>
       <x:c r="W10" s="15"/>
       <x:c r="X10" s="15"/>
@@ -3323,54 +3438,58 @@
       <x:c r="Z10" s="15"/>
       <x:c r="AA10" s="15"/>
       <x:c r="AB10" s="15" t="str">
-        <x:v>CSP/CST；笛卡尔阻抗和关节阻抗标记待实现</x:v>
+        <x:v>未公开</x:v>
       </x:c>
       <x:c r="AC10" s="15"/>
       <x:c r="AD10" s="15"/>
       <x:c r="AE10" s="15" t="str">
-        <x:v>Cerebellum+Orin</x:v>
-      </x:c>
-      <x:c r="AF10" s="15" t="str"/>
-      <x:c r="AG10" s="15" t="str"/>
+        <x:v>RK3588 6 TOPS</x:v>
+      </x:c>
+      <x:c r="AF10" s="15" t="str">
+        <x:v>4-6</x:v>
+      </x:c>
+      <x:c r="AG10" s="15" t="str">
+        <x:v>IP40</x:v>
+      </x:c>
       <x:c r="AH10" s="15" t="str">
-        <x:v>夹爪或灵巧手</x:v>
+        <x:v>七自由度灵巧手或夹爪</x:v>
       </x:c>
       <x:c r="AI10" s="15" t="str">
-        <x:v>DDS；C++17；CycloneDDS 0.10.5</x:v>
+        <x:v>C++；ROS；Python</x:v>
       </x:c>
       <x:c r="AJ10" s="15" t="str">
-        <x:v>供应商开发手册</x:v>
+        <x:v>供应商产品册</x:v>
       </x:c>
       <x:c r="AK10" s="15" t="str">
-        <x:v>仅有SDK资料；接口命名、矩阵顺序和力矩单位存在待澄清项</x:v>
+        <x:v>无长行程升降；负载较低</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="15" t="str">
-        <x:v>unitree_g1d_flagship</x:v>
+        <x:v>zdl_z1</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>宇树</x:v>
+        <x:v>智动力</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>Unitree G1-D 旗舰版</x:v>
+        <x:v>Z1</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>移动双臂本体</x:v>
+        <x:v>移动双臂本体/SDK平台</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
-        <x:v>官方产品</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="n">
-        <x:v>19</x:v>
-      </x:c>
+        <x:v>开发手册r26.6</x:v>
+      </x:c>
+      <x:c r="F11" s="15"/>
       <x:c r="G11" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H11" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I11" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I11" s="15"/>
       <x:c r="J11" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -3380,29 +3499,15 @@
       <x:c r="L11" s="15" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="M11" s="15" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="N11" s="15" t="n">
-        <x:v>1260</x:v>
-      </x:c>
-      <x:c r="O11" s="15" t="n">
-        <x:v>1680</x:v>
-      </x:c>
-      <x:c r="P11" s="15" t="n">
-        <x:v>525</x:v>
-      </x:c>
-      <x:c r="Q11" s="15" t="n">
-        <x:v>570</x:v>
-      </x:c>
-      <x:c r="R11" s="15" t="n">
-        <x:v>90</x:v>
-      </x:c>
+      <x:c r="M11" s="15"/>
+      <x:c r="N11" s="15"/>
+      <x:c r="O11" s="15"/>
+      <x:c r="P11" s="15"/>
+      <x:c r="Q11" s="15"/>
+      <x:c r="R11" s="15"/>
       <x:c r="S11" s="15"/>
       <x:c r="T11" s="15"/>
-      <x:c r="U11" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="U11" s="15"/>
       <x:c r="V11" s="15"/>
       <x:c r="W11" s="15"/>
       <x:c r="X11" s="15"/>
@@ -3410,48 +3515,46 @@
       <x:c r="Z11" s="15"/>
       <x:c r="AA11" s="15"/>
       <x:c r="AB11" s="15" t="str">
-        <x:v>未公开</x:v>
+        <x:v>CSP/CST；笛卡尔阻抗和关节阻抗标记待实现</x:v>
       </x:c>
       <x:c r="AC11" s="15"/>
       <x:c r="AD11" s="15"/>
       <x:c r="AE11" s="15" t="str">
-        <x:v>8核CPU；可选Orin NX 100 TOPS</x:v>
-      </x:c>
-      <x:c r="AF11" s="15" t="str">
-        <x:v>6</x:v>
-      </x:c>
+        <x:v>Cerebellum+Orin</x:v>
+      </x:c>
+      <x:c r="AF11" s="15" t="str"/>
       <x:c r="AG11" s="15" t="str"/>
       <x:c r="AH11" s="15" t="str">
-        <x:v>二指夹爪或三/五指灵巧手</x:v>
+        <x:v>夹爪或灵巧手</x:v>
       </x:c>
       <x:c r="AI11" s="15" t="str">
-        <x:v>支持二次开发</x:v>
+        <x:v>DDS；C++17；CycloneDDS 0.10.5</x:v>
       </x:c>
       <x:c r="AJ11" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商开发手册</x:v>
       </x:c>
       <x:c r="AK11" s="15" t="str">
-        <x:v>差速底盘支持原地旋转，不支持纯横移</x:v>
+        <x:v>仅有SDK资料；接口命名、矩阵顺序和力矩单位存在待澄清项</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="34" customHeight="1">
       <x:c r="A12" s="15" t="str">
-        <x:v>unitree_g1d_standard</x:v>
+        <x:v>unitree_g1d_flagship</x:v>
       </x:c>
       <x:c r="B12" s="15" t="str">
         <x:v>宇树</x:v>
       </x:c>
       <x:c r="C12" s="15" t="str">
-        <x:v>Unitree G1-D 通用版</x:v>
+        <x:v>Unitree G1-D 旗舰版</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
-        <x:v>固定/可搬运双臂平台</x:v>
+        <x:v>移动双臂本体</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
         <x:v>官方产品</x:v>
       </x:c>
       <x:c r="F12" s="15" t="n">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G12" s="15" t="n">
         <x:v>7</x:v>
@@ -3461,15 +3564,17 @@
       </x:c>
       <x:c r="I12" s="15"/>
       <x:c r="J12" s="15" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K12" s="15" t="str">
-        <x:v>无主动移动参数</x:v>
+        <x:v>双轮差速底盘</x:v>
       </x:c>
       <x:c r="L12" s="15" t="str">
         <x:v>否</x:v>
       </x:c>
-      <x:c r="M12" s="15"/>
+      <x:c r="M12" s="15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
       <x:c r="N12" s="15" t="n">
         <x:v>1260</x:v>
       </x:c>
@@ -3477,10 +3582,10 @@
         <x:v>1680</x:v>
       </x:c>
       <x:c r="P12" s="15" t="n">
-        <x:v>620</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="Q12" s="15" t="n">
-        <x:v>620</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="R12" s="15" t="n">
         <x:v>90</x:v>
@@ -3505,7 +3610,7 @@
         <x:v>8核CPU；可选Orin NX 100 TOPS</x:v>
       </x:c>
       <x:c r="AF12" s="15" t="str">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="AG12" s="15" t="str"/>
       <x:c r="AH12" s="15" t="str">
@@ -3518,259 +3623,271 @@
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK12" s="15" t="str">
-        <x:v>官方参数表未给出主动底盘速度与驱动形式</x:v>
+        <x:v>差速底盘支持原地旋转，不支持纯横移</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="15" t="str">
-        <x:v>tianji_marvin_m6ccs</x:v>
+        <x:v>unitree_g1d_standard</x:v>
       </x:c>
       <x:c r="B13" s="15" t="str">
-        <x:v>天机智能</x:v>
+        <x:v>宇树</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Marvin M6 CCS</x:v>
+        <x:v>Unitree G1-D 通用版</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
-        <x:v>双臂模块</x:v>
+        <x:v>固定/可搬运双臂平台</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
-        <x:v>供应商产品资料</x:v>
+        <x:v>官方产品</x:v>
       </x:c>
       <x:c r="F13" s="15" t="n">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="G13" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H13" s="15"/>
+      <x:c r="H13" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I13" s="15"/>
-      <x:c r="J13" s="15"/>
+      <x:c r="J13" s="15" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="K13" s="15" t="str">
-        <x:v>需集成第三方底盘</x:v>
+        <x:v>无主动移动参数</x:v>
       </x:c>
       <x:c r="L13" s="15" t="str">
-        <x:v>待集成</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="M13" s="15"/>
-      <x:c r="N13" s="15"/>
-      <x:c r="O13" s="15"/>
-      <x:c r="P13" s="15"/>
-      <x:c r="Q13" s="15"/>
+      <x:c r="N13" s="15" t="n">
+        <x:v>1260</x:v>
+      </x:c>
+      <x:c r="O13" s="15" t="n">
+        <x:v>1680</x:v>
+      </x:c>
+      <x:c r="P13" s="15" t="n">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="Q13" s="15" t="n">
+        <x:v>620</x:v>
+      </x:c>
       <x:c r="R13" s="15" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="S13" s="15" t="n">
-        <x:v>696</x:v>
-      </x:c>
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="S13" s="15"/>
       <x:c r="T13" s="15"/>
       <x:c r="U13" s="15" t="n">
-        <x:v>6</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V13" s="15"/>
       <x:c r="W13" s="15"/>
       <x:c r="X13" s="15"/>
       <x:c r="Y13" s="15" t="str"/>
-      <x:c r="Z13" s="15" t="n">
-        <x:v>0.03</x:v>
-      </x:c>
+      <x:c r="Z13" s="15"/>
       <x:c r="AA13" s="15"/>
       <x:c r="AB13" s="15" t="str">
-        <x:v>全关节扭矩传感和阻抗控制；作用力重复精度≤0.15N/0.05N·m</x:v>
+        <x:v>未公开</x:v>
       </x:c>
       <x:c r="AC13" s="15"/>
-      <x:c r="AD13" s="15" t="n">
-        <x:v>8000</x:v>
-      </x:c>
-      <x:c r="AE13" s="15" t="str"/>
+      <x:c r="AD13" s="15"/>
+      <x:c r="AE13" s="15" t="str">
+        <x:v>8核CPU；可选Orin NX 100 TOPS</x:v>
+      </x:c>
       <x:c r="AF13" s="15" t="str">
-        <x:v>外部供电</x:v>
-      </x:c>
-      <x:c r="AG13" s="15" t="str">
-        <x:v>IP54</x:v>
-      </x:c>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AG13" s="15" t="str"/>
       <x:c r="AH13" s="15" t="str">
-        <x:v>末端执行器由集成方配置</x:v>
+        <x:v>二指夹爪或三/五指灵巧手</x:v>
       </x:c>
       <x:c r="AI13" s="15" t="str">
-        <x:v>EtherCAT；CAN-FD；RS485；最高1kHz SDK</x:v>
+        <x:v>支持二次开发</x:v>
       </x:c>
       <x:c r="AJ13" s="15" t="str">
-        <x:v>供应商产品册</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK13" s="15" t="str">
-        <x:v>单臂参数；不含标准移动底盘，不参加移动本体排名</x:v>
+        <x:v>官方参数表未给出主动底盘速度与驱动形式</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="34" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>boston_atlas_2026</x:v>
+        <x:v>tianji_marvin_m6ccs</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Boston Dynamics</x:v>
+        <x:v>天机智能</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>Atlas</x:v>
+        <x:v>Marvin M6 CCS</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>全尺寸双足工业人形</x:v>
+        <x:v>双臂模块</x:v>
       </x:c>
       <x:c r="E14" s="15" t="str">
-        <x:v>早期客户导入</x:v>
+        <x:v>供应商产品资料</x:v>
       </x:c>
       <x:c r="F14" s="15" t="n">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="G14" s="15"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G14" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="H14" s="15"/>
       <x:c r="I14" s="15"/>
       <x:c r="J14" s="15"/>
       <x:c r="K14" s="15" t="str">
-        <x:v>双足全电驱</x:v>
+        <x:v>需集成第三方底盘</x:v>
       </x:c>
       <x:c r="L14" s="15" t="str">
-        <x:v>步态可侧移；连续工业横移待验证</x:v>
+        <x:v>待集成</x:v>
       </x:c>
       <x:c r="M14" s="15"/>
-      <x:c r="N14" s="15" t="n">
-        <x:v>1900</x:v>
-      </x:c>
-      <x:c r="O14" s="15" t="n">
-        <x:v>1900</x:v>
-      </x:c>
+      <x:c r="N14" s="15"/>
+      <x:c r="O14" s="15"/>
       <x:c r="P14" s="15"/>
       <x:c r="Q14" s="15"/>
       <x:c r="R14" s="15" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="S14" s="15"/>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="S14" s="15" t="n">
+        <x:v>696</x:v>
+      </x:c>
       <x:c r="T14" s="15"/>
-      <x:c r="U14" s="15"/>
+      <x:c r="U14" s="15" t="n">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="V14" s="15"/>
-      <x:c r="W14" s="15" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="X14" s="15" t="n">
-        <x:v>50</x:v>
-      </x:c>
+      <x:c r="W14" s="15"/>
+      <x:c r="X14" s="15"/>
       <x:c r="Y14" s="15" t="str"/>
-      <x:c r="Z14" s="15"/>
+      <x:c r="Z14" s="15" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
       <x:c r="AA14" s="15"/>
       <x:c r="AB14" s="15" t="str">
-        <x:v>触觉感知；全身力控量化指标未公开</x:v>
+        <x:v>全关节扭矩传感和阻抗控制；作用力重复精度≤0.15N/0.05N·m</x:v>
       </x:c>
       <x:c r="AC14" s="15"/>
-      <x:c r="AD14" s="15"/>
+      <x:c r="AD14" s="15" t="n">
+        <x:v>8000</x:v>
+      </x:c>
       <x:c r="AE14" s="15" t="str"/>
       <x:c r="AF14" s="15" t="str">
-        <x:v>4</x:v>
+        <x:v>外部供电</x:v>
       </x:c>
       <x:c r="AG14" s="15" t="str">
-        <x:v>IP67</x:v>
+        <x:v>IP54</x:v>
       </x:c>
       <x:c r="AH14" s="15" t="str">
-        <x:v>工业任务手/夹具未披露</x:v>
+        <x:v>末端执行器由集成方配置</x:v>
       </x:c>
       <x:c r="AI14" s="15" t="str">
-        <x:v>Orbit可对接MES/WMS；支持条码和工作流集成</x:v>
+        <x:v>EtherCAT；CAN-FD；RS485；最高1kHz SDK</x:v>
       </x:c>
       <x:c r="AJ14" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商产品册</x:v>
       </x:c>
       <x:c r="AK14" s="15" t="str">
-        <x:v>全身Reach 2.3m；持续负载30kg/瞬时50kg；自动换电；仅面向选择性早期客户</x:v>
+        <x:v>单臂参数；不含标准移动底盘，不参加移动本体排名</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="34" customHeight="1">
       <x:c r="A15" s="15" t="str">
-        <x:v>figure_03</x:v>
+        <x:v>boston_atlas_2026</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>Figure AI</x:v>
+        <x:v>Boston Dynamics</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Figure 03</x:v>
+        <x:v>Atlas</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>全尺寸双足通用人形</x:v>
+        <x:v>全尺寸双足工业人形</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
-        <x:v>量产爬坡/客户验证</x:v>
-      </x:c>
-      <x:c r="F15" s="15"/>
+        <x:v>早期客户导入</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="n">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="G15" s="15"/>
       <x:c r="H15" s="15"/>
       <x:c r="I15" s="15"/>
       <x:c r="J15" s="15"/>
       <x:c r="K15" s="15" t="str">
-        <x:v>双足电驱</x:v>
+        <x:v>双足全电驱</x:v>
       </x:c>
       <x:c r="L15" s="15" t="str">
-        <x:v>步态可侧移；工业横移精度未披露</x:v>
-      </x:c>
-      <x:c r="M15" s="15" t="n">
-        <x:v>1.2</x:v>
-      </x:c>
+        <x:v>步态可侧移；连续工业横移待验证</x:v>
+      </x:c>
+      <x:c r="M15" s="15"/>
       <x:c r="N15" s="15" t="n">
-        <x:v>1727</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="O15" s="15" t="n">
-        <x:v>1727</x:v>
+        <x:v>1900</x:v>
       </x:c>
       <x:c r="P15" s="15"/>
       <x:c r="Q15" s="15"/>
       <x:c r="R15" s="15" t="n">
-        <x:v>61</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="S15" s="15"/>
       <x:c r="T15" s="15"/>
       <x:c r="U15" s="15"/>
       <x:c r="V15" s="15"/>
       <x:c r="W15" s="15" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="X15" s="15"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="X15" s="15" t="n">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="Y15" s="15" t="str"/>
       <x:c r="Z15" s="15"/>
       <x:c r="AA15" s="15"/>
       <x:c r="AB15" s="15" t="str">
-        <x:v>柔顺触觉手；指尖可检测约3g压力</x:v>
+        <x:v>触觉感知；全身力控量化指标未公开</x:v>
       </x:c>
       <x:c r="AC15" s="15"/>
       <x:c r="AD15" s="15"/>
       <x:c r="AE15" s="15" t="str"/>
       <x:c r="AF15" s="15" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="AG15" s="15" t="str"/>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AG15" s="15" t="str">
+        <x:v>IP67</x:v>
+      </x:c>
       <x:c r="AH15" s="15" t="str">
-        <x:v>自研触觉灵巧手</x:v>
+        <x:v>工业任务手/夹具未披露</x:v>
       </x:c>
       <x:c r="AI15" s="15" t="str">
-        <x:v>Helix专有系统；10Gbps毫米波数据卸载；无公开工业SDK</x:v>
+        <x:v>Orbit可对接MES/WMS；支持条码和工作流集成</x:v>
       </x:c>
       <x:c r="AJ15" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK15" s="15" t="str">
-        <x:v>2.3kWh电池；2kW无线充电；UN38.3；BMW生产验证；接口和采购方式不公开</x:v>
+        <x:v>全身Reach 2.3m；持续负载30kg/瞬时50kg；自动换电；仅面向选择性早期客户</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="34" customHeight="1">
       <x:c r="A16" s="15" t="str">
-        <x:v>tesla_optimus</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>Tesla</x:v>
+        <x:v>Figure AI</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Optimus</x:v>
+        <x:v>Figure 03</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
         <x:v>全尺寸双足通用人形</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
-        <x:v>产线建设/内部验证</x:v>
+        <x:v>量产爬坡/客户验证</x:v>
       </x:c>
       <x:c r="F16" s="15"/>
       <x:c r="G16" s="15"/>
@@ -3781,103 +3898,93 @@
         <x:v>双足电驱</x:v>
       </x:c>
       <x:c r="L16" s="15" t="str">
-        <x:v>工业横移能力与精度未披露</x:v>
-      </x:c>
-      <x:c r="M16" s="15"/>
-      <x:c r="N16" s="15"/>
-      <x:c r="O16" s="15"/>
+        <x:v>步态可侧移；工业横移精度未披露</x:v>
+      </x:c>
+      <x:c r="M16" s="15" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="N16" s="15" t="n">
+        <x:v>1727</x:v>
+      </x:c>
+      <x:c r="O16" s="15" t="n">
+        <x:v>1727</x:v>
+      </x:c>
       <x:c r="P16" s="15"/>
       <x:c r="Q16" s="15"/>
-      <x:c r="R16" s="15"/>
+      <x:c r="R16" s="15" t="n">
+        <x:v>61</x:v>
+      </x:c>
       <x:c r="S16" s="15"/>
       <x:c r="T16" s="15"/>
       <x:c r="U16" s="15"/>
       <x:c r="V16" s="15"/>
-      <x:c r="W16" s="15"/>
+      <x:c r="W16" s="15" t="n">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="X16" s="15"/>
       <x:c r="Y16" s="15" t="str"/>
       <x:c r="Z16" s="15"/>
       <x:c r="AA16" s="15"/>
       <x:c r="AB16" s="15" t="str">
-        <x:v>未公开</x:v>
+        <x:v>柔顺触觉手；指尖可检测约3g压力</x:v>
       </x:c>
       <x:c r="AC16" s="15"/>
       <x:c r="AD16" s="15"/>
       <x:c r="AE16" s="15" t="str"/>
-      <x:c r="AF16" s="15" t="str"/>
+      <x:c r="AF16" s="15" t="str">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="AG16" s="15" t="str"/>
       <x:c r="AH16" s="15" t="str">
-        <x:v>灵巧手</x:v>
+        <x:v>自研触觉灵巧手</x:v>
       </x:c>
       <x:c r="AI16" s="15" t="str">
-        <x:v>专有软硬件栈；未公开第三方SDK</x:v>
+        <x:v>Helix专有系统；10Gbps毫米波数据卸载；无公开工业SDK</x:v>
       </x:c>
       <x:c r="AJ16" s="15" t="str">
-        <x:v>官方网站+投资者披露</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK16" s="15" t="str">
-        <x:v>官方当前页面未披露身高负载续航自由度等可采购规格；不具备供应商选型基线</x:v>
+        <x:v>2.3kWh电池；2kW无线充电；UN38.3；BMW生产验证；接口和采购方式不公开</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="34" customHeight="1">
       <x:c r="A17" s="15" t="str">
-        <x:v>limx_oli_edu</x:v>
+        <x:v>tesla_optimus</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>逐际动力</x:v>
+        <x:v>Tesla</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
-        <x:v>LimX Oli EDU</x:v>
+        <x:v>Optimus</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>全尺寸双足开发平台</x:v>
+        <x:v>全尺寸双足通用人形</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
-        <x:v>可购/持续迭代</x:v>
-      </x:c>
-      <x:c r="F17" s="15" t="n">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G17" s="15" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="H17" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I17" s="15" t="n">
-        <x:v>2</x:v>
-      </x:c>
+        <x:v>产线建设/内部验证</x:v>
+      </x:c>
+      <x:c r="F17" s="15"/>
+      <x:c r="G17" s="15"/>
+      <x:c r="H17" s="15"/>
+      <x:c r="I17" s="15"/>
       <x:c r="J17" s="15"/>
       <x:c r="K17" s="15" t="str">
-        <x:v>双足步行</x:v>
+        <x:v>双足电驱</x:v>
       </x:c>
       <x:c r="L17" s="15" t="str">
-        <x:v>步态可侧移；连续贴线横移待实测</x:v>
-      </x:c>
-      <x:c r="M17" s="15" t="n">
-        <x:v>1.389</x:v>
-      </x:c>
-      <x:c r="N17" s="15" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="O17" s="15" t="n">
-        <x:v>1650</x:v>
-      </x:c>
-      <x:c r="P17" s="15" t="n">
-        <x:v>550</x:v>
-      </x:c>
+        <x:v>工业横移能力与精度未披露</x:v>
+      </x:c>
+      <x:c r="M17" s="15"/>
+      <x:c r="N17" s="15"/>
+      <x:c r="O17" s="15"/>
+      <x:c r="P17" s="15"/>
       <x:c r="Q17" s="15"/>
-      <x:c r="R17" s="15" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="S17" s="15" t="n">
-        <x:v>700</x:v>
-      </x:c>
+      <x:c r="R17" s="15"/>
+      <x:c r="S17" s="15"/>
       <x:c r="T17" s="15"/>
       <x:c r="U17" s="15"/>
-      <x:c r="V17" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="V17" s="15"/>
       <x:c r="W17" s="15"/>
       <x:c r="X17" s="15"/>
       <x:c r="Y17" s="15" t="str"/>
@@ -3888,162 +3995,154 @@
       </x:c>
       <x:c r="AC17" s="15"/>
       <x:c r="AD17" s="15"/>
-      <x:c r="AE17" s="15" t="str">
-        <x:v>RK3588运控+Orin NX 157TOPS感知</x:v>
-      </x:c>
-      <x:c r="AF17" s="15" t="str">
-        <x:v>2</x:v>
-      </x:c>
+      <x:c r="AE17" s="15" t="str"/>
+      <x:c r="AF17" s="15" t="str"/>
       <x:c r="AG17" s="15" t="str"/>
       <x:c r="AH17" s="15" t="str">
-        <x:v>二指夹爪或五指灵巧手</x:v>
+        <x:v>灵巧手</x:v>
       </x:c>
       <x:c r="AI17" s="15" t="str">
-        <x:v>WiFi6；蓝牙；USB3；千兆网；Type-C；遥控/传感/底层和上层运动API</x:v>
+        <x:v>专有软硬件栈；未公开第三方SDK</x:v>
       </x:c>
       <x:c r="AJ17" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>官方网站+投资者披露</x:v>
       </x:c>
       <x:c r="AK17" s="15" t="str">
-        <x:v>约2h续航；9500mAh抽屉式电池；最大负载3kg；开放度较好但工业精度和认证未公开</x:v>
+        <x:v>官方当前页面未披露身高负载续航自由度等可采购规格；不具备供应商选型基线</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="34" customHeight="1">
       <x:c r="A18" s="15" t="str">
-        <x:v>limx_tron2_dualarm</x:v>
+        <x:v>limx_oli_edu</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
         <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
-        <x:v>TRON 2 双臂形态</x:v>
+        <x:v>LimX Oli EDU</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>多形态双臂移动平台</x:v>
+        <x:v>全尺寸双足开发平台</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
         <x:v>可购/持续迭代</x:v>
       </x:c>
-      <x:c r="F18" s="15"/>
+      <x:c r="F18" s="15" t="n">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="G18" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H18" s="15"/>
+      <x:c r="H18" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="I18" s="15" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="J18" s="15"/>
       <x:c r="K18" s="15" t="str">
-        <x:v>双足/双轮足可换形</x:v>
+        <x:v>双足步行</x:v>
       </x:c>
       <x:c r="L18" s="15" t="str">
-        <x:v>官方称四向移动；纯横移机制待确认</x:v>
+        <x:v>步态可侧移；连续贴线横移待实测</x:v>
       </x:c>
       <x:c r="M18" s="15" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="N18" s="15"/>
-      <x:c r="O18" s="15"/>
-      <x:c r="P18" s="15"/>
+        <x:v>1.389</x:v>
+      </x:c>
+      <x:c r="N18" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="O18" s="15" t="n">
+        <x:v>1650</x:v>
+      </x:c>
+      <x:c r="P18" s="15" t="n">
+        <x:v>550</x:v>
+      </x:c>
       <x:c r="Q18" s="15"/>
-      <x:c r="R18" s="15"/>
-      <x:c r="S18" s="15"/>
+      <x:c r="R18" s="15" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="S18" s="15" t="n">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="T18" s="15"/>
-      <x:c r="U18" s="15" t="n">
+      <x:c r="U18" s="15"/>
+      <x:c r="V18" s="15" t="n">
         <x:v>3</x:v>
-      </x:c>
-      <x:c r="V18" s="15" t="n">
-        <x:v>5</x:v>
       </x:c>
       <x:c r="W18" s="15"/>
       <x:c r="X18" s="15"/>
       <x:c r="Y18" s="15" t="str"/>
-      <x:c r="Z18" s="15" t="n">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="Z18" s="15"/>
       <x:c r="AA18" s="15"/>
       <x:c r="AB18" s="15" t="str">
-        <x:v>双臂安全边界；力控和力传感量化未公开</x:v>
+        <x:v>未公开</x:v>
       </x:c>
       <x:c r="AC18" s="15"/>
       <x:c r="AD18" s="15"/>
       <x:c r="AE18" s="15" t="str">
-        <x:v>Intel Core Ultra拓展模块</x:v>
-      </x:c>
-      <x:c r="AF18" s="15" t="str"/>
+        <x:v>RK3588运控+Orin NX 157TOPS感知</x:v>
+      </x:c>
+      <x:c r="AF18" s="15" t="str">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="AG18" s="15" t="str"/>
       <x:c r="AH18" s="15" t="str">
-        <x:v>夹爪或灵巧手</x:v>
+        <x:v>二指夹爪或五指灵巧手</x:v>
       </x:c>
       <x:c r="AI18" s="15" t="str">
-        <x:v>Python；C++；ROS1/ROS2；以太网；USB3；EtherCAT×2；RS485；多电压供电</x:v>
+        <x:v>WiFi6；蓝牙；USB3；千兆网；Type-C；遥控/传感/底层和上层运动API</x:v>
       </x:c>
       <x:c r="AJ18" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK18" s="15" t="str">
-        <x:v>双轮足速度3至5m/s；重复定位±0.5mm；遥操延迟100ms；更偏研发和多形态验证</x:v>
+        <x:v>约2h续航；9500mAh抽屉式电池；最大负载3kg；开放度较好但工业精度和认证未公开</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="34" customHeight="1">
       <x:c r="A19" s="15" t="str">
-        <x:v>galaxea_r1pro_2026</x:v>
+        <x:v>limx_tron2_dualarm</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>星海图</x:v>
+        <x:v>逐际动力</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>Galaxea R1 Pro 2026</x:v>
+        <x:v>TRON 2 双臂形态</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>轮式双臂仿人形本体</x:v>
+        <x:v>多形态双臂移动平台</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>现货/科研与行业落地</x:v>
-      </x:c>
-      <x:c r="F19" s="15" t="n">
-        <x:v>24</x:v>
-      </x:c>
+        <x:v>可购/持续迭代</x:v>
+      </x:c>
+      <x:c r="F19" s="15"/>
       <x:c r="G19" s="15" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H19" s="15" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I19" s="15"/>
-      <x:c r="J19" s="15" t="n">
-        <x:v>3</x:v>
-      </x:c>
+      <x:c r="H19" s="15"/>
+      <x:c r="I19" s="15" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="J19" s="15"/>
       <x:c r="K19" s="15" t="str">
-        <x:v>三舵轮360度全向底盘</x:v>
+        <x:v>双足/双轮足可换形</x:v>
       </x:c>
       <x:c r="L19" s="15" t="str">
-        <x:v>是</x:v>
+        <x:v>官方称四向移动；纯横移机制待确认</x:v>
       </x:c>
       <x:c r="M19" s="15" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="N19" s="15" t="n">
-        <x:v>1700</x:v>
-      </x:c>
-      <x:c r="O19" s="15" t="n">
-        <x:v>1700</x:v>
-      </x:c>
-      <x:c r="P19" s="15" t="n">
-        <x:v>675</x:v>
-      </x:c>
-      <x:c r="Q19" s="15" t="n">
-        <x:v>636</x:v>
-      </x:c>
-      <x:c r="R19" s="15" t="n">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="S19" s="15" t="n">
-        <x:v>620</x:v>
-      </x:c>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="N19" s="15"/>
+      <x:c r="O19" s="15"/>
+      <x:c r="P19" s="15"/>
+      <x:c r="Q19" s="15"/>
+      <x:c r="R19" s="15"/>
+      <x:c r="S19" s="15"/>
       <x:c r="T19" s="15"/>
       <x:c r="U19" s="15" t="n">
-        <x:v>3.5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="V19" s="15" t="n">
         <x:v>5</x:v>
@@ -4056,88 +4155,181 @@
       </x:c>
       <x:c r="AA19" s="15"/>
       <x:c r="AB19" s="15" t="str">
-        <x:v>七轴仿人力控机械臂；力传感为选配</x:v>
+        <x:v>双臂安全边界；力控和力传感量化未公开</x:v>
       </x:c>
       <x:c r="AC19" s="15"/>
       <x:c r="AD19" s="15"/>
       <x:c r="AE19" s="15" t="str">
-        <x:v>Jetson AGX Orin 32GB 200TOPS</x:v>
+        <x:v>Intel Core Ultra拓展模块</x:v>
       </x:c>
       <x:c r="AF19" s="15" t="str"/>
       <x:c r="AG19" s="15" t="str"/>
       <x:c r="AH19" s="15" t="str">
-        <x:v>电动平行夹爪</x:v>
+        <x:v>夹爪或灵巧手</x:v>
       </x:c>
       <x:c r="AI19" s="15" t="str">
-        <x:v>USB3；HDMI；千兆以太网；WiFi6；蓝牙</x:v>
+        <x:v>Python；C++；ROS1/ROS2；以太网；USB3；EtherCAT×2；RS485；多电压供电</x:v>
       </x:c>
       <x:c r="AJ19" s="15" t="str">
-        <x:v>官方产品页+开发文档</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="AK19" s="15" t="str">
-        <x:v>垂直工作空间0至2m；带夹爪水平半径861mm；夹持力额定150N峰值350N；A2机械臂无制动器需重点评估断电下坠</x:v>
+        <x:v>双轮足速度3至5m/s；重复定位±0.5mm；遥操延迟100ms；更偏研发和多形态验证</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="34" customHeight="1">
       <x:c r="A20" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>galaxea_r1pro_2026</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>它石智航</x:v>
+        <x:v>星海图</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
-        <x:v>TARS A1</x:v>
+        <x:v>Galaxea R1 Pro 2026</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>轮式工业具身本体</x:v>
+        <x:v>轮式双臂仿人形本体</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
-        <x:v>产线验证/规模部署计划</x:v>
-      </x:c>
-      <x:c r="F20" s="15"/>
-      <x:c r="G20" s="15"/>
-      <x:c r="H20" s="15"/>
+        <x:v>现货/科研与行业落地</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G20" s="15" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H20" s="15" t="n">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="I20" s="15"/>
-      <x:c r="J20" s="15"/>
+      <x:c r="J20" s="15" t="n">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="K20" s="15" t="str">
-        <x:v>轮式底盘（轮系未公开）</x:v>
+        <x:v>三舵轮360度全向底盘</x:v>
       </x:c>
       <x:c r="L20" s="15" t="str">
-        <x:v>待确认</x:v>
-      </x:c>
-      <x:c r="M20" s="15"/>
-      <x:c r="N20" s="15"/>
-      <x:c r="O20" s="15"/>
-      <x:c r="P20" s="15"/>
-      <x:c r="Q20" s="15"/>
-      <x:c r="R20" s="15"/>
-      <x:c r="S20" s="15"/>
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="M20" s="15" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="N20" s="15" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="O20" s="15" t="n">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="P20" s="15" t="n">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="Q20" s="15" t="n">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="R20" s="15" t="n">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="S20" s="15" t="n">
+        <x:v>620</x:v>
+      </x:c>
       <x:c r="T20" s="15"/>
-      <x:c r="U20" s="15"/>
-      <x:c r="V20" s="15"/>
+      <x:c r="U20" s="15" t="n">
+        <x:v>3.5</x:v>
+      </x:c>
+      <x:c r="V20" s="15" t="n">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="W20" s="15"/>
       <x:c r="X20" s="15"/>
       <x:c r="Y20" s="15" t="str"/>
-      <x:c r="Z20" s="15"/>
+      <x:c r="Z20" s="15" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
       <x:c r="AA20" s="15"/>
       <x:c r="AB20" s="15" t="str">
-        <x:v>线束亚毫米装配有公开任务证据；本体力控指标未公开</x:v>
+        <x:v>七轴仿人力控机械臂；力传感为选配</x:v>
       </x:c>
       <x:c r="AC20" s="15"/>
       <x:c r="AD20" s="15"/>
-      <x:c r="AE20" s="15" t="str"/>
+      <x:c r="AE20" s="15" t="str">
+        <x:v>Jetson AGX Orin 32GB 200TOPS</x:v>
+      </x:c>
       <x:c r="AF20" s="15" t="str"/>
       <x:c r="AG20" s="15" t="str"/>
       <x:c r="AH20" s="15" t="str">
+        <x:v>电动平行夹爪</x:v>
+      </x:c>
+      <x:c r="AI20" s="15" t="str">
+        <x:v>USB3；HDMI；千兆以太网；WiFi6；蓝牙</x:v>
+      </x:c>
+      <x:c r="AJ20" s="15" t="str">
+        <x:v>官方产品页+开发文档</x:v>
+      </x:c>
+      <x:c r="AK20" s="15" t="str">
+        <x:v>垂直工作空间0至2m；带夹爪水平半径861mm；夹持力额定150N峰值350N；A2机械臂无制动器需重点评估断电下坠</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="34" customHeight="1">
+      <x:c r="A21" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="B21" s="15" t="str">
+        <x:v>它石智航</x:v>
+      </x:c>
+      <x:c r="C21" s="15" t="str">
+        <x:v>TARS A1</x:v>
+      </x:c>
+      <x:c r="D21" s="15" t="str">
+        <x:v>轮式工业具身本体</x:v>
+      </x:c>
+      <x:c r="E21" s="15" t="str">
+        <x:v>产线验证/规模部署计划</x:v>
+      </x:c>
+      <x:c r="F21" s="15"/>
+      <x:c r="G21" s="15"/>
+      <x:c r="H21" s="15"/>
+      <x:c r="I21" s="15"/>
+      <x:c r="J21" s="15"/>
+      <x:c r="K21" s="15" t="str">
+        <x:v>轮式底盘（轮系未公开）</x:v>
+      </x:c>
+      <x:c r="L21" s="15" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="M21" s="15"/>
+      <x:c r="N21" s="15"/>
+      <x:c r="O21" s="15"/>
+      <x:c r="P21" s="15"/>
+      <x:c r="Q21" s="15"/>
+      <x:c r="R21" s="15"/>
+      <x:c r="S21" s="15"/>
+      <x:c r="T21" s="15"/>
+      <x:c r="U21" s="15"/>
+      <x:c r="V21" s="15"/>
+      <x:c r="W21" s="15"/>
+      <x:c r="X21" s="15"/>
+      <x:c r="Y21" s="15" t="str"/>
+      <x:c r="Z21" s="15"/>
+      <x:c r="AA21" s="15"/>
+      <x:c r="AB21" s="15" t="str">
+        <x:v>线束亚毫米装配有公开任务证据；本体力控指标未公开</x:v>
+      </x:c>
+      <x:c r="AC21" s="15"/>
+      <x:c r="AD21" s="15"/>
+      <x:c r="AE21" s="15" t="str"/>
+      <x:c r="AF21" s="15" t="str"/>
+      <x:c r="AG21" s="15" t="str"/>
+      <x:c r="AH21" s="15" t="str">
         <x:v>定制夹爪或DexHand</x:v>
       </x:c>
-      <x:c r="AI20" s="15" t="str">
+      <x:c r="AI21" s="15" t="str">
         <x:v>SDK与末端电气接口未公开</x:v>
       </x:c>
-      <x:c r="AJ20" s="15" t="str">
+      <x:c r="AJ21" s="15" t="str">
         <x:v>客户/政府/吉尼斯+内部沟通</x:v>
       </x:c>
-      <x:c r="AK20" s="15" t="str">
+      <x:c r="AK21" s="15" t="str">
         <x:v>公开完成105次每小时亚毫米线束装配纪录；内部沟通显示规模部署验收仍有差距且前期工装耗材投入高</x:v>
       </x:c>
     </x:row>
@@ -4147,7 +4339,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47646d5dd2334ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d832e6ed72e4cf5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5152,11 +5344,207 @@
       <x:c r="I35" s="15" t="str"/>
       <x:c r="J35" s="15" t="str"/>
     </x:row>
+    <x:row r="36" ht="38" customHeight="1">
+      <x:c r="A36" s="15" t="str">
+        <x:v>Q033</x:v>
+      </x:c>
+      <x:c r="B36" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C36" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D36" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E36" s="15" t="str">
+        <x:v>版本与交付</x:v>
+      </x:c>
+      <x:c r="F36" s="15" t="str">
+        <x:v>提供Moz1 Pro专属用户手册、SDK兼容矩阵和最终交付BOM，并逐项解释与Moz1 v2.7手册的差异</x:v>
+      </x:c>
+      <x:c r="G36" s="15" t="str">
+        <x:v>现有在线手册的相机数量、速度、夹爪和补能方式与Pro彩页不一致</x:v>
+      </x:c>
+      <x:c r="H36" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I36" s="15" t="str"/>
+      <x:c r="J36" s="15" t="str"/>
+    </x:row>
+    <x:row r="37" ht="38" customHeight="1">
+      <x:c r="A37" s="15" t="str">
+        <x:v>Q034</x:v>
+      </x:c>
+      <x:c r="B37" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C37" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D37" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="str">
+        <x:v>底盘POC</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="str">
+        <x:v>执行保持航向横移2米、斜移和低速贴线测试，并给出航向漂移、停车回摆、底盘定位误差和TCP收敛时间</x:v>
+      </x:c>
+      <x:c r="G37" s="15" t="str">
+        <x:v>SDK的vx/vy/wz确认具备纯横移指令但未给实测精度</x:v>
+      </x:c>
+      <x:c r="H37" s="15" t="str">
+        <x:v>待POC</x:v>
+      </x:c>
+      <x:c r="I37" s="15" t="str"/>
+      <x:c r="J37" s="15" t="str"/>
+    </x:row>
+    <x:row r="38" ht="38" customHeight="1">
+      <x:c r="A38" s="15" t="str">
+        <x:v>Q035</x:v>
+      </x:c>
+      <x:c r="B38" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="str">
+        <x:v>力控SDK</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="str">
+        <x:v>是否开放关节力矩与外力观测、末端力指令、阻抗/导纳参数、接触事件和六维力传感数据；频率、延迟和时间戳分别是多少</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="str">
+        <x:v>公开SDK仅见位置与底盘速度指令且没有force/torque字段</x:v>
+      </x:c>
+      <x:c r="H38" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I38" s="15" t="str"/>
+      <x:c r="J38" s="15" t="str"/>
+    </x:row>
+    <x:row r="39" ht="38" customHeight="1">
+      <x:c r="A39" s="15" t="str">
+        <x:v>Q036</x:v>
+      </x:c>
+      <x:c r="B39" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="str">
+        <x:v>补能与连续运行</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="str">
+        <x:v>自动回充、无线充电和换电是否为标准交付；单次续航、补能节拍、7×24小时降额与MTBF是多少</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="str">
+        <x:v>Pro彩页宣传24小时作业而旧款手册要求人工插线且安全页建议每日不超过8小时</x:v>
+      </x:c>
+      <x:c r="H39" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I39" s="15" t="str"/>
+      <x:c r="J39" s="15" t="str"/>
+    </x:row>
+    <x:row r="40" ht="38" customHeight="1">
+      <x:c r="A40" s="15" t="str">
+        <x:v>Q037</x:v>
+      </x:c>
+      <x:c r="B40" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="str">
+        <x:v>工业安全</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="str">
+        <x:v>提供Pro的IP等级、额定温湿度、功能安全认证、急停/STO安全回路、电池认证和火灾处置方案</x:v>
+      </x:c>
+      <x:c r="G40" s="15" t="str">
+        <x:v>旧款手册的10至35℃与负10至50℃口径冲突且未见PL/SIL证明</x:v>
+      </x:c>
+      <x:c r="H40" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I40" s="15" t="str"/>
+      <x:c r="J40" s="15" t="str"/>
+    </x:row>
+    <x:row r="41" ht="38" customHeight="1">
+      <x:c r="A41" s="15" t="str">
+        <x:v>Q038</x:v>
+      </x:c>
+      <x:c r="B41" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="str">
+        <x:v>网络与安全</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="str">
+        <x:v>解释172.16.0.20与172.16.1.20网络拓扑并提供密码修改、WiFi关闭、DDS隔离、端口白名单和外部控制鉴权方案</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="str">
+        <x:v>公开手册包含固定IP、固定Domain ID和默认账号密码</x:v>
+      </x:c>
+      <x:c r="H41" s="15" t="str">
+        <x:v>待IT联调</x:v>
+      </x:c>
+      <x:c r="I41" s="15" t="str"/>
+      <x:c r="J41" s="15" t="str"/>
+    </x:row>
+    <x:row r="42" ht="38" customHeight="1">
+      <x:c r="A42" s="15" t="str">
+        <x:v>Q039</x:v>
+      </x:c>
+      <x:c r="B42" s="15" t="str">
+        <x:v>千寻智能</x:v>
+      </x:c>
+      <x:c r="C42" s="15" t="str">
+        <x:v>Moz1 Pro</x:v>
+      </x:c>
+      <x:c r="D42" s="15" t="str">
+        <x:v>P0</x:v>
+      </x:c>
+      <x:c r="E42" s="15" t="str">
+        <x:v>末端接口</x:v>
+      </x:c>
+      <x:c r="F42" s="15" t="str">
+        <x:v>提供自研夹爪机械法兰、电气针脚、24/48V功率、CAN/RS485协议、快换结构、夹持力、开合行程和断电保持数据</x:v>
+      </x:c>
+      <x:c r="G42" s="15" t="str">
+        <x:v>旧款HMI写智元夹爪且第三方夹爪更换需技术支持；Pro彩页改称自研夹爪</x:v>
+      </x:c>
+      <x:c r="H42" s="15" t="str">
+        <x:v>待供应商回复</x:v>
+      </x:c>
+      <x:c r="I42" s="15" t="str"/>
+      <x:c r="J42" s="15" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
-  <x:conditionalFormatting sqref="D4:D35">
+  <x:conditionalFormatting sqref="D4:D42">
     <x:cfRule type="cellIs" dxfId="4" priority="1">
       <x:formula>"P0"</x:formula>
     </x:cfRule>
@@ -5165,13 +5553,13 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H4:H35">
+    <x:dataValidation type="list" sqref="H4:H42">
       <x:formula1>"待供应商回复,待POC,待IT联调,进行中,已关闭,不适用"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfceb751f894a4c15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21384adde6234c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5308,138 +5696,134 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="15" t="str">
+        <x:v>src_spirit_moz1pro_brochure</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="str">
+        <x:v>spirit_moz1_pro</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="str">
+        <x:v>Moz1 Pro产品彩页</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="str">
+        <x:v>sources/raw/04_千寻智能_Moz1/Moz1_Pro_产品彩页.pdf</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="str">
+        <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="str">
+        <x:v>中高</x:v>
+      </x:c>
+      <x:c r="I5" s="15" t="str">
+        <x:v>披露26自由度、全向轮、5kg负载、700mm臂展、标称±0.05mm、Thor平台和补能能力；缺测试条件</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="42" customHeight="1">
+      <x:c r="A6" s="15" t="str">
+        <x:v>src_spirit_fullstack</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="str">
+        <x:v>spirit_moz1_pro</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>供应商PDF</x:v>
+      </x:c>
+      <x:c r="D6" s="15" t="str">
+        <x:v>千寻智能具身智能全栈式解决方案画册</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="str">
+        <x:v>sources/raw/04_千寻智能_Moz1/全栈式解决方案画册.pdf</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="str">
+        <x:v>2026-03</x:v>
+      </x:c>
+      <x:c r="G6" s="15" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="H6" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I6" s="15" t="str">
+        <x:v>主体为旧款Moz1及CaptureX/Quanta方案；可靠性与案例不能直接继承给Pro</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="42" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>src_spirit_docs_robot</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>spirit_moz1_pro</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>官方在线手册</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
+        <x:v>Moz1 v2.7机器人手册</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="e">
+        <x:f>HYPERLINK("https://docs.spirit-ai.com/zh/moz1/get-started.html","https://docs.spirit-ai.com/zh/moz1/get-started.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://docs.spirit-ai.com/zh/moz1/get-started.html, friendlyName=https://docs.spirit-ai.com/zh/moz1/get-started.html</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str"/>
+      <x:c r="G7" s="15" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="H7" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I7" s="15" t="str">
+        <x:v>确认急停、接口、IP40和机械结构；主体为旧款Moz1而非Pro</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="42" customHeight="1">
+      <x:c r="A8" s="15" t="str">
+        <x:v>src_spirit_docs_sdk</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="str">
+        <x:v>spirit_moz1_pro</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="str">
+        <x:v>官方开发文档</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="str">
+        <x:v>MozRobot SDK v0.1.x</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="e">
+        <x:f>HYPERLINK("https://docs.spirit-ai.com/zh/sdk/get-started.html","https://docs.spirit-ai.com/zh/sdk/get-started.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://docs.spirit-ai.com/zh/sdk/get-started.html, friendlyName=https://docs.spirit-ai.com/zh/sdk/get-started.html</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="str"/>
+      <x:c r="G8" s="15" t="str">
+        <x:v>2026-09-17</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="str">
+        <x:v>确认ROS2 Humble、Python、最高120Hz及vx/vy/wz底盘指令；未开放力矩和末端力控</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" customHeight="1">
+      <x:c r="A9" s="15" t="str">
         <x:v>src_astribot_t1_home</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B9" s="15" t="str">
         <x:v>astribot_t1</x:v>
       </x:c>
-      <x:c r="C5" s="15" t="str">
+      <x:c r="C9" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
-      <x:c r="D5" s="15" t="str">
+      <x:c r="D9" s="15" t="str">
         <x:v>星尘智能首页 T1 发布信息</x:v>
       </x:c>
-      <x:c r="E5" s="15" t="e">
+      <x:c r="E9" s="15" t="e">
         <x:f>HYPERLINK("https://www.astribot.com/","https://www.astribot.com/")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.astribot.com/, friendlyName=https://www.astribot.com/</x:v>
-      </x:c>
-      <x:c r="F5" s="15" t="str"/>
-      <x:c r="G5" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H5" s="15" t="str">
-        <x:v>高</x:v>
-      </x:c>
-      <x:c r="I5" s="15" t="str">
-        <x:v>确认T1型号与8.99万元起售价；官网尚无T1完整数据表</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="42" customHeight="1">
-      <x:c r="A6" s="15" t="str">
-        <x:v>src_astribot_t1_wuxi</x:v>
-      </x:c>
-      <x:c r="B6" s="15" t="str">
-        <x:v>astribot_t1</x:v>
-      </x:c>
-      <x:c r="C6" s="15" t="str">
-        <x:v>政府公开信息</x:v>
-      </x:c>
-      <x:c r="D6" s="15" t="str">
-        <x:v>技术硬核价格亲民 多元场景显身手</x:v>
-      </x:c>
-      <x:c r="E6" s="15" t="e">
-        <x:f>HYPERLINK("https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml","https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml, friendlyName=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml</x:v>
-      </x:c>
-      <x:c r="F6" s="15" t="str">
-        <x:v>2026-07-11</x:v>
-      </x:c>
-      <x:c r="G6" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H6" s="15" t="str">
-        <x:v>高</x:v>
-      </x:c>
-      <x:c r="I6" s="15" t="str">
-        <x:v>确认无锡工厂量产下线、23自由度、单臂5kg、绳驱和底盘扩展接口</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="42" customHeight="1">
-      <x:c r="A7" s="15" t="str">
-        <x:v>src_astribot_t1_sznews</x:v>
-      </x:c>
-      <x:c r="B7" s="15" t="str">
-        <x:v>astribot_t1</x:v>
-      </x:c>
-      <x:c r="C7" s="15" t="str">
-        <x:v>地方官方媒体</x:v>
-      </x:c>
-      <x:c r="D7" s="15" t="str">
-        <x:v>煎牛排调酒做实验 星尘智能发布绳驱AI机器人T1</x:v>
-      </x:c>
-      <x:c r="E7" s="15" t="e">
-        <x:f>HYPERLINK("https://www.sznews.com/news/content/2026-05/27/content_32067943.htm","https://www.sznews.com/news/content/2026-05/27/content_32067943.htm")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm, friendlyName=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm</x:v>
-      </x:c>
-      <x:c r="F7" s="15" t="str">
-        <x:v>2026-05-27</x:v>
-      </x:c>
-      <x:c r="G7" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H7" s="15" t="str">
-        <x:v>中</x:v>
-      </x:c>
-      <x:c r="I7" s="15" t="str">
-        <x:v>确认155cm、约66kg、23自由度不含末端、单臂5kg、自动回充和快捷换电</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="42" customHeight="1">
-      <x:c r="A8" s="15" t="str">
-        <x:v>src_astribot_t1_wrc</x:v>
-      </x:c>
-      <x:c r="B8" s="15" t="str">
-        <x:v>astribot_t1</x:v>
-      </x:c>
-      <x:c r="C8" s="15" t="str">
-        <x:v>行业展会官方信息</x:v>
-      </x:c>
-      <x:c r="D8" s="15" t="str">
-        <x:v>2026世界机器人大会星尘智能展品介绍</x:v>
-      </x:c>
-      <x:c r="E8" s="15" t="e">
-        <x:f>HYPERLINK("https://wrc.cie.org.cn/expo/company/441.html","https://wrc.cie.org.cn/expo/company/441.html")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://wrc.cie.org.cn/expo/company/441.html, friendlyName=https://wrc.cie.org.cn/expo/company/441.html</x:v>
-      </x:c>
-      <x:c r="F8" s="15" t="str">
-        <x:v>2026-08-19</x:v>
-      </x:c>
-      <x:c r="G8" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H8" s="15" t="str">
-        <x:v>中高</x:v>
-      </x:c>
-      <x:c r="I8" s="15" t="str">
-        <x:v>确认轻量化机身、紧凑底盘、多样末端和软硬件扩展；未披露轮系</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="42" customHeight="1">
-      <x:c r="A9" s="15" t="str">
-        <x:v>src_unitree_g1d</x:v>
-      </x:c>
-      <x:c r="B9" s="15" t="str">
-        <x:v>unitree_g1d_flagship</x:v>
-      </x:c>
-      <x:c r="C9" s="15" t="str">
-        <x:v>官方网站</x:v>
-      </x:c>
-      <x:c r="D9" s="15" t="str">
-        <x:v>Unitree G1-D产品参数</x:v>
-      </x:c>
-      <x:c r="E9" s="15" t="e">
-        <x:f>HYPERLINK("https://www.unitree.com/cn/mobile/G1-D/","https://www.unitree.com/cn/mobile/G1-D/")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.unitree.com/cn/mobile/G1-D/, friendlyName=https://www.unitree.com/cn/mobile/G1-D/</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str"/>
       <x:c r="G9" s="15" t="str">
@@ -5449,164 +5833,172 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I9" s="15" t="str">
-        <x:v>同时覆盖旗舰版和通用版</x:v>
+        <x:v>确认T1型号与8.99万元起售价；官网尚无T1完整数据表</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="42" customHeight="1">
       <x:c r="A10" s="15" t="str">
-        <x:v>src_unitree_g1d_std</x:v>
+        <x:v>src_astribot_t1_wuxi</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>unitree_g1d_standard</x:v>
+        <x:v>astribot_t1</x:v>
       </x:c>
       <x:c r="C10" s="15" t="str">
+        <x:v>政府公开信息</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
+        <x:v>技术硬核价格亲民 多元场景显身手</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="e">
+        <x:f>HYPERLINK("https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml","https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml, friendlyName=https://www.wuxi.gov.cn/doc/2026/07/11/4803940.shtml</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="str">
+        <x:v>2026-07-11</x:v>
+      </x:c>
+      <x:c r="G10" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H10" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I10" s="15" t="str">
+        <x:v>确认无锡工厂量产下线、23自由度、单臂5kg、绳驱和底盘扩展接口</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="42" customHeight="1">
+      <x:c r="A11" s="15" t="str">
+        <x:v>src_astribot_t1_sznews</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="str">
+        <x:v>astribot_t1</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="str">
+        <x:v>地方官方媒体</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
+        <x:v>煎牛排调酒做实验 星尘智能发布绳驱AI机器人T1</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="e">
+        <x:f>HYPERLINK("https://www.sznews.com/news/content/2026-05/27/content_32067943.htm","https://www.sznews.com/news/content/2026-05/27/content_32067943.htm")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm, friendlyName=https://www.sznews.com/news/content/2026-05/27/content_32067943.htm</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="str">
+        <x:v>2026-05-27</x:v>
+      </x:c>
+      <x:c r="G11" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H11" s="15" t="str">
+        <x:v>中</x:v>
+      </x:c>
+      <x:c r="I11" s="15" t="str">
+        <x:v>确认155cm、约66kg、23自由度不含末端、单臂5kg、自动回充和快捷换电</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="42" customHeight="1">
+      <x:c r="A12" s="15" t="str">
+        <x:v>src_astribot_t1_wrc</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="str">
+        <x:v>astribot_t1</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="str">
+        <x:v>行业展会官方信息</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>2026世界机器人大会星尘智能展品介绍</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="e">
+        <x:f>HYPERLINK("https://wrc.cie.org.cn/expo/company/441.html","https://wrc.cie.org.cn/expo/company/441.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://wrc.cie.org.cn/expo/company/441.html, friendlyName=https://wrc.cie.org.cn/expo/company/441.html</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="str">
+        <x:v>2026-08-19</x:v>
+      </x:c>
+      <x:c r="G12" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H12" s="15" t="str">
+        <x:v>中高</x:v>
+      </x:c>
+      <x:c r="I12" s="15" t="str">
+        <x:v>确认轻量化机身、紧凑底盘、多样末端和软硬件扩展；未披露轮系</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="42" customHeight="1">
+      <x:c r="A13" s="15" t="str">
+        <x:v>src_unitree_g1d</x:v>
+      </x:c>
+      <x:c r="B13" s="15" t="str">
+        <x:v>unitree_g1d_flagship</x:v>
+      </x:c>
+      <x:c r="C13" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
-      <x:c r="D10" s="15" t="str">
+      <x:c r="D13" s="15" t="str">
         <x:v>Unitree G1-D产品参数</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="e">
+      <x:c r="E13" s="15" t="e">
         <x:f>HYPERLINK("https://www.unitree.com/cn/mobile/G1-D/","https://www.unitree.com/cn/mobile/G1-D/")</x:f>
         <x:v>HYPERLINK is not implemented. linkLocation=https://www.unitree.com/cn/mobile/G1-D/, friendlyName=https://www.unitree.com/cn/mobile/G1-D/</x:v>
-      </x:c>
-      <x:c r="F10" s="15" t="str"/>
-      <x:c r="G10" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H10" s="15" t="str">
-        <x:v>高</x:v>
-      </x:c>
-      <x:c r="I10" s="15" t="str">
-        <x:v>通用版无主动底盘参数</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="42" customHeight="1">
-      <x:c r="A11" s="15" t="str">
-        <x:v>src_zdl_d1</x:v>
-      </x:c>
-      <x:c r="B11" s="15" t="str">
-        <x:v>zdl_d1</x:v>
-      </x:c>
-      <x:c r="C11" s="15" t="str">
-        <x:v>供应商PDF</x:v>
-      </x:c>
-      <x:c r="D11" s="15" t="str">
-        <x:v>D1（擎骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E11" s="15" t="str">
-        <x:v>sources/raw/01_智动力/D1（擎骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="F11" s="15" t="str"/>
-      <x:c r="G11" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H11" s="15" t="str">
-        <x:v>中</x:v>
-      </x:c>
-      <x:c r="I11" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="42" customHeight="1">
-      <x:c r="A12" s="15" t="str">
-        <x:v>src_zdl_juno2</x:v>
-      </x:c>
-      <x:c r="B12" s="15" t="str">
-        <x:v>zdl_juno2</x:v>
-      </x:c>
-      <x:c r="C12" s="15" t="str">
-        <x:v>供应商PDF</x:v>
-      </x:c>
-      <x:c r="D12" s="15" t="str">
-        <x:v>JUNO2-SD（龙骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E12" s="15" t="str">
-        <x:v>sources/raw/01_智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="F12" s="15" t="str"/>
-      <x:c r="G12" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
-      <x:c r="H12" s="15" t="str">
-        <x:v>中</x:v>
-      </x:c>
-      <x:c r="I12" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="42" customHeight="1">
-      <x:c r="A13" s="15" t="str">
-        <x:v>src_zdl_juno1</x:v>
-      </x:c>
-      <x:c r="B13" s="15" t="str">
-        <x:v>zdl_juno1</x:v>
-      </x:c>
-      <x:c r="C13" s="15" t="str">
-        <x:v>供应商PDF</x:v>
-      </x:c>
-      <x:c r="D13" s="15" t="str">
-        <x:v>JUNO1-P（智骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E13" s="15" t="str">
-        <x:v>sources/raw/01_智动力/JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F13" s="15" t="str"/>
       <x:c r="G13" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H13" s="15" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I13" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
+        <x:v>同时覆盖旗舰版和通用版</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" customHeight="1">
       <x:c r="A14" s="15" t="str">
-        <x:v>src_zdl_l1</x:v>
+        <x:v>src_unitree_g1d_std</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>zdl_l1</x:v>
+        <x:v>unitree_g1d_standard</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>供应商PDF</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>L1（灵骏系列）.pdf</x:v>
-      </x:c>
-      <x:c r="E14" s="15" t="str">
-        <x:v>sources/raw/01_智动力/L1（灵骏系列）.pdf</x:v>
+        <x:v>Unitree G1-D产品参数</x:v>
+      </x:c>
+      <x:c r="E14" s="15" t="e">
+        <x:f>HYPERLINK("https://www.unitree.com/cn/mobile/G1-D/","https://www.unitree.com/cn/mobile/G1-D/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.unitree.com/cn/mobile/G1-D/, friendlyName=https://www.unitree.com/cn/mobile/G1-D/</x:v>
       </x:c>
       <x:c r="F14" s="15" t="str"/>
       <x:c r="G14" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H14" s="15" t="str">
-        <x:v>中</x:v>
+        <x:v>高</x:v>
       </x:c>
       <x:c r="I14" s="15" t="str">
-        <x:v>供应商产品册，尚未实测</x:v>
+        <x:v>通用版无主动底盘参数</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" customHeight="1">
       <x:c r="A15" s="15" t="str">
-        <x:v>src_zdl_z1</x:v>
+        <x:v>src_zdl_d1</x:v>
       </x:c>
       <x:c r="B15" s="15" t="str">
-        <x:v>zdl_z1</x:v>
+        <x:v>zdl_d1</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>供应商开发手册</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
+        <x:v>D1（擎骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
-        <x:v>sources/raw/01_智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
-      </x:c>
-      <x:c r="F15" s="15" t="str">
-        <x:v>2026-07-25</x:v>
-      </x:c>
+        <x:v>sources/raw/01_智动力/D1（擎骏系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F15" s="15" t="str"/>
       <x:c r="G15" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5614,24 +6006,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I15" s="15" t="str">
-        <x:v>接口文档存在多项待澄清问题</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" customHeight="1">
       <x:c r="A16" s="15" t="str">
-        <x:v>src_zdl_ha</x:v>
+        <x:v>src_zdl_juno2</x:v>
       </x:c>
       <x:c r="B16" s="15" t="str">
-        <x:v>zdl_ha</x:v>
+        <x:v>zdl_juno2</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>人形臂（HA系列）.pdf</x:v>
+        <x:v>JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
-        <x:v>sources/raw/01_智动力/人形臂（HA系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/JUNO2-SD（龙骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F16" s="15" t="str"/>
       <x:c r="G16" s="15" t="str">
@@ -5641,24 +6033,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I16" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="42" customHeight="1">
       <x:c r="A17" s="15" t="str">
-        <x:v>src_zdl_fa</x:v>
+        <x:v>src_zdl_juno1</x:v>
       </x:c>
       <x:c r="B17" s="15" t="str">
-        <x:v>zdl_fa</x:v>
+        <x:v>zdl_juno1</x:v>
       </x:c>
       <x:c r="C17" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>桌面臂（FA系列）.pdf</x:v>
+        <x:v>JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
-        <x:v>sources/raw/01_智动力/桌面臂（FA系列）.pdf</x:v>
+        <x:v>sources/raw/01_智动力/JUNO1-P（智骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F17" s="15" t="str"/>
       <x:c r="G17" s="15" t="str">
@@ -5668,24 +6060,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I17" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" customHeight="1">
       <x:c r="A18" s="15" t="str">
-        <x:v>src_flexiv_rizon4_manual</x:v>
+        <x:v>src_zdl_l1</x:v>
       </x:c>
       <x:c r="B18" s="15" t="str">
-        <x:v>flexiv_rizon4</x:v>
+        <x:v>zdl_l1</x:v>
       </x:c>
       <x:c r="C18" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+        <x:v>L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+        <x:v>sources/raw/01_智动力/L1（灵骏系列）.pdf</x:v>
       </x:c>
       <x:c r="F18" s="15" t="str"/>
       <x:c r="G18" s="15" t="str">
@@ -5695,27 +6087,27 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I18" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>供应商产品册，尚未实测</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" customHeight="1">
       <x:c r="A19" s="15" t="str">
-        <x:v>src_flexiv_rizon_datasheet</x:v>
+        <x:v>src_zdl_z1</x:v>
       </x:c>
       <x:c r="B19" s="15" t="str">
-        <x:v>flexiv_rizon</x:v>
+        <x:v>zdl_z1</x:v>
       </x:c>
       <x:c r="C19" s="15" t="str">
-        <x:v>供应商PDF</x:v>
+        <x:v>供应商开发手册</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+        <x:v>全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+        <x:v>sources/raw/01_智动力/全尺寸人形机器人Z1开发手册 r26.6.md</x:v>
       </x:c>
       <x:c r="F19" s="15" t="str">
-        <x:v>2024-09</x:v>
+        <x:v>2026-07-25</x:v>
       </x:c>
       <x:c r="G19" s="15" t="str">
         <x:v>2026-09-15</x:v>
@@ -5724,28 +6116,26 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I19" s="15" t="str">
-        <x:v>待纳入机械臂专项对比</x:v>
+        <x:v>接口文档存在多项待澄清问题</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" customHeight="1">
       <x:c r="A20" s="15" t="str">
-        <x:v>src_flexiv_grav_manual</x:v>
+        <x:v>src_zdl_ha</x:v>
       </x:c>
       <x:c r="B20" s="15" t="str">
-        <x:v>flexiv_grav</x:v>
+        <x:v>zdl_ha</x:v>
       </x:c>
       <x:c r="C20" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>星擎用户手册_V1.0_202404(2).pdf</x:v>
+        <x:v>人形臂（HA系列）.pdf</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/02_Grav_星擎/星擎用户手册_V1.0_202404(2).pdf</x:v>
-      </x:c>
-      <x:c r="F20" s="15" t="str">
-        <x:v>2024-04</x:v>
-      </x:c>
+        <x:v>sources/raw/01_智动力/人形臂（HA系列）.pdf</x:v>
+      </x:c>
+      <x:c r="F20" s="15" t="str"/>
       <x:c r="G20" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5753,24 +6143,24 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I20" s="15" t="str">
-        <x:v>末端执行器资料待结构化</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" customHeight="1">
       <x:c r="A21" s="15" t="str">
-        <x:v>src_flexiv_ft_datasheet</x:v>
+        <x:v>src_zdl_fa</x:v>
       </x:c>
       <x:c r="B21" s="15" t="str">
-        <x:v>flexiv_ft</x:v>
+        <x:v>zdl_fa</x:v>
       </x:c>
       <x:c r="C21" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+        <x:v>桌面臂（FA系列）.pdf</x:v>
       </x:c>
       <x:c r="E21" s="15" t="str">
-        <x:v>sources/raw/02_非夕_Flexiv/03_FT_拂晓传感器/拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+        <x:v>sources/raw/01_智动力/桌面臂（FA系列）.pdf</x:v>
       </x:c>
       <x:c r="F21" s="15" t="str"/>
       <x:c r="G21" s="15" t="str">
@@ -5780,28 +6170,26 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I21" s="15" t="str">
-        <x:v>力传感器资料待结构化</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="42" customHeight="1">
       <x:c r="A22" s="15" t="str">
-        <x:v>src_tianji_marvin</x:v>
+        <x:v>src_flexiv_rizon4_manual</x:v>
       </x:c>
       <x:c r="B22" s="15" t="str">
-        <x:v>tianji_marvin_m6ccs</x:v>
+        <x:v>flexiv_rizon4</x:v>
       </x:c>
       <x:c r="C22" s="15" t="str">
         <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
+        <x:v>Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
       </x:c>
       <x:c r="E22" s="15" t="str">
-        <x:v>sources/raw/03_天机智能_Marvin/01_Marvin双臂/Marvin系列 三折页 250721-CN.pdf</x:v>
-      </x:c>
-      <x:c r="F22" s="15" t="str">
-        <x:v>2025-07</x:v>
-      </x:c>
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/Rizon4 用户手册_V3.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="F22" s="15" t="str"/>
       <x:c r="G22" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5809,24 +6197,28 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I22" s="15" t="str">
-        <x:v>单臂/双臂模块参数，不含标准底盘</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="42" customHeight="1">
       <x:c r="A23" s="15" t="str">
-        <x:v>src_material_index</x:v>
-      </x:c>
-      <x:c r="B23" s="15" t="str"/>
+        <x:v>src_flexiv_rizon_datasheet</x:v>
+      </x:c>
+      <x:c r="B23" s="15" t="str">
+        <x:v>flexiv_rizon</x:v>
+      </x:c>
       <x:c r="C23" s="15" t="str">
-        <x:v>内部索引</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>供应链材料索引.md</x:v>
+        <x:v>拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
       </x:c>
       <x:c r="E23" s="15" t="str">
-        <x:v>sources/raw/00_索引/供应链材料索引.md</x:v>
-      </x:c>
-      <x:c r="F23" s="15" t="str"/>
+        <x:v>sources/raw/02_非夕_Flexiv/01_Rizon_拂晓/拂晓(Rizon)机器人数据表_V2.0_202409.pdf</x:v>
+      </x:c>
+      <x:c r="F23" s="15" t="str">
+        <x:v>2024-09</x:v>
+      </x:c>
       <x:c r="G23" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -5834,141 +6226,135 @@
         <x:v>中</x:v>
       </x:c>
       <x:c r="I23" s="15" t="str">
-        <x:v>原目录索引的归档副本</x:v>
+        <x:v>待纳入机械臂专项对比</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="42" customHeight="1">
       <x:c r="A24" s="15" t="str">
-        <x:v>src_boston_atlas</x:v>
+        <x:v>src_flexiv_grav_manual</x:v>
       </x:c>
       <x:c r="B24" s="15" t="str">
-        <x:v>boston_atlas_2026</x:v>
+        <x:v>flexiv_grav</x:v>
       </x:c>
       <x:c r="C24" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
-        <x:v>Atlas产品与规格</x:v>
-      </x:c>
-      <x:c r="E24" s="15" t="e">
-        <x:f>HYPERLINK("https://bostondynamics.com/products/atlas/","https://bostondynamics.com/products/atlas/")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://bostondynamics.com/products/atlas/, friendlyName=https://bostondynamics.com/products/atlas/</x:v>
-      </x:c>
-      <x:c r="F24" s="15" t="str"/>
+        <x:v>星擎用户手册_V1.0_202404(2).pdf</x:v>
+      </x:c>
+      <x:c r="E24" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/02_Grav_星擎/星擎用户手册_V1.0_202404(2).pdf</x:v>
+      </x:c>
+      <x:c r="F24" s="15" t="str">
+        <x:v>2024-04</x:v>
+      </x:c>
       <x:c r="G24" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H24" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I24" s="15" t="str">
-        <x:v>披露56自由度、负载、续航、IP67、工作范围和Orbit集成</x:v>
+        <x:v>末端执行器资料待结构化</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="42" customHeight="1">
       <x:c r="A25" s="15" t="str">
-        <x:v>src_figure03_product</x:v>
+        <x:v>src_flexiv_ft_datasheet</x:v>
       </x:c>
       <x:c r="B25" s="15" t="str">
-        <x:v>figure_03</x:v>
+        <x:v>flexiv_ft</x:v>
       </x:c>
       <x:c r="C25" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>Figure 03产品页</x:v>
-      </x:c>
-      <x:c r="E25" s="15" t="e">
-        <x:f>HYPERLINK("https://www.figure.ai/figure","https://www.figure.ai/figure")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/figure, friendlyName=https://www.figure.ai/figure</x:v>
+        <x:v>拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="str">
+        <x:v>sources/raw/02_非夕_Flexiv/03_FT_拂晓传感器/拂晓 F_T 传感器数据表_V1.0_zh-CN.pdf</x:v>
       </x:c>
       <x:c r="F25" s="15" t="str"/>
       <x:c r="G25" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H25" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I25" s="15" t="str">
-        <x:v>披露身高、重量、负载、速度和续航</x:v>
+        <x:v>力传感器资料待结构化</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="42" customHeight="1">
       <x:c r="A26" s="15" t="str">
-        <x:v>src_figure03_intro</x:v>
+        <x:v>src_tianji_marvin</x:v>
       </x:c>
       <x:c r="B26" s="15" t="str">
-        <x:v>figure_03</x:v>
+        <x:v>tianji_marvin_m6ccs</x:v>
       </x:c>
       <x:c r="C26" s="15" t="str">
-        <x:v>官方技术文章</x:v>
+        <x:v>供应商PDF</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>Introducing Figure 03</x:v>
-      </x:c>
-      <x:c r="E26" s="15" t="e">
-        <x:f>HYPERLINK("https://www.figure.ai/news/introducing-figure-03","https://www.figure.ai/news/introducing-figure-03")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/introducing-figure-03, friendlyName=https://www.figure.ai/news/introducing-figure-03</x:v>
+        <x:v>Marvin系列 三折页 250721-CN.pdf</x:v>
+      </x:c>
+      <x:c r="E26" s="15" t="str">
+        <x:v>sources/raw/03_天机智能_Marvin/01_Marvin双臂/Marvin系列 三折页 250721-CN.pdf</x:v>
       </x:c>
       <x:c r="F26" s="15" t="str">
-        <x:v>2025-10-09</x:v>
+        <x:v>2025-07</x:v>
       </x:c>
       <x:c r="G26" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H26" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I26" s="15" t="str">
-        <x:v>披露触觉、感知、充电、电池安全和量产设计</x:v>
+        <x:v>单臂/双臂模块参数，不含标准底盘</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="42" customHeight="1">
       <x:c r="A27" s="15" t="str">
-        <x:v>src_figure03_bmw</x:v>
-      </x:c>
-      <x:c r="B27" s="15" t="str">
-        <x:v>figure_03</x:v>
-      </x:c>
+        <x:v>src_material_index</x:v>
+      </x:c>
+      <x:c r="B27" s="15" t="str"/>
       <x:c r="C27" s="15" t="str">
-        <x:v>官方客户进展</x:v>
+        <x:v>内部索引</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>F.03 Arrives at BMW</x:v>
-      </x:c>
-      <x:c r="E27" s="15" t="e">
-        <x:f>HYPERLINK("https://www.figure.ai/news/f-03-at-bmw","https://www.figure.ai/news/f-03-at-bmw")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/f-03-at-bmw, friendlyName=https://www.figure.ai/news/f-03-at-bmw</x:v>
-      </x:c>
-      <x:c r="F27" s="15" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
+        <x:v>供应链材料索引.md</x:v>
+      </x:c>
+      <x:c r="E27" s="15" t="str">
+        <x:v>sources/raw/00_索引/供应链材料索引.md</x:v>
+      </x:c>
+      <x:c r="F27" s="15" t="str"/>
       <x:c r="G27" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H27" s="15" t="str">
-        <x:v>高</x:v>
+        <x:v>中</x:v>
       </x:c>
       <x:c r="I27" s="15" t="str">
-        <x:v>披露BMW工厂物流验证和全身操作</x:v>
+        <x:v>原目录索引的归档副本</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="42" customHeight="1">
       <x:c r="A28" s="15" t="str">
-        <x:v>src_tesla_ai</x:v>
+        <x:v>src_boston_atlas</x:v>
       </x:c>
       <x:c r="B28" s="15" t="str">
-        <x:v>tesla_optimus</x:v>
+        <x:v>boston_atlas_2026</x:v>
       </x:c>
       <x:c r="C28" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>Tesla AI and Robotics</x:v>
+        <x:v>Atlas产品与规格</x:v>
       </x:c>
       <x:c r="E28" s="15" t="e">
-        <x:f>HYPERLINK("https://www.tesla.com/AI","https://www.tesla.com/AI")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.tesla.com/AI, friendlyName=https://www.tesla.com/AI</x:v>
+        <x:f>HYPERLINK("https://bostondynamics.com/products/atlas/","https://bostondynamics.com/products/atlas/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://bostondynamics.com/products/atlas/, friendlyName=https://bostondynamics.com/products/atlas/</x:v>
       </x:c>
       <x:c r="F28" s="15" t="str"/>
       <x:c r="G28" s="15" t="str">
@@ -5978,29 +6364,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I28" s="15" t="str">
-        <x:v>仅说明双足通用自主机器人目标；未给工程规格</x:v>
+        <x:v>披露56自由度、负载、续航、IP67、工作范围和Orbit集成</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="42" customHeight="1">
       <x:c r="A29" s="15" t="str">
-        <x:v>src_tesla_2026q2</x:v>
+        <x:v>src_figure03_product</x:v>
       </x:c>
       <x:c r="B29" s="15" t="str">
-        <x:v>tesla_optimus</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C29" s="15" t="str">
-        <x:v>官方投资者文件</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
-        <x:v>Tesla 2026 Q2 Update</x:v>
+        <x:v>Figure 03产品页</x:v>
       </x:c>
       <x:c r="E29" s="15" t="e">
-        <x:f>HYPERLINK("https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf","https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf, friendlyName=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf</x:v>
-      </x:c>
-      <x:c r="F29" s="15" t="str">
-        <x:v>2026-07-22</x:v>
-      </x:c>
+        <x:f>HYPERLINK("https://www.figure.ai/figure","https://www.figure.ai/figure")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/figure, friendlyName=https://www.figure.ai/figure</x:v>
+      </x:c>
+      <x:c r="F29" s="15" t="str"/>
       <x:c r="G29" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6008,27 +6392,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I29" s="15" t="str">
-        <x:v>披露Optimus产线建设与训练数据用途；未给本体规格</x:v>
+        <x:v>披露身高、重量、负载、速度和续航</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="42" customHeight="1">
       <x:c r="A30" s="15" t="str">
-        <x:v>src_limx_oli</x:v>
+        <x:v>src_figure03_intro</x:v>
       </x:c>
       <x:c r="B30" s="15" t="str">
-        <x:v>limx_oli_edu</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C30" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>官方技术文章</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
-        <x:v>LimX Oli产品参数</x:v>
+        <x:v>Introducing Figure 03</x:v>
       </x:c>
       <x:c r="E30" s="15" t="e">
-        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/oli/spec","https://www.limxdynamics.com/zh/products/oli/spec")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/oli/spec, friendlyName=https://www.limxdynamics.com/zh/products/oli/spec</x:v>
-      </x:c>
-      <x:c r="F30" s="15" t="str"/>
+        <x:f>HYPERLINK("https://www.figure.ai/news/introducing-figure-03","https://www.figure.ai/news/introducing-figure-03")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/introducing-figure-03, friendlyName=https://www.figure.ai/news/introducing-figure-03</x:v>
+      </x:c>
+      <x:c r="F30" s="15" t="str">
+        <x:v>2025-10-09</x:v>
+      </x:c>
       <x:c r="G30" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6036,27 +6422,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I30" s="15" t="str">
-        <x:v>披露自由度、尺寸、负载、续航、算力和开发接口</x:v>
+        <x:v>披露触觉、感知、充电、电池安全和量产设计</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="42" customHeight="1">
       <x:c r="A31" s="15" t="str">
-        <x:v>src_limx_tron2</x:v>
+        <x:v>src_figure03_bmw</x:v>
       </x:c>
       <x:c r="B31" s="15" t="str">
-        <x:v>limx_tron2_dualarm</x:v>
+        <x:v>figure_03</x:v>
       </x:c>
       <x:c r="C31" s="15" t="str">
-        <x:v>官方网站</x:v>
+        <x:v>官方客户进展</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
-        <x:v>TRON 2产品参数</x:v>
+        <x:v>F.03 Arrives at BMW</x:v>
       </x:c>
       <x:c r="E31" s="15" t="e">
-        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/tron2/spec","https://www.limxdynamics.com/zh/products/tron2/spec")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/tron2/spec, friendlyName=https://www.limxdynamics.com/zh/products/tron2/spec</x:v>
-      </x:c>
-      <x:c r="F31" s="15" t="str"/>
+        <x:f>HYPERLINK("https://www.figure.ai/news/f-03-at-bmw","https://www.figure.ai/news/f-03-at-bmw")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.figure.ai/news/f-03-at-bmw, friendlyName=https://www.figure.ai/news/f-03-at-bmw</x:v>
+      </x:c>
+      <x:c r="F31" s="15" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
       <x:c r="G31" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6064,25 +6452,25 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I31" s="15" t="str">
-        <x:v>披露双臂负载精度、多形态移动、接口和开发工具</x:v>
+        <x:v>披露BMW工厂物流验证和全身操作</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="42" customHeight="1">
       <x:c r="A32" s="15" t="str">
-        <x:v>src_galaxea_r1pro_product</x:v>
+        <x:v>src_tesla_ai</x:v>
       </x:c>
       <x:c r="B32" s="15" t="str">
-        <x:v>galaxea_r1pro_2026</x:v>
+        <x:v>tesla_optimus</x:v>
       </x:c>
       <x:c r="C32" s="15" t="str">
         <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>R1 Pro产品参数</x:v>
+        <x:v>Tesla AI and Robotics</x:v>
       </x:c>
       <x:c r="E32" s="15" t="e">
-        <x:f>HYPERLINK("https://galaxea-ai.com/cn/products/R1-Pro","https://galaxea-ai.com/cn/products/R1-Pro")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://galaxea-ai.com/cn/products/R1-Pro, friendlyName=https://galaxea-ai.com/cn/products/R1-Pro</x:v>
+        <x:f>HYPERLINK("https://www.tesla.com/AI","https://www.tesla.com/AI")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.tesla.com/AI, friendlyName=https://www.tesla.com/AI</x:v>
       </x:c>
       <x:c r="F32" s="15" t="str"/>
       <x:c r="G32" s="15" t="str">
@@ -6092,27 +6480,29 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I32" s="15" t="str">
-        <x:v>披露三舵轮全向底盘、双臂负载、工作空间和算力</x:v>
+        <x:v>仅说明双足通用自主机器人目标；未给工程规格</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="42" customHeight="1">
       <x:c r="A33" s="15" t="str">
-        <x:v>src_galaxea_r1pro_docs</x:v>
+        <x:v>src_tesla_2026q2</x:v>
       </x:c>
       <x:c r="B33" s="15" t="str">
-        <x:v>galaxea_r1pro_2026</x:v>
+        <x:v>tesla_optimus</x:v>
       </x:c>
       <x:c r="C33" s="15" t="str">
-        <x:v>官方开发文档</x:v>
+        <x:v>官方投资者文件</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
-        <x:v>R1 Pro 2026硬件说明</x:v>
+        <x:v>Tesla 2026 Q2 Update</x:v>
       </x:c>
       <x:c r="E33" s="15" t="e">
-        <x:f>HYPERLINK("https://docs.galaxea-dynamics.com/R1Pro/docs/2026/","https://docs.galaxea-dynamics.com/R1Pro/docs/2026/")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/, friendlyName=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/</x:v>
-      </x:c>
-      <x:c r="F33" s="15" t="str"/>
+        <x:f>HYPERLINK("https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf","https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf, friendlyName=https://ir.tesla.com/_flysystem/s3/sec/000162828026049213/tsla-20260722-gen.pdf</x:v>
+      </x:c>
+      <x:c r="F33" s="15" t="str">
+        <x:v>2026-07-22</x:v>
+      </x:c>
       <x:c r="G33" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6120,29 +6510,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I33" s="15" t="str">
-        <x:v>披露重量、电池、夹爪、接口和机械臂无制动器风险</x:v>
+        <x:v>披露Optimus产线建设与训练数据用途；未给本体规格</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="42" customHeight="1">
       <x:c r="A34" s="15" t="str">
-        <x:v>src_tars_tianhai</x:v>
+        <x:v>src_limx_oli</x:v>
       </x:c>
       <x:c r="B34" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>limx_oli_edu</x:v>
       </x:c>
       <x:c r="C34" s="15" t="str">
-        <x:v>客户官方新闻</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>天海电子与它石智航战略合作</x:v>
+        <x:v>LimX Oli产品参数</x:v>
       </x:c>
       <x:c r="E34" s="15" t="e">
-        <x:f>HYPERLINK("https://www.thb.com.cn/content/details_17_319668.html","https://www.thb.com.cn/content/details_17_319668.html")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thb.com.cn/content/details_17_319668.html, friendlyName=https://www.thb.com.cn/content/details_17_319668.html</x:v>
-      </x:c>
-      <x:c r="F34" s="15" t="str">
-        <x:v>2026-06-28</x:v>
-      </x:c>
+        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/oli/spec","https://www.limxdynamics.com/zh/products/oli/spec")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/oli/spec, friendlyName=https://www.limxdynamics.com/zh/products/oli/spec</x:v>
+      </x:c>
+      <x:c r="F34" s="15" t="str"/>
       <x:c r="G34" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6150,29 +6538,27 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I34" s="15" t="str">
-        <x:v>确认汽车线束联合产线与近半年联合攻坚</x:v>
+        <x:v>披露自由度、尺寸、负载、续航、算力和开发接口</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="42" customHeight="1">
       <x:c r="A35" s="15" t="str">
-        <x:v>src_tars_shanghai</x:v>
+        <x:v>src_limx_tron2</x:v>
       </x:c>
       <x:c r="B35" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>limx_tron2_dualarm</x:v>
       </x:c>
       <x:c r="C35" s="15" t="str">
-        <x:v>政府官方信息</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>它石智航产业化闭环</x:v>
+        <x:v>TRON 2产品参数</x:v>
       </x:c>
       <x:c r="E35" s="15" t="e">
-        <x:f>HYPERLINK("https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html","https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html, friendlyName=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html</x:v>
-      </x:c>
-      <x:c r="F35" s="15" t="str">
-        <x:v>2026-07-10</x:v>
-      </x:c>
+        <x:f>HYPERLINK("https://www.limxdynamics.com/zh/products/tron2/spec","https://www.limxdynamics.com/zh/products/tron2/spec")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.limxdynamics.com/zh/products/tron2/spec, friendlyName=https://www.limxdynamics.com/zh/products/tron2/spec</x:v>
+      </x:c>
+      <x:c r="F35" s="15" t="str"/>
       <x:c r="G35" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
@@ -6180,25 +6566,25 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I35" s="15" t="str">
-        <x:v>披露安波福百台计划、33类场景、46工位和DexHand</x:v>
+        <x:v>披露双臂负载精度、多形态移动、接口和开发工具</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="42" customHeight="1">
       <x:c r="A36" s="15" t="str">
-        <x:v>src_tars_guinness</x:v>
+        <x:v>src_galaxea_r1pro_product</x:v>
       </x:c>
       <x:c r="B36" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>galaxea_r1pro_2026</x:v>
       </x:c>
       <x:c r="C36" s="15" t="str">
-        <x:v>独立纪录机构</x:v>
+        <x:v>官方网站</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
-        <x:v>Most sub-millimeter wire harness assembled by a robot in one hour</x:v>
+        <x:v>R1 Pro产品参数</x:v>
       </x:c>
       <x:c r="E36" s="15" t="e">
-        <x:f>HYPERLINK("https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour","https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour")</x:f>
-        <x:v>HYPERLINK is not implemented. linkLocation=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour, friendlyName=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour</x:v>
+        <x:f>HYPERLINK("https://galaxea-ai.com/cn/products/R1-Pro","https://galaxea-ai.com/cn/products/R1-Pro")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://galaxea-ai.com/cn/products/R1-Pro, friendlyName=https://galaxea-ai.com/cn/products/R1-Pro</x:v>
       </x:c>
       <x:c r="F36" s="15" t="str"/>
       <x:c r="G36" s="15" t="str">
@@ -6208,35 +6594,151 @@
         <x:v>高</x:v>
       </x:c>
       <x:c r="I36" s="15" t="str">
-        <x:v>确认一小时105次亚毫米线束装配纪录</x:v>
+        <x:v>披露三舵轮全向底盘、双臂负载、工作空间和算力</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="42" customHeight="1">
       <x:c r="A37" s="15" t="str">
-        <x:v>src_tars_internal</x:v>
+        <x:v>src_galaxea_r1pro_docs</x:v>
       </x:c>
       <x:c r="B37" s="15" t="str">
-        <x:v>tars_a1</x:v>
+        <x:v>galaxea_r1pro_2026</x:v>
       </x:c>
       <x:c r="C37" s="15" t="str">
-        <x:v>内部沟通</x:v>
+        <x:v>官方开发文档</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
-        <x:v>它石线束部署与工程问题纪要</x:v>
-      </x:c>
-      <x:c r="E37" s="15" t="str">
-        <x:v>conversation-context:2026-09-15</x:v>
-      </x:c>
-      <x:c r="F37" s="15" t="str">
-        <x:v>2026-09-15</x:v>
-      </x:c>
+        <x:v>R1 Pro 2026硬件说明</x:v>
+      </x:c>
+      <x:c r="E37" s="15" t="e">
+        <x:f>HYPERLINK("https://docs.galaxea-dynamics.com/R1Pro/docs/2026/","https://docs.galaxea-dynamics.com/R1Pro/docs/2026/")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/, friendlyName=https://docs.galaxea-dynamics.com/R1Pro/docs/2026/</x:v>
+      </x:c>
+      <x:c r="F37" s="15" t="str"/>
       <x:c r="G37" s="15" t="str">
         <x:v>2026-09-15</x:v>
       </x:c>
       <x:c r="H37" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I37" s="15" t="str">
+        <x:v>披露重量、电池、夹爪、接口和机械臂无制动器风险</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="42" customHeight="1">
+      <x:c r="A38" s="15" t="str">
+        <x:v>src_tars_tianhai</x:v>
+      </x:c>
+      <x:c r="B38" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C38" s="15" t="str">
+        <x:v>客户官方新闻</x:v>
+      </x:c>
+      <x:c r="D38" s="15" t="str">
+        <x:v>天海电子与它石智航战略合作</x:v>
+      </x:c>
+      <x:c r="E38" s="15" t="e">
+        <x:f>HYPERLINK("https://www.thb.com.cn/content/details_17_319668.html","https://www.thb.com.cn/content/details_17_319668.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.thb.com.cn/content/details_17_319668.html, friendlyName=https://www.thb.com.cn/content/details_17_319668.html</x:v>
+      </x:c>
+      <x:c r="F38" s="15" t="str">
+        <x:v>2026-06-28</x:v>
+      </x:c>
+      <x:c r="G38" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H38" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I38" s="15" t="str">
+        <x:v>确认汽车线束联合产线与近半年联合攻坚</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="42" customHeight="1">
+      <x:c r="A39" s="15" t="str">
+        <x:v>src_tars_shanghai</x:v>
+      </x:c>
+      <x:c r="B39" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C39" s="15" t="str">
+        <x:v>政府官方信息</x:v>
+      </x:c>
+      <x:c r="D39" s="15" t="str">
+        <x:v>它石智航产业化闭环</x:v>
+      </x:c>
+      <x:c r="E39" s="15" t="e">
+        <x:f>HYPERLINK("https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html","https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html, friendlyName=https://www.sheitc.sh.gov.cn/zxxx/20260710/480d32461ca145e3bf067ce67dc6c203.html</x:v>
+      </x:c>
+      <x:c r="F39" s="15" t="str">
+        <x:v>2026-07-10</x:v>
+      </x:c>
+      <x:c r="G39" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H39" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I39" s="15" t="str">
+        <x:v>披露安波福百台计划、33类场景、46工位和DexHand</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="42" customHeight="1">
+      <x:c r="A40" s="15" t="str">
+        <x:v>src_tars_guinness</x:v>
+      </x:c>
+      <x:c r="B40" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C40" s="15" t="str">
+        <x:v>独立纪录机构</x:v>
+      </x:c>
+      <x:c r="D40" s="15" t="str">
+        <x:v>Most sub-millimeter wire harness assembled by a robot in one hour</x:v>
+      </x:c>
+      <x:c r="E40" s="15" t="e">
+        <x:f>HYPERLINK("https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour","https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour")</x:f>
+        <x:v>HYPERLINK is not implemented. linkLocation=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour, friendlyName=https://guinnessworldrecords.com.br/world-records/782788-most-sub-millimeter-wire-harness-assembled-by-a-robot-in-one-hour</x:v>
+      </x:c>
+      <x:c r="F40" s="15" t="str"/>
+      <x:c r="G40" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H40" s="15" t="str">
+        <x:v>高</x:v>
+      </x:c>
+      <x:c r="I40" s="15" t="str">
+        <x:v>确认一小时105次亚毫米线束装配纪录</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="42" customHeight="1">
+      <x:c r="A41" s="15" t="str">
+        <x:v>src_tars_internal</x:v>
+      </x:c>
+      <x:c r="B41" s="15" t="str">
+        <x:v>tars_a1</x:v>
+      </x:c>
+      <x:c r="C41" s="15" t="str">
+        <x:v>内部沟通</x:v>
+      </x:c>
+      <x:c r="D41" s="15" t="str">
+        <x:v>它石线束部署与工程问题纪要</x:v>
+      </x:c>
+      <x:c r="E41" s="15" t="str">
+        <x:v>conversation-context:2026-09-15</x:v>
+      </x:c>
+      <x:c r="F41" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="G41" s="15" t="str">
+        <x:v>2026-09-15</x:v>
+      </x:c>
+      <x:c r="H41" s="15" t="str">
         <x:v>待核验</x:v>
       </x:c>
-      <x:c r="I37" s="15" t="str">
+      <x:c r="I41" s="15" t="str">
         <x:v>反馈百台部署尚未达到要求并存在臂展、工装耗材、夹爪和MES依赖问题</x:v>
       </x:c>
     </x:row>
@@ -6246,7 +6748,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b3be9ef54844195"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf67f4ea7eebc48f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>